--- a/Tomodachi Life Living the Dream island dating analysis.xlsx
+++ b/Tomodachi Life Living the Dream island dating analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Robin\OneDrive\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1CB3271-3D29-4776-B8B8-2ACE5DDA4E4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F387BBB-17D7-4D51-AA45-72A7E59F335F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18700" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18700" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mii List" sheetId="1" r:id="rId1"/>
@@ -1347,7 +1347,7 @@
     <t>Greedy model: Miis pair with random compatible partners. Uses Poisson competition model with iterative pool depletion and competition-ratio correction for shared partner pools.</t>
   </si>
   <si>
-    <t>Tomodachi Life and Mii are trademarks of Nintendo. This work is not affiliated with or endorsed by Nintendo.</t>
+    <t>Tomodachi Life and Mii are trademarks of Nintendo. This project is not affiliated with or endorsed by Nintendo.</t>
   </si>
 </sst>
 </file>
@@ -9704,6 +9704,7 @@
       <c r="A273" s="38"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -21564,6 +21565,7 @@
       <c r="P200" s="52"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/Tomodachi Life Living the Dream island dating analysis.xlsx
+++ b/Tomodachi Life Living the Dream island dating analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Robin\OneDrive\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F387BBB-17D7-4D51-AA45-72A7E59F335F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{915F2B4A-D86F-42D6-82DC-5E64C225F5CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18700" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18700" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mii List" sheetId="1" r:id="rId1"/>
@@ -327,9 +327,6 @@
     <t>Rank</t>
   </si>
   <si>
-    <t>Probability of finding a match</t>
-  </si>
-  <si>
     <t># compatible</t>
   </si>
   <si>
@@ -1348,6 +1345,9 @@
   </si>
   <si>
     <t>Tomodachi Life and Mii are trademarks of Nintendo. This project is not affiliated with or endorsed by Nintendo.</t>
+  </si>
+  <si>
+    <t>Percentage of Miis compatible</t>
   </si>
 </sst>
 </file>
@@ -1852,14 +1852,14 @@
     <xf numFmtId="0" fontId="34" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Calculation" xfId="1" builtinId="22"/>
@@ -2179,7 +2179,7 @@
     </row>
     <row r="2" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B2" s="58" t="s">
         <v>10</v>
@@ -2210,7 +2210,7 @@
     </row>
     <row r="3" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B3" s="59" t="s">
         <v>13</v>
@@ -2241,7 +2241,7 @@
     </row>
     <row r="4" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B4" s="60" t="s">
         <v>6</v>
@@ -2272,7 +2272,7 @@
     </row>
     <row r="5" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B5" s="61" t="s">
         <v>6</v>
@@ -2298,7 +2298,7 @@
     </row>
     <row r="6" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B6" s="60" t="s">
         <v>6</v>
@@ -2315,7 +2315,7 @@
     </row>
     <row r="7" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B7" s="61" t="s">
         <v>6</v>
@@ -2332,7 +2332,7 @@
     </row>
     <row r="8" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B8" s="60" t="s">
         <v>6</v>
@@ -2349,7 +2349,7 @@
     </row>
     <row r="9" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B9" s="61" t="s">
         <v>6</v>
@@ -2366,7 +2366,7 @@
     </row>
     <row r="10" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B10" s="60" t="s">
         <v>6</v>
@@ -2383,7 +2383,7 @@
     </row>
     <row r="11" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B11" s="61" t="s">
         <v>6</v>
@@ -2400,7 +2400,7 @@
     </row>
     <row r="12" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B12" s="60" t="s">
         <v>6</v>
@@ -2417,7 +2417,7 @@
     </row>
     <row r="13" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B13" s="61" t="s">
         <v>6</v>
@@ -2434,7 +2434,7 @@
     </row>
     <row r="14" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B14" s="60" t="s">
         <v>6</v>
@@ -2451,7 +2451,7 @@
     </row>
     <row r="15" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B15" s="62" t="s">
         <v>10</v>
@@ -2468,7 +2468,7 @@
     </row>
     <row r="16" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B16" s="58" t="s">
         <v>10</v>
@@ -2485,7 +2485,7 @@
     </row>
     <row r="17" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B17" s="62" t="s">
         <v>10</v>
@@ -2502,7 +2502,7 @@
     </row>
     <row r="18" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B18" s="58" t="s">
         <v>10</v>
@@ -2519,7 +2519,7 @@
     </row>
     <row r="19" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B19" s="62" t="s">
         <v>10</v>
@@ -2536,7 +2536,7 @@
     </row>
     <row r="20" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B20" s="58" t="s">
         <v>10</v>
@@ -2553,7 +2553,7 @@
     </row>
     <row r="21" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B21" s="62" t="s">
         <v>10</v>
@@ -2570,7 +2570,7 @@
     </row>
     <row r="22" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B22" s="58" t="s">
         <v>10</v>
@@ -2587,7 +2587,7 @@
     </row>
     <row r="23" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B23" s="62" t="s">
         <v>10</v>
@@ -2604,7 +2604,7 @@
     </row>
     <row r="24" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B24" s="58" t="s">
         <v>10</v>
@@ -2621,7 +2621,7 @@
     </row>
     <row r="25" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B25" s="62" t="s">
         <v>10</v>
@@ -2638,7 +2638,7 @@
     </row>
     <row r="26" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B26" s="58" t="s">
         <v>10</v>
@@ -2655,7 +2655,7 @@
     </row>
     <row r="27" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B27" s="62" t="s">
         <v>10</v>
@@ -2672,7 +2672,7 @@
     </row>
     <row r="28" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B28" s="58" t="s">
         <v>10</v>
@@ -2689,7 +2689,7 @@
     </row>
     <row r="29" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B29" s="62" t="s">
         <v>10</v>
@@ -2706,7 +2706,7 @@
     </row>
     <row r="30" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B30" s="58" t="s">
         <v>10</v>
@@ -2723,7 +2723,7 @@
     </row>
     <row r="31" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B31" s="62" t="s">
         <v>10</v>
@@ -2740,7 +2740,7 @@
     </row>
     <row r="32" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B32" s="58" t="s">
         <v>10</v>
@@ -2757,7 +2757,7 @@
     </row>
     <row r="33" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B33" s="59" t="s">
         <v>13</v>
@@ -2774,7 +2774,7 @@
     </row>
     <row r="34" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B34" s="63" t="s">
         <v>13</v>
@@ -2791,7 +2791,7 @@
     </row>
     <row r="35" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B35" s="59" t="s">
         <v>13</v>
@@ -2808,7 +2808,7 @@
     </row>
     <row r="36" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B36" s="63" t="s">
         <v>13</v>
@@ -2825,7 +2825,7 @@
     </row>
     <row r="37" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B37" s="59" t="s">
         <v>13</v>
@@ -2842,7 +2842,7 @@
     </row>
     <row r="38" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B38" s="63" t="s">
         <v>13</v>
@@ -2859,7 +2859,7 @@
     </row>
     <row r="39" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B39" s="59" t="s">
         <v>13</v>
@@ -2876,7 +2876,7 @@
     </row>
     <row r="40" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B40" s="63" t="s">
         <v>13</v>
@@ -2893,7 +2893,7 @@
     </row>
     <row r="41" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B41" s="59" t="s">
         <v>13</v>
@@ -2910,7 +2910,7 @@
     </row>
     <row r="42" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B42" s="63" t="s">
         <v>13</v>
@@ -2927,7 +2927,7 @@
     </row>
     <row r="43" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B43" s="59" t="s">
         <v>13</v>
@@ -2944,7 +2944,7 @@
     </row>
     <row r="44" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B44" s="63" t="s">
         <v>13</v>
@@ -2961,7 +2961,7 @@
     </row>
     <row r="45" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B45" s="59" t="s">
         <v>13</v>
@@ -2978,7 +2978,7 @@
     </row>
     <row r="46" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B46" s="63" t="s">
         <v>13</v>
@@ -2995,7 +2995,7 @@
     </row>
     <row r="47" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B47" s="62" t="s">
         <v>10</v>
@@ -3012,7 +3012,7 @@
     </row>
     <row r="48" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B48" s="58" t="s">
         <v>10</v>
@@ -3029,7 +3029,7 @@
     </row>
     <row r="49" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B49" s="62" t="s">
         <v>10</v>
@@ -3046,7 +3046,7 @@
     </row>
     <row r="50" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="18" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B50" s="58" t="s">
         <v>10</v>
@@ -6327,7 +6327,7 @@
         <v>34</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -6580,7 +6580,7 @@
       </c>
       <c r="E33" s="33"/>
     </row>
-    <row r="34" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="33" t="s">
         <v>49</v>
       </c>
@@ -6834,7 +6834,7 @@
     </row>
     <row r="52" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="45" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B52" s="46">
         <f>INT((B6-B51)/2)</f>
@@ -6846,7 +6846,7 @@
     </row>
     <row r="53" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="45" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B53" s="54">
         <f>(B6-B51)/B6</f>
@@ -6858,26 +6858,26 @@
     </row>
     <row r="54" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="45" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B54" s="49" cm="1">
         <f t="array" ref="B54">_xlfn.LET(_xlpm.a,'Matching Engine'!N2:N50,_xlpm.b,'Matching Engine'!L2:L50,_xlpm.c,B6,_xlpm.s,'Matching Engine'!P2:P50,_xlpm.d,_xlpm.c/2,_xlpm.e,SUMPRODUCT(IF(_xlpm.b=0,1,EXP(-(_xlpm.a+_xlpm.b*_xlpm.s*_xlpm.d/_xlpm.c)))),_xlpm.f,(_xlpm.e+_xlpm.d)/2,_xlpm.g,SUMPRODUCT(IF(_xlpm.b=0,1,EXP(-(_xlpm.a+_xlpm.b*_xlpm.s*_xlpm.f/_xlpm.c)))),_xlpm.h,(_xlpm.g+_xlpm.f)/2,_xlpm.i,SUMPRODUCT(IF(_xlpm.b=0,1,EXP(-(_xlpm.a+_xlpm.b*_xlpm.s*_xlpm.h/_xlpm.c)))),_xlpm.j,(_xlpm.i+_xlpm.h)/2,_xlpm.k,SUMPRODUCT(IF(_xlpm.b=0,1,EXP(-(_xlpm.a+_xlpm.b*_xlpm.s*_xlpm.j/_xlpm.c)))),_xlpm.l,(_xlpm.k+_xlpm.j)/2,_xlpm.m,SUMPRODUCT(IF(_xlpm.b=0,1,EXP(-(_xlpm.a+_xlpm.b*_xlpm.s*_xlpm.l/_xlpm.c)))),_xlpm.n,(_xlpm.m+_xlpm.l)/2,(_xlpm.c-_xlpm.n)/2)</f>
         <v>19.685961845282833</v>
       </c>
       <c r="C54" s="45" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="45" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B55" s="54">
         <f>B54*2/B6</f>
         <v>0.80350864674623812</v>
       </c>
       <c r="C55" s="45" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -6900,7 +6900,7 @@
         <v>74</v>
       </c>
       <c r="D58" s="27" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E58" s="27" t="s">
         <v>76</v>
@@ -7070,7 +7070,7 @@
         <v/>
       </c>
       <c r="D66" s="28" t="str">
-        <f t="shared" ref="D59:D68" si="1">IF(A66="","",0)</f>
+        <f t="shared" ref="D66:D68" si="1">IF(A66="","",0)</f>
         <v/>
       </c>
       <c r="E66" t="str">
@@ -7134,10 +7134,10 @@
         <v>74</v>
       </c>
       <c r="D71" s="27" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E71" s="27" t="s">
-        <v>88</v>
+        <v>428</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -9336,7 +9336,7 @@
         <v/>
       </c>
       <c r="E171" s="28" t="str">
-        <f t="shared" ref="E171:E202" si="5">IF(A171="","",IF(D171=0,"0% — no compatible partners",TEXT(D171/($B$6-1),"0%")&amp;" — "&amp;D171&amp;" of "&amp;($B$6-1)&amp;" compatible"))</f>
+        <f t="shared" ref="E171:E174" si="5">IF(A171="","",IF(D171=0,"0% — no compatible partners",TEXT(D171/($B$6-1),"0%")&amp;" — "&amp;D171&amp;" of "&amp;($B$6-1)&amp;" compatible"))</f>
         <v/>
       </c>
     </row>
@@ -9704,7 +9704,6 @@
       <c r="A273" s="38"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -9771,13 +9770,13 @@
         <v>87</v>
       </c>
       <c r="N1" s="51" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O1" s="51" t="s">
+        <v>95</v>
+      </c>
+      <c r="P1" s="51" t="s">
         <v>96</v>
-      </c>
-      <c r="P1" s="51" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:16" s="37" customFormat="1" x14ac:dyDescent="0.35">
@@ -21215,7 +21214,7 @@
         <v/>
       </c>
       <c r="M194" s="52" t="str">
-        <f t="shared" ref="M194:M225" si="49">IF(A194="","",RANK(L194,L$2:L$200,1)+COUNTIFS(L$2:L$200,L194,A$2:A$200,"&lt;"&amp;A194))</f>
+        <f t="shared" ref="M194:M200" si="49">IF(A194="","",RANK(L194,L$2:L$200,1)+COUNTIFS(L$2:L$200,L194,A$2:A$200,"&lt;"&amp;A194))</f>
         <v/>
       </c>
       <c r="N194" s="52"/>
@@ -21565,7 +21564,6 @@
       <c r="P200" s="52"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -21576,1475 +21574,1791 @@
   <dimension ref="A1:A340"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="16384" width="8.7265625" style="66"/>
+    <col min="1" max="16384" width="8.7265625" style="64"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="67" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="64" t="s">
+    <row r="1" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="65" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="66" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="66" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="4" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="64" t="s">
+    <row r="5" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="6" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="66" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="5" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="6" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="64" t="s">
+    <row r="7" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="66" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="7" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="64" t="s">
+    <row r="8" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="66" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="8" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="64" t="s">
+    <row r="9" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="66" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="9" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="64" t="s">
+    <row r="10" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="11" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="66" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="10" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="11" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="64" t="s">
+    <row r="12" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="13" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="66" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="12" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="64" t="s">
+    <row r="14" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="66" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="14" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="64" t="s">
+    <row r="15" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="66" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="15" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="64" t="s">
+    <row r="16" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="66" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="16" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="64" t="s">
+    <row r="17" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="66" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="17" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="64" t="s">
+    <row r="18" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="66" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="18" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="64" t="s">
+    <row r="19" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="66" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="19" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="64" t="s">
+    <row r="20" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="66" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="20" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="64" t="s">
+    <row r="21" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="66" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="21" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="64" t="s">
+    <row r="22" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="23" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="66" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="22" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="23" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="64" t="s">
+    <row r="24" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="66" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="24" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="64" t="s">
+    <row r="25" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="66" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="25" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="64" t="s">
+    <row r="26" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="66" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="26" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="64" t="s">
+    <row r="27" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="66" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="27" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="64" t="s">
+    <row r="28" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="66" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="28" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="64" t="s">
+    <row r="29" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="30" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="66" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="29" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="30" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="64" t="s">
+    <row r="31" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="66" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="31" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="64" t="s">
+    <row r="32" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="66" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="32" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="64" t="s">
+    <row r="33" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="66" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="33" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="64" t="s">
+    <row r="34" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="35" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="66" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="34" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="35" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="64" t="s">
+    <row r="36" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="66" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="36" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="64" t="s">
+    <row r="37" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="66" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="37" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="64" t="s">
+    <row r="38" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="66" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="38" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="64" t="s">
+    <row r="39" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="66" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="39" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="64" t="s">
+    <row r="40" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="41" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="66" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="40" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="41" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="64" t="s">
+    <row r="42" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="66" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="42" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="64" t="s">
+    <row r="43" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="66" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="43" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="64" t="s">
+    <row r="44" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="45" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="66" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="44" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="45" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="64" t="s">
+    <row r="46" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="66" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="46" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="64" t="s">
+    <row r="47" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="66" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="47" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="64" t="s">
+    <row r="48" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="66" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="48" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="64" t="s">
+    <row r="49" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="66" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="49" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="64" t="s">
+    <row r="50" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="66" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="50" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="64" t="s">
+    <row r="51" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="52" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="66" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="51" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="52" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="64" t="s">
+    <row r="53" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="66" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="53" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="64" t="s">
+    <row r="54" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="66" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="54" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="64" t="s">
+    <row r="55" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="66" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="55" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="64" t="s">
+    <row r="56" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="66" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="56" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="64" t="s">
+    <row r="57" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="58" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="66" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="57" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="58" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="64" t="s">
+    <row r="59" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="66" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="59" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="64" t="s">
+    <row r="60" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="61" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="66" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="66" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="60" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="61" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="64" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="64" t="s">
+    <row r="63" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="64" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="66" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="63" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="64" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="64" t="s">
+    <row r="65" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="66" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="65" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="64" t="s">
+    <row r="66" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="66" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="66" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="64" t="s">
+    <row r="67" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="66" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="67" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="64" t="s">
+    <row r="68" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="66" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="68" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="64" t="s">
+    <row r="69" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="66" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="69" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="64" t="s">
+    <row r="70" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="66" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="70" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="64" t="s">
+    <row r="71" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="66" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="71" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="64" t="s">
+    <row r="72" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="66" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="72" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="64" t="s">
+    <row r="73" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="74" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="66" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="73" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="74" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="64" t="s">
+    <row r="75" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="66" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="75" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="64" t="s">
+    <row r="76" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="66" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="76" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="64" t="s">
+    <row r="77" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="66" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="77" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="64" t="s">
+    <row r="78" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="66" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="78" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="64" t="s">
+    <row r="79" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="66" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="79" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="64" t="s">
+    <row r="80" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="81" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="66" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="80" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="81" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="64" t="s">
+    <row r="82" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="66" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="82" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="64" t="s">
+    <row r="83" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="66" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="83" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="64" t="s">
+    <row r="84" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="66" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="84" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="64" t="s">
+    <row r="85" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="66" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="85" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="64" t="s">
+    <row r="86" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="66" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="86" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="64" t="s">
+    <row r="87" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A87" s="66" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="87" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="64" t="s">
+    <row r="88" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="89" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="66" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="88" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="89" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="64" t="s">
+    <row r="90" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="66" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="90" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="64" t="s">
+    <row r="91" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="92" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A92" s="66" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="91" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="92" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="64" t="s">
+    <row r="93" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A93" s="66" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="93" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="64" t="s">
+    <row r="94" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A94" s="66" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="94" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="64" t="s">
+    <row r="95" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A95" s="66" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="95" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="64" t="s">
+    <row r="96" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="97" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A97" s="66" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="96" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="97" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="64" t="s">
+    <row r="98" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A98" s="66" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="98" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="64" t="s">
+    <row r="99" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="100" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A100" s="66" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="99" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="100" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A100" s="64" t="s">
+    <row r="101" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A101" s="66" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="101" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="64" t="s">
+    <row r="102" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A102" s="66" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="102" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A102" s="64" t="s">
+    <row r="103" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A103" s="66" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="103" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="64" t="s">
+    <row r="104" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="105" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A105" s="66" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="104" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="105" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="64" t="s">
+    <row r="106" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A106" s="66" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="106" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="64" t="s">
+    <row r="107" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A107" s="66" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="107" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A107" s="64" t="s">
+    <row r="108" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A108" s="66" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="108" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A108" s="64" t="s">
+    <row r="109" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A109" s="66" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="109" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A109" s="64" t="s">
+    <row r="110" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A110" s="66" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="110" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A110" s="64" t="s">
+    <row r="111" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A111" s="66" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="111" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A111" s="64" t="s">
+    <row r="112" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A112" s="66" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="112" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="64" t="s">
+    <row r="113" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A113" s="66" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="113" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A113" s="64" t="s">
+    <row r="114" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A114" s="66" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="114" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A114" s="64" t="s">
+    <row r="115" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="116" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A116" s="66" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="115" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="116" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A116" s="64" t="s">
+    <row r="117" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A117" s="66" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="117" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A117" s="64" t="s">
+    <row r="118" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A118" s="66" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="118" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A118" s="64" t="s">
+    <row r="119" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A119" s="66" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="119" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A119" s="64" t="s">
+    <row r="120" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A120" s="66" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="120" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A120" s="64" t="s">
+    <row r="121" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A121" s="66" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="121" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="64" t="s">
+    <row r="122" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A122" s="66" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="122" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A122" s="64" t="s">
+    <row r="123" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A123" s="66" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="123" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A123" s="64" t="s">
+    <row r="124" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A124" s="66" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="124" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A124" s="64" t="s">
+    <row r="125" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="126" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A126" s="66" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="125" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="126" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A126" s="64" t="s">
+    <row r="127" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A127" s="66" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="127" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A127" s="64" t="s">
+    <row r="128" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A128" s="66" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="128" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A128" s="64" t="s">
+    <row r="129" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A129" s="66" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="129" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A129" s="64" t="s">
+    <row r="130" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="131" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A131" s="66" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="130" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="131" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A131" s="64" t="s">
+    <row r="132" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A132" s="66" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="132" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A132" s="64" t="s">
+    <row r="133" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A133" s="66" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="133" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A133" s="64" t="s">
+    <row r="134" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A134" s="66" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="134" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A134" s="64" t="s">
+    <row r="135" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="136" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A136" s="66" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="135" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="136" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A136" s="64" t="s">
+    <row r="137" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A137" s="66" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="137" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A137" s="64" t="s">
+    <row r="138" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A138" s="66" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="138" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A138" s="64" t="s">
+    <row r="139" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="140" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A140" s="66" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="139" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="140" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A140" s="64" t="s">
+    <row r="141" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A141" s="66" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="141" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A141" s="64" t="s">
+    <row r="142" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A142" s="66" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="142" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A142" s="64" t="s">
+    <row r="143" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="144" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A144" s="66" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="143" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="144" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A144" s="64" t="s">
+    <row r="145" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A145" s="66" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="145" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A145" s="64" t="s">
+    <row r="146" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A146" s="66" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="146" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A146" s="64" t="s">
+    <row r="147" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A147" s="66" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="147" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A147" s="64" t="s">
+    <row r="148" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A148" s="66" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="148" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A148" s="64" t="s">
+    <row r="149" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A149" s="66" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="149" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A149" s="64" t="s">
+    <row r="150" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="151" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A151" s="66" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="150" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="151" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A151" s="64" t="s">
+    <row r="152" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A152" s="66" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="152" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A152" s="64" t="s">
+    <row r="153" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A153" s="66" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="153" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A153" s="64" t="s">
+    <row r="154" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A154" s="66" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="154" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A154" s="64" t="s">
+    <row r="155" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A155" s="66" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="155" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A155" s="64" t="s">
+    <row r="156" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="157" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A157" s="66" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="156" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="157" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A157" s="64" t="s">
+    <row r="158" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A158" s="66" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="158" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A158" s="64" t="s">
+    <row r="159" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A159" s="66" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="159" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A159" s="64" t="s">
+    <row r="160" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A160" s="66" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="160" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A160" s="64" t="s">
+    <row r="161" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A161" s="66" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="161" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A161" s="64" t="s">
+    <row r="162" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A162" s="66" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="162" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A162" s="64" t="s">
+    <row r="163" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A163" s="66" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="163" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A163" s="64" t="s">
+    <row r="164" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A164" s="66" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="164" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A164" s="64" t="s">
+    <row r="165" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A165" s="66" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="165" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A165" s="64" t="s">
+    <row r="166" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A166" s="66" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="166" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A166" s="64" t="s">
+    <row r="167" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="168" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A168" s="66" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="167" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="168" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A168" s="64" t="s">
+    <row r="169" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A169" s="66" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="169" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A169" s="64" t="s">
+    <row r="170" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A170" s="66" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="170" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A170" s="64" t="s">
+    <row r="171" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A171" s="66" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="171" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A171" s="64" t="s">
+    <row r="172" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A172" s="66" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="172" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A172" s="64" t="s">
+    <row r="173" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="174" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A174" s="66" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="173" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="174" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A174" s="64" t="s">
+    <row r="175" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A175" s="66" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="175" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A175" s="64" t="s">
+    <row r="176" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A176" s="66" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="176" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A176" s="64" t="s">
+    <row r="177" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A177" s="66" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="177" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A177" s="64" t="s">
+    <row r="178" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A178" s="66" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="178" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A178" s="64" t="s">
+    <row r="179" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A179" s="66" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="179" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A179" s="64" t="s">
+    <row r="180" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A180" s="66" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="180" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A180" s="64" t="s">
+    <row r="181" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="182" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A182" s="66" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="181" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="182" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A182" s="64" t="s">
+    <row r="183" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A183" s="66" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="183" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A183" s="64" t="s">
+    <row r="184" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A184" s="66" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="184" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A184" s="64" t="s">
+    <row r="185" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A185" s="66" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="185" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A185" s="64" t="s">
+    <row r="186" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A186" s="66" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="186" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A186" s="64" t="s">
+    <row r="187" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A187" s="66" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="187" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A187" s="64" t="s">
+    <row r="188" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A188" s="66" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="188" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A188" s="64" t="s">
+    <row r="189" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A189" s="66" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="189" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A189" s="64" t="s">
+    <row r="190" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="191" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A191" s="66" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="190" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="191" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A191" s="64" t="s">
+    <row r="192" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A192" s="66" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="192" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A192" s="64" t="s">
+    <row r="193" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A193" s="66" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="193" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A193" s="64" t="s">
+    <row r="194" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A194" s="66" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="194" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A194" s="64" t="s">
+    <row r="195" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A195" s="66" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="195" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A195" s="64" t="s">
+    <row r="196" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A196" s="66" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="196" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A196" s="64" t="s">
+    <row r="197" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A197" s="66" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="197" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A197" s="64" t="s">
+    <row r="198" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="199" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A199" s="66" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="198" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="199" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A199" s="64" t="s">
+    <row r="200" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A200" s="66" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="200" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A200" s="64" t="s">
+    <row r="201" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A201" s="66" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="201" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A201" s="64" t="s">
+    <row r="202" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A202" s="66" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="202" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A202" s="64" t="s">
+    <row r="203" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A203" s="66" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="203" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A203" s="64" t="s">
+    <row r="204" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A204" s="66" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="204" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A204" s="64" t="s">
+    <row r="205" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A205" s="66" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="205" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A205" s="64" t="s">
+    <row r="206" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A206" s="66" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="206" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A206" s="64" t="s">
+    <row r="207" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A207" s="66" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="207" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A207" s="64" t="s">
+    <row r="208" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A208" s="66" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="208" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A208" s="64" t="s">
+    <row r="209" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A209" s="66" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="209" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A209" s="64" t="s">
+    <row r="210" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A210" s="66" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="210" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A210" s="64" t="s">
+    <row r="211" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="212" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A212" s="66" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="211" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="212" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A212" s="64" t="s">
+    <row r="213" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A213" s="66" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="213" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A213" s="64" t="s">
+    <row r="214" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A214" s="66" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="214" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A214" s="64" t="s">
+    <row r="215" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A215" s="66" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="215" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A215" s="64" t="s">
+    <row r="216" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="217" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A217" s="66" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="216" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="217" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A217" s="64" t="s">
+    <row r="218" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A218" s="66" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="218" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A218" s="64" t="s">
+    <row r="219" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A219" s="66" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="219" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A219" s="64" t="s">
+    <row r="220" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A220" s="66" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="220" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A220" s="64" t="s">
+    <row r="221" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A221" s="66" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="221" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A221" s="64" t="s">
+    <row r="222" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A222" s="66" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="222" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A222" s="64" t="s">
+    <row r="223" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A223" s="66" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="223" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A223" s="64" t="s">
+    <row r="224" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A224" s="66" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="224" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A224" s="64" t="s">
+    <row r="225" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A225" s="66" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="225" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A225" s="64" t="s">
+    <row r="226" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A226" s="66" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="226" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A226" s="64" t="s">
+    <row r="227" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="228" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A228" s="66" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="227" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="228" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A228" s="64" t="s">
+    <row r="229" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A229" s="66" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="229" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A229" s="64" t="s">
+    <row r="230" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="231" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A231" s="66" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="230" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="231" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A231" s="64" t="s">
+    <row r="232" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A232" s="66" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="232" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A232" s="64" t="s">
+    <row r="233" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A233" s="66" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="233" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A233" s="64" t="s">
+    <row r="234" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A234" s="66" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="234" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A234" s="64" t="s">
+    <row r="235" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A235" s="66" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="235" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A235" s="64" t="s">
+    <row r="236" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A236" s="66" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="236" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A236" s="64" t="s">
+    <row r="237" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A237" s="66" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="237" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A237" s="64" t="s">
+    <row r="238" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="239" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A239" s="66" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="238" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="239" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A239" s="64" t="s">
+    <row r="240" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A240" s="66" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="240" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A240" s="64" t="s">
+    <row r="241" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A241" s="66" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="241" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A241" s="64" t="s">
+    <row r="242" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A242" s="66" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="242" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A242" s="64" t="s">
+    <row r="243" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="244" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A244" s="66" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="243" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="244" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A244" s="64" t="s">
+    <row r="245" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A245" s="66" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="245" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A245" s="64" t="s">
+    <row r="246" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A246" s="66" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="246" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A246" s="64" t="s">
+    <row r="247" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A247" s="66" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="247" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A247" s="64" t="s">
+    <row r="248" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A248" s="66" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="248" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A248" s="64" t="s">
+    <row r="249" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A249" s="66" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="249" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A249" s="64" t="s">
+    <row r="250" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A250" s="66" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="250" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A250" s="64" t="s">
+    <row r="251" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="252" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A252" s="66" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="251" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="252" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A252" s="64" t="s">
+    <row r="253" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A253" s="66" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="253" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A253" s="64" t="s">
+    <row r="254" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A254" s="66" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="254" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A254" s="64" t="s">
+    <row r="255" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A255" s="66" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="255" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A255" s="64" t="s">
+    <row r="256" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A256" s="66" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="256" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A256" s="64" t="s">
+    <row r="257" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A257" s="66" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="257" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A257" s="64" t="s">
+    <row r="258" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A258" s="66" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="258" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A258" s="64" t="s">
+    <row r="259" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="260" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A260" s="66" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="259" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="260" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A260" s="64" t="s">
+    <row r="261" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="262" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A262" s="66" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="261" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="262" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A262" s="64" t="s">
+    <row r="263" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A263" s="66" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="263" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A263" s="64" t="s">
+    <row r="264" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A264" s="66" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="264" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A264" s="64" t="s">
+    <row r="265" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A265" s="66" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="265" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A265" s="64" t="s">
+    <row r="266" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A266" s="66" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="266" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A266" s="64" t="s">
+    <row r="267" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A267" s="66" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="267" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A267" s="64" t="s">
+    <row r="268" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A268" s="66" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="268" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A268" s="64" t="s">
+    <row r="269" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A269" s="66" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="269" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A269" s="64" t="s">
+    <row r="270" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A270" s="66" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="270" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A270" s="64" t="s">
+    <row r="271" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="272" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A272" s="66" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="271" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="272" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A272" s="64" t="s">
+    <row r="273" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A273" s="66" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="273" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A273" s="64" t="s">
+    <row r="274" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A274" s="66" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="274" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A274" s="64" t="s">
+    <row r="275" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A275" s="66" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="275" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A275" s="64" t="s">
+    <row r="276" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A276" s="66" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="276" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A276" s="64" t="s">
+    <row r="277" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A277" s="66" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="277" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A277" s="64" t="s">
+    <row r="278" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A278" s="66" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="278" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A278" s="64" t="s">
+    <row r="279" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A279" s="66" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="279" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A279" s="64" t="s">
+    <row r="280" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A280" s="66" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="280" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A280" s="64" t="s">
+    <row r="281" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="282" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A282" s="66" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="281" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="282" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A282" s="64" t="s">
+    <row r="283" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="284" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A284" s="66" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="283" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="284" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A284" s="64" t="s">
+    <row r="285" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="286" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A286" s="66" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="285" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="286" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A286" s="64" t="s">
+    <row r="287" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A287" s="66" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="287" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A287" s="64" t="s">
+    <row r="288" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A288" s="66" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="288" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A288" s="64" t="s">
+    <row r="289" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="290" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A290" s="66" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="289" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="290" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A290" s="64" t="s">
+    <row r="291" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A291" s="66" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="291" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A291" s="64" t="s">
+    <row r="292" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A292" s="66" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="292" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A292" s="64" t="s">
+    <row r="293" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A293" s="66" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="293" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A293" s="64" t="s">
+    <row r="294" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="295" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A295" s="66" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="294" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="295" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A295" s="64" t="s">
+    <row r="296" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A296" s="66" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="296" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A296" s="64" t="s">
+    <row r="297" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="298" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A298" s="66" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="297" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="298" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A298" s="64" t="s">
+    <row r="299" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A299" s="66" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="299" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A299" s="64" t="s">
+    <row r="300" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A300" s="66" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="300" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A300" s="64" t="s">
+    <row r="301" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A301" s="66" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="301" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A301" s="64" t="s">
+    <row r="302" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="303" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A303" s="66" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="302" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="303" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A303" s="64" t="s">
+    <row r="304" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A304" s="66" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="304" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A304" s="64" t="s">
+    <row r="305" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A305" s="66" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="305" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A305" s="64" t="s">
+    <row r="306" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A306" s="66" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="306" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A306" s="64" t="s">
+    <row r="307" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="308" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A308" s="66" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="307" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="308" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A308" s="64" t="s">
+    <row r="309" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A309" s="66" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="309" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A309" s="64" t="s">
+    <row r="310" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="311" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A311" s="66" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="310" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="311" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A311" s="64" t="s">
+    <row r="312" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="313" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A313" s="66" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="312" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="313" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A313" s="64" t="s">
+    <row r="314" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A314" s="66" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="314" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A314" s="64" t="s">
+    <row r="315" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="316" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A316" s="66" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="315" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="316" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A316" s="64" t="s">
+    <row r="317" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A317" s="66" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="317" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A317" s="64" t="s">
+    <row r="318" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A318" s="66" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="318" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A318" s="64" t="s">
+    <row r="319" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A319" s="66" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="319" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A319" s="64" t="s">
+    <row r="320" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="321" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A321" s="66" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="320" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="321" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A321" s="64" t="s">
+    <row r="322" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A322" s="66" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="322" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A322" s="64" t="s">
+    <row r="323" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A323" s="66" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="323" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A323" s="64" t="s">
+    <row r="324" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A324" s="66" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="324" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A324" s="64" t="s">
+    <row r="325" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="326" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A326" s="66" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="325" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="326" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A326" s="64" t="s">
+    <row r="327" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A327" s="66" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="327" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A327" s="64" t="s">
+    <row r="328" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A328" s="66" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="328" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A328" s="64" t="s">
+    <row r="329" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="330" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A330" s="66" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="329" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="330" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A330" s="64" t="s">
+    <row r="331" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A331" s="66" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="331" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A331" s="64" t="s">
+    <row r="332" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="333" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A333" s="66" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="332" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="333" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A333" s="64" t="s">
+    <row r="334" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A334" s="66" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="334" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A334" s="64" t="s">
+    <row r="335" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="336" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A336" s="66" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="335" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="336" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A336" s="64" t="s">
+    <row r="337" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A337" s="66" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="337" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A337" s="64" t="s">
+    <row r="338" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A338" s="66" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="338" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A338" s="64" t="s">
+    <row r="339" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A339" s="66" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="339" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A339" s="64" t="s">
+    <row r="340" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A340" s="66" t="s">
         <v>425</v>
-      </c>
-    </row>
-    <row r="340" spans="1:1" s="64" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A340" s="64" t="s">
-        <v>426</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="340">
+    <mergeCell ref="A12:XFD12"/>
+    <mergeCell ref="A13:XFD13"/>
+    <mergeCell ref="A14:XFD14"/>
+    <mergeCell ref="A15:XFD15"/>
+    <mergeCell ref="A16:XFD16"/>
+    <mergeCell ref="A17:XFD17"/>
+    <mergeCell ref="A3:XFD3"/>
+    <mergeCell ref="A4:XFD4"/>
+    <mergeCell ref="A5:XFD5"/>
+    <mergeCell ref="A6:XFD6"/>
+    <mergeCell ref="A7:XFD7"/>
+    <mergeCell ref="A8:XFD8"/>
+    <mergeCell ref="A9:XFD9"/>
+    <mergeCell ref="A10:XFD10"/>
+    <mergeCell ref="A11:XFD11"/>
+    <mergeCell ref="A24:XFD24"/>
+    <mergeCell ref="A25:XFD25"/>
+    <mergeCell ref="A26:XFD26"/>
+    <mergeCell ref="A27:XFD27"/>
+    <mergeCell ref="A28:XFD28"/>
+    <mergeCell ref="A29:XFD29"/>
+    <mergeCell ref="A18:XFD18"/>
+    <mergeCell ref="A19:XFD19"/>
+    <mergeCell ref="A20:XFD20"/>
+    <mergeCell ref="A21:XFD21"/>
+    <mergeCell ref="A22:XFD22"/>
+    <mergeCell ref="A23:XFD23"/>
+    <mergeCell ref="A36:XFD36"/>
+    <mergeCell ref="A37:XFD37"/>
+    <mergeCell ref="A38:XFD38"/>
+    <mergeCell ref="A39:XFD39"/>
+    <mergeCell ref="A40:XFD40"/>
+    <mergeCell ref="A41:XFD41"/>
+    <mergeCell ref="A30:XFD30"/>
+    <mergeCell ref="A31:XFD31"/>
+    <mergeCell ref="A32:XFD32"/>
+    <mergeCell ref="A33:XFD33"/>
+    <mergeCell ref="A34:XFD34"/>
+    <mergeCell ref="A35:XFD35"/>
+    <mergeCell ref="A48:XFD48"/>
+    <mergeCell ref="A49:XFD49"/>
+    <mergeCell ref="A50:XFD50"/>
+    <mergeCell ref="A51:XFD51"/>
+    <mergeCell ref="A52:XFD52"/>
+    <mergeCell ref="A53:XFD53"/>
+    <mergeCell ref="A42:XFD42"/>
+    <mergeCell ref="A43:XFD43"/>
+    <mergeCell ref="A44:XFD44"/>
+    <mergeCell ref="A45:XFD45"/>
+    <mergeCell ref="A46:XFD46"/>
+    <mergeCell ref="A47:XFD47"/>
+    <mergeCell ref="A60:XFD60"/>
+    <mergeCell ref="A61:XFD61"/>
+    <mergeCell ref="A62:XFD62"/>
+    <mergeCell ref="A63:XFD63"/>
+    <mergeCell ref="A64:XFD64"/>
+    <mergeCell ref="A65:XFD65"/>
+    <mergeCell ref="A54:XFD54"/>
+    <mergeCell ref="A55:XFD55"/>
+    <mergeCell ref="A56:XFD56"/>
+    <mergeCell ref="A57:XFD57"/>
+    <mergeCell ref="A58:XFD58"/>
+    <mergeCell ref="A59:XFD59"/>
+    <mergeCell ref="A72:XFD72"/>
+    <mergeCell ref="A73:XFD73"/>
+    <mergeCell ref="A74:XFD74"/>
+    <mergeCell ref="A75:XFD75"/>
+    <mergeCell ref="A76:XFD76"/>
+    <mergeCell ref="A77:XFD77"/>
+    <mergeCell ref="A66:XFD66"/>
+    <mergeCell ref="A67:XFD67"/>
+    <mergeCell ref="A68:XFD68"/>
+    <mergeCell ref="A69:XFD69"/>
+    <mergeCell ref="A70:XFD70"/>
+    <mergeCell ref="A71:XFD71"/>
+    <mergeCell ref="A84:XFD84"/>
+    <mergeCell ref="A85:XFD85"/>
+    <mergeCell ref="A86:XFD86"/>
+    <mergeCell ref="A87:XFD87"/>
+    <mergeCell ref="A88:XFD88"/>
+    <mergeCell ref="A89:XFD89"/>
+    <mergeCell ref="A78:XFD78"/>
+    <mergeCell ref="A79:XFD79"/>
+    <mergeCell ref="A80:XFD80"/>
+    <mergeCell ref="A81:XFD81"/>
+    <mergeCell ref="A82:XFD82"/>
+    <mergeCell ref="A83:XFD83"/>
+    <mergeCell ref="A96:XFD96"/>
+    <mergeCell ref="A97:XFD97"/>
+    <mergeCell ref="A98:XFD98"/>
+    <mergeCell ref="A99:XFD99"/>
+    <mergeCell ref="A100:XFD100"/>
+    <mergeCell ref="A101:XFD101"/>
+    <mergeCell ref="A90:XFD90"/>
+    <mergeCell ref="A91:XFD91"/>
+    <mergeCell ref="A92:XFD92"/>
+    <mergeCell ref="A93:XFD93"/>
+    <mergeCell ref="A94:XFD94"/>
+    <mergeCell ref="A95:XFD95"/>
+    <mergeCell ref="A108:XFD108"/>
+    <mergeCell ref="A109:XFD109"/>
+    <mergeCell ref="A110:XFD110"/>
+    <mergeCell ref="A111:XFD111"/>
+    <mergeCell ref="A112:XFD112"/>
+    <mergeCell ref="A113:XFD113"/>
+    <mergeCell ref="A102:XFD102"/>
+    <mergeCell ref="A103:XFD103"/>
+    <mergeCell ref="A104:XFD104"/>
+    <mergeCell ref="A105:XFD105"/>
+    <mergeCell ref="A106:XFD106"/>
+    <mergeCell ref="A107:XFD107"/>
+    <mergeCell ref="A120:XFD120"/>
+    <mergeCell ref="A121:XFD121"/>
+    <mergeCell ref="A122:XFD122"/>
+    <mergeCell ref="A123:XFD123"/>
+    <mergeCell ref="A124:XFD124"/>
+    <mergeCell ref="A125:XFD125"/>
+    <mergeCell ref="A114:XFD114"/>
+    <mergeCell ref="A115:XFD115"/>
+    <mergeCell ref="A116:XFD116"/>
+    <mergeCell ref="A117:XFD117"/>
+    <mergeCell ref="A118:XFD118"/>
+    <mergeCell ref="A119:XFD119"/>
+    <mergeCell ref="A132:XFD132"/>
+    <mergeCell ref="A133:XFD133"/>
+    <mergeCell ref="A134:XFD134"/>
+    <mergeCell ref="A135:XFD135"/>
+    <mergeCell ref="A136:XFD136"/>
+    <mergeCell ref="A137:XFD137"/>
+    <mergeCell ref="A126:XFD126"/>
+    <mergeCell ref="A127:XFD127"/>
+    <mergeCell ref="A128:XFD128"/>
+    <mergeCell ref="A129:XFD129"/>
+    <mergeCell ref="A130:XFD130"/>
+    <mergeCell ref="A131:XFD131"/>
+    <mergeCell ref="A144:XFD144"/>
+    <mergeCell ref="A145:XFD145"/>
+    <mergeCell ref="A146:XFD146"/>
+    <mergeCell ref="A147:XFD147"/>
+    <mergeCell ref="A148:XFD148"/>
+    <mergeCell ref="A149:XFD149"/>
+    <mergeCell ref="A138:XFD138"/>
+    <mergeCell ref="A139:XFD139"/>
+    <mergeCell ref="A140:XFD140"/>
+    <mergeCell ref="A141:XFD141"/>
+    <mergeCell ref="A142:XFD142"/>
+    <mergeCell ref="A143:XFD143"/>
+    <mergeCell ref="A156:XFD156"/>
+    <mergeCell ref="A157:XFD157"/>
+    <mergeCell ref="A158:XFD158"/>
+    <mergeCell ref="A159:XFD159"/>
+    <mergeCell ref="A160:XFD160"/>
+    <mergeCell ref="A161:XFD161"/>
+    <mergeCell ref="A150:XFD150"/>
+    <mergeCell ref="A151:XFD151"/>
+    <mergeCell ref="A152:XFD152"/>
+    <mergeCell ref="A153:XFD153"/>
+    <mergeCell ref="A154:XFD154"/>
+    <mergeCell ref="A155:XFD155"/>
+    <mergeCell ref="A168:XFD168"/>
+    <mergeCell ref="A169:XFD169"/>
+    <mergeCell ref="A170:XFD170"/>
+    <mergeCell ref="A171:XFD171"/>
+    <mergeCell ref="A172:XFD172"/>
+    <mergeCell ref="A173:XFD173"/>
+    <mergeCell ref="A162:XFD162"/>
+    <mergeCell ref="A163:XFD163"/>
+    <mergeCell ref="A164:XFD164"/>
+    <mergeCell ref="A165:XFD165"/>
+    <mergeCell ref="A166:XFD166"/>
+    <mergeCell ref="A167:XFD167"/>
+    <mergeCell ref="A180:XFD180"/>
+    <mergeCell ref="A181:XFD181"/>
+    <mergeCell ref="A182:XFD182"/>
+    <mergeCell ref="A183:XFD183"/>
+    <mergeCell ref="A184:XFD184"/>
+    <mergeCell ref="A185:XFD185"/>
+    <mergeCell ref="A174:XFD174"/>
+    <mergeCell ref="A175:XFD175"/>
+    <mergeCell ref="A176:XFD176"/>
+    <mergeCell ref="A177:XFD177"/>
+    <mergeCell ref="A178:XFD178"/>
+    <mergeCell ref="A179:XFD179"/>
+    <mergeCell ref="A192:XFD192"/>
+    <mergeCell ref="A193:XFD193"/>
+    <mergeCell ref="A194:XFD194"/>
+    <mergeCell ref="A195:XFD195"/>
+    <mergeCell ref="A196:XFD196"/>
+    <mergeCell ref="A197:XFD197"/>
+    <mergeCell ref="A186:XFD186"/>
+    <mergeCell ref="A187:XFD187"/>
+    <mergeCell ref="A188:XFD188"/>
+    <mergeCell ref="A189:XFD189"/>
+    <mergeCell ref="A190:XFD190"/>
+    <mergeCell ref="A191:XFD191"/>
+    <mergeCell ref="A204:XFD204"/>
+    <mergeCell ref="A205:XFD205"/>
+    <mergeCell ref="A206:XFD206"/>
+    <mergeCell ref="A207:XFD207"/>
+    <mergeCell ref="A208:XFD208"/>
+    <mergeCell ref="A209:XFD209"/>
+    <mergeCell ref="A198:XFD198"/>
+    <mergeCell ref="A199:XFD199"/>
+    <mergeCell ref="A200:XFD200"/>
+    <mergeCell ref="A201:XFD201"/>
+    <mergeCell ref="A202:XFD202"/>
+    <mergeCell ref="A203:XFD203"/>
+    <mergeCell ref="A216:XFD216"/>
+    <mergeCell ref="A217:XFD217"/>
+    <mergeCell ref="A218:XFD218"/>
+    <mergeCell ref="A219:XFD219"/>
+    <mergeCell ref="A220:XFD220"/>
+    <mergeCell ref="A221:XFD221"/>
+    <mergeCell ref="A210:XFD210"/>
+    <mergeCell ref="A211:XFD211"/>
+    <mergeCell ref="A212:XFD212"/>
+    <mergeCell ref="A213:XFD213"/>
+    <mergeCell ref="A214:XFD214"/>
+    <mergeCell ref="A215:XFD215"/>
+    <mergeCell ref="A228:XFD228"/>
+    <mergeCell ref="A229:XFD229"/>
+    <mergeCell ref="A230:XFD230"/>
+    <mergeCell ref="A231:XFD231"/>
+    <mergeCell ref="A232:XFD232"/>
+    <mergeCell ref="A233:XFD233"/>
+    <mergeCell ref="A222:XFD222"/>
+    <mergeCell ref="A223:XFD223"/>
+    <mergeCell ref="A224:XFD224"/>
+    <mergeCell ref="A225:XFD225"/>
+    <mergeCell ref="A226:XFD226"/>
+    <mergeCell ref="A227:XFD227"/>
+    <mergeCell ref="A240:XFD240"/>
+    <mergeCell ref="A241:XFD241"/>
+    <mergeCell ref="A242:XFD242"/>
+    <mergeCell ref="A243:XFD243"/>
+    <mergeCell ref="A244:XFD244"/>
+    <mergeCell ref="A245:XFD245"/>
+    <mergeCell ref="A234:XFD234"/>
+    <mergeCell ref="A235:XFD235"/>
+    <mergeCell ref="A236:XFD236"/>
+    <mergeCell ref="A237:XFD237"/>
+    <mergeCell ref="A238:XFD238"/>
+    <mergeCell ref="A239:XFD239"/>
+    <mergeCell ref="A252:XFD252"/>
+    <mergeCell ref="A253:XFD253"/>
+    <mergeCell ref="A254:XFD254"/>
+    <mergeCell ref="A255:XFD255"/>
+    <mergeCell ref="A256:XFD256"/>
+    <mergeCell ref="A257:XFD257"/>
+    <mergeCell ref="A246:XFD246"/>
+    <mergeCell ref="A247:XFD247"/>
+    <mergeCell ref="A248:XFD248"/>
+    <mergeCell ref="A249:XFD249"/>
+    <mergeCell ref="A250:XFD250"/>
+    <mergeCell ref="A251:XFD251"/>
+    <mergeCell ref="A264:XFD264"/>
+    <mergeCell ref="A265:XFD265"/>
+    <mergeCell ref="A266:XFD266"/>
+    <mergeCell ref="A267:XFD267"/>
+    <mergeCell ref="A268:XFD268"/>
+    <mergeCell ref="A269:XFD269"/>
+    <mergeCell ref="A258:XFD258"/>
+    <mergeCell ref="A259:XFD259"/>
+    <mergeCell ref="A260:XFD260"/>
+    <mergeCell ref="A261:XFD261"/>
+    <mergeCell ref="A262:XFD262"/>
+    <mergeCell ref="A263:XFD263"/>
+    <mergeCell ref="A276:XFD276"/>
+    <mergeCell ref="A277:XFD277"/>
+    <mergeCell ref="A278:XFD278"/>
+    <mergeCell ref="A279:XFD279"/>
+    <mergeCell ref="A280:XFD280"/>
+    <mergeCell ref="A281:XFD281"/>
+    <mergeCell ref="A270:XFD270"/>
+    <mergeCell ref="A271:XFD271"/>
+    <mergeCell ref="A272:XFD272"/>
+    <mergeCell ref="A273:XFD273"/>
+    <mergeCell ref="A274:XFD274"/>
+    <mergeCell ref="A275:XFD275"/>
+    <mergeCell ref="A288:XFD288"/>
+    <mergeCell ref="A289:XFD289"/>
+    <mergeCell ref="A290:XFD290"/>
+    <mergeCell ref="A291:XFD291"/>
+    <mergeCell ref="A292:XFD292"/>
+    <mergeCell ref="A293:XFD293"/>
+    <mergeCell ref="A282:XFD282"/>
+    <mergeCell ref="A283:XFD283"/>
+    <mergeCell ref="A284:XFD284"/>
+    <mergeCell ref="A285:XFD285"/>
+    <mergeCell ref="A286:XFD286"/>
+    <mergeCell ref="A287:XFD287"/>
+    <mergeCell ref="A300:XFD300"/>
+    <mergeCell ref="A301:XFD301"/>
+    <mergeCell ref="A302:XFD302"/>
+    <mergeCell ref="A303:XFD303"/>
+    <mergeCell ref="A304:XFD304"/>
+    <mergeCell ref="A305:XFD305"/>
+    <mergeCell ref="A294:XFD294"/>
+    <mergeCell ref="A295:XFD295"/>
+    <mergeCell ref="A296:XFD296"/>
+    <mergeCell ref="A297:XFD297"/>
+    <mergeCell ref="A298:XFD298"/>
+    <mergeCell ref="A299:XFD299"/>
+    <mergeCell ref="A323:XFD323"/>
+    <mergeCell ref="A312:XFD312"/>
+    <mergeCell ref="A313:XFD313"/>
+    <mergeCell ref="A314:XFD314"/>
+    <mergeCell ref="A315:XFD315"/>
+    <mergeCell ref="A316:XFD316"/>
+    <mergeCell ref="A317:XFD317"/>
+    <mergeCell ref="A306:XFD306"/>
+    <mergeCell ref="A307:XFD307"/>
+    <mergeCell ref="A308:XFD308"/>
+    <mergeCell ref="A309:XFD309"/>
+    <mergeCell ref="A310:XFD310"/>
+    <mergeCell ref="A311:XFD311"/>
     <mergeCell ref="A1:XFD1"/>
     <mergeCell ref="A336:XFD336"/>
     <mergeCell ref="A337:XFD337"/>
@@ -23069,322 +23383,6 @@
     <mergeCell ref="A320:XFD320"/>
     <mergeCell ref="A321:XFD321"/>
     <mergeCell ref="A322:XFD322"/>
-    <mergeCell ref="A323:XFD323"/>
-    <mergeCell ref="A312:XFD312"/>
-    <mergeCell ref="A313:XFD313"/>
-    <mergeCell ref="A314:XFD314"/>
-    <mergeCell ref="A315:XFD315"/>
-    <mergeCell ref="A316:XFD316"/>
-    <mergeCell ref="A317:XFD317"/>
-    <mergeCell ref="A306:XFD306"/>
-    <mergeCell ref="A307:XFD307"/>
-    <mergeCell ref="A308:XFD308"/>
-    <mergeCell ref="A309:XFD309"/>
-    <mergeCell ref="A310:XFD310"/>
-    <mergeCell ref="A311:XFD311"/>
-    <mergeCell ref="A300:XFD300"/>
-    <mergeCell ref="A301:XFD301"/>
-    <mergeCell ref="A302:XFD302"/>
-    <mergeCell ref="A303:XFD303"/>
-    <mergeCell ref="A304:XFD304"/>
-    <mergeCell ref="A305:XFD305"/>
-    <mergeCell ref="A294:XFD294"/>
-    <mergeCell ref="A295:XFD295"/>
-    <mergeCell ref="A296:XFD296"/>
-    <mergeCell ref="A297:XFD297"/>
-    <mergeCell ref="A298:XFD298"/>
-    <mergeCell ref="A299:XFD299"/>
-    <mergeCell ref="A288:XFD288"/>
-    <mergeCell ref="A289:XFD289"/>
-    <mergeCell ref="A290:XFD290"/>
-    <mergeCell ref="A291:XFD291"/>
-    <mergeCell ref="A292:XFD292"/>
-    <mergeCell ref="A293:XFD293"/>
-    <mergeCell ref="A282:XFD282"/>
-    <mergeCell ref="A283:XFD283"/>
-    <mergeCell ref="A284:XFD284"/>
-    <mergeCell ref="A285:XFD285"/>
-    <mergeCell ref="A286:XFD286"/>
-    <mergeCell ref="A287:XFD287"/>
-    <mergeCell ref="A276:XFD276"/>
-    <mergeCell ref="A277:XFD277"/>
-    <mergeCell ref="A278:XFD278"/>
-    <mergeCell ref="A279:XFD279"/>
-    <mergeCell ref="A280:XFD280"/>
-    <mergeCell ref="A281:XFD281"/>
-    <mergeCell ref="A270:XFD270"/>
-    <mergeCell ref="A271:XFD271"/>
-    <mergeCell ref="A272:XFD272"/>
-    <mergeCell ref="A273:XFD273"/>
-    <mergeCell ref="A274:XFD274"/>
-    <mergeCell ref="A275:XFD275"/>
-    <mergeCell ref="A264:XFD264"/>
-    <mergeCell ref="A265:XFD265"/>
-    <mergeCell ref="A266:XFD266"/>
-    <mergeCell ref="A267:XFD267"/>
-    <mergeCell ref="A268:XFD268"/>
-    <mergeCell ref="A269:XFD269"/>
-    <mergeCell ref="A258:XFD258"/>
-    <mergeCell ref="A259:XFD259"/>
-    <mergeCell ref="A260:XFD260"/>
-    <mergeCell ref="A261:XFD261"/>
-    <mergeCell ref="A262:XFD262"/>
-    <mergeCell ref="A263:XFD263"/>
-    <mergeCell ref="A252:XFD252"/>
-    <mergeCell ref="A253:XFD253"/>
-    <mergeCell ref="A254:XFD254"/>
-    <mergeCell ref="A255:XFD255"/>
-    <mergeCell ref="A256:XFD256"/>
-    <mergeCell ref="A257:XFD257"/>
-    <mergeCell ref="A246:XFD246"/>
-    <mergeCell ref="A247:XFD247"/>
-    <mergeCell ref="A248:XFD248"/>
-    <mergeCell ref="A249:XFD249"/>
-    <mergeCell ref="A250:XFD250"/>
-    <mergeCell ref="A251:XFD251"/>
-    <mergeCell ref="A240:XFD240"/>
-    <mergeCell ref="A241:XFD241"/>
-    <mergeCell ref="A242:XFD242"/>
-    <mergeCell ref="A243:XFD243"/>
-    <mergeCell ref="A244:XFD244"/>
-    <mergeCell ref="A245:XFD245"/>
-    <mergeCell ref="A234:XFD234"/>
-    <mergeCell ref="A235:XFD235"/>
-    <mergeCell ref="A236:XFD236"/>
-    <mergeCell ref="A237:XFD237"/>
-    <mergeCell ref="A238:XFD238"/>
-    <mergeCell ref="A239:XFD239"/>
-    <mergeCell ref="A228:XFD228"/>
-    <mergeCell ref="A229:XFD229"/>
-    <mergeCell ref="A230:XFD230"/>
-    <mergeCell ref="A231:XFD231"/>
-    <mergeCell ref="A232:XFD232"/>
-    <mergeCell ref="A233:XFD233"/>
-    <mergeCell ref="A222:XFD222"/>
-    <mergeCell ref="A223:XFD223"/>
-    <mergeCell ref="A224:XFD224"/>
-    <mergeCell ref="A225:XFD225"/>
-    <mergeCell ref="A226:XFD226"/>
-    <mergeCell ref="A227:XFD227"/>
-    <mergeCell ref="A216:XFD216"/>
-    <mergeCell ref="A217:XFD217"/>
-    <mergeCell ref="A218:XFD218"/>
-    <mergeCell ref="A219:XFD219"/>
-    <mergeCell ref="A220:XFD220"/>
-    <mergeCell ref="A221:XFD221"/>
-    <mergeCell ref="A210:XFD210"/>
-    <mergeCell ref="A211:XFD211"/>
-    <mergeCell ref="A212:XFD212"/>
-    <mergeCell ref="A213:XFD213"/>
-    <mergeCell ref="A214:XFD214"/>
-    <mergeCell ref="A215:XFD215"/>
-    <mergeCell ref="A204:XFD204"/>
-    <mergeCell ref="A205:XFD205"/>
-    <mergeCell ref="A206:XFD206"/>
-    <mergeCell ref="A207:XFD207"/>
-    <mergeCell ref="A208:XFD208"/>
-    <mergeCell ref="A209:XFD209"/>
-    <mergeCell ref="A198:XFD198"/>
-    <mergeCell ref="A199:XFD199"/>
-    <mergeCell ref="A200:XFD200"/>
-    <mergeCell ref="A201:XFD201"/>
-    <mergeCell ref="A202:XFD202"/>
-    <mergeCell ref="A203:XFD203"/>
-    <mergeCell ref="A192:XFD192"/>
-    <mergeCell ref="A193:XFD193"/>
-    <mergeCell ref="A194:XFD194"/>
-    <mergeCell ref="A195:XFD195"/>
-    <mergeCell ref="A196:XFD196"/>
-    <mergeCell ref="A197:XFD197"/>
-    <mergeCell ref="A186:XFD186"/>
-    <mergeCell ref="A187:XFD187"/>
-    <mergeCell ref="A188:XFD188"/>
-    <mergeCell ref="A189:XFD189"/>
-    <mergeCell ref="A190:XFD190"/>
-    <mergeCell ref="A191:XFD191"/>
-    <mergeCell ref="A180:XFD180"/>
-    <mergeCell ref="A181:XFD181"/>
-    <mergeCell ref="A182:XFD182"/>
-    <mergeCell ref="A183:XFD183"/>
-    <mergeCell ref="A184:XFD184"/>
-    <mergeCell ref="A185:XFD185"/>
-    <mergeCell ref="A174:XFD174"/>
-    <mergeCell ref="A175:XFD175"/>
-    <mergeCell ref="A176:XFD176"/>
-    <mergeCell ref="A177:XFD177"/>
-    <mergeCell ref="A178:XFD178"/>
-    <mergeCell ref="A179:XFD179"/>
-    <mergeCell ref="A168:XFD168"/>
-    <mergeCell ref="A169:XFD169"/>
-    <mergeCell ref="A170:XFD170"/>
-    <mergeCell ref="A171:XFD171"/>
-    <mergeCell ref="A172:XFD172"/>
-    <mergeCell ref="A173:XFD173"/>
-    <mergeCell ref="A162:XFD162"/>
-    <mergeCell ref="A163:XFD163"/>
-    <mergeCell ref="A164:XFD164"/>
-    <mergeCell ref="A165:XFD165"/>
-    <mergeCell ref="A166:XFD166"/>
-    <mergeCell ref="A167:XFD167"/>
-    <mergeCell ref="A156:XFD156"/>
-    <mergeCell ref="A157:XFD157"/>
-    <mergeCell ref="A158:XFD158"/>
-    <mergeCell ref="A159:XFD159"/>
-    <mergeCell ref="A160:XFD160"/>
-    <mergeCell ref="A161:XFD161"/>
-    <mergeCell ref="A150:XFD150"/>
-    <mergeCell ref="A151:XFD151"/>
-    <mergeCell ref="A152:XFD152"/>
-    <mergeCell ref="A153:XFD153"/>
-    <mergeCell ref="A154:XFD154"/>
-    <mergeCell ref="A155:XFD155"/>
-    <mergeCell ref="A144:XFD144"/>
-    <mergeCell ref="A145:XFD145"/>
-    <mergeCell ref="A146:XFD146"/>
-    <mergeCell ref="A147:XFD147"/>
-    <mergeCell ref="A148:XFD148"/>
-    <mergeCell ref="A149:XFD149"/>
-    <mergeCell ref="A138:XFD138"/>
-    <mergeCell ref="A139:XFD139"/>
-    <mergeCell ref="A140:XFD140"/>
-    <mergeCell ref="A141:XFD141"/>
-    <mergeCell ref="A142:XFD142"/>
-    <mergeCell ref="A143:XFD143"/>
-    <mergeCell ref="A132:XFD132"/>
-    <mergeCell ref="A133:XFD133"/>
-    <mergeCell ref="A134:XFD134"/>
-    <mergeCell ref="A135:XFD135"/>
-    <mergeCell ref="A136:XFD136"/>
-    <mergeCell ref="A137:XFD137"/>
-    <mergeCell ref="A126:XFD126"/>
-    <mergeCell ref="A127:XFD127"/>
-    <mergeCell ref="A128:XFD128"/>
-    <mergeCell ref="A129:XFD129"/>
-    <mergeCell ref="A130:XFD130"/>
-    <mergeCell ref="A131:XFD131"/>
-    <mergeCell ref="A120:XFD120"/>
-    <mergeCell ref="A121:XFD121"/>
-    <mergeCell ref="A122:XFD122"/>
-    <mergeCell ref="A123:XFD123"/>
-    <mergeCell ref="A124:XFD124"/>
-    <mergeCell ref="A125:XFD125"/>
-    <mergeCell ref="A114:XFD114"/>
-    <mergeCell ref="A115:XFD115"/>
-    <mergeCell ref="A116:XFD116"/>
-    <mergeCell ref="A117:XFD117"/>
-    <mergeCell ref="A118:XFD118"/>
-    <mergeCell ref="A119:XFD119"/>
-    <mergeCell ref="A108:XFD108"/>
-    <mergeCell ref="A109:XFD109"/>
-    <mergeCell ref="A110:XFD110"/>
-    <mergeCell ref="A111:XFD111"/>
-    <mergeCell ref="A112:XFD112"/>
-    <mergeCell ref="A113:XFD113"/>
-    <mergeCell ref="A102:XFD102"/>
-    <mergeCell ref="A103:XFD103"/>
-    <mergeCell ref="A104:XFD104"/>
-    <mergeCell ref="A105:XFD105"/>
-    <mergeCell ref="A106:XFD106"/>
-    <mergeCell ref="A107:XFD107"/>
-    <mergeCell ref="A96:XFD96"/>
-    <mergeCell ref="A97:XFD97"/>
-    <mergeCell ref="A98:XFD98"/>
-    <mergeCell ref="A99:XFD99"/>
-    <mergeCell ref="A100:XFD100"/>
-    <mergeCell ref="A101:XFD101"/>
-    <mergeCell ref="A90:XFD90"/>
-    <mergeCell ref="A91:XFD91"/>
-    <mergeCell ref="A92:XFD92"/>
-    <mergeCell ref="A93:XFD93"/>
-    <mergeCell ref="A94:XFD94"/>
-    <mergeCell ref="A95:XFD95"/>
-    <mergeCell ref="A84:XFD84"/>
-    <mergeCell ref="A85:XFD85"/>
-    <mergeCell ref="A86:XFD86"/>
-    <mergeCell ref="A87:XFD87"/>
-    <mergeCell ref="A88:XFD88"/>
-    <mergeCell ref="A89:XFD89"/>
-    <mergeCell ref="A78:XFD78"/>
-    <mergeCell ref="A79:XFD79"/>
-    <mergeCell ref="A80:XFD80"/>
-    <mergeCell ref="A81:XFD81"/>
-    <mergeCell ref="A82:XFD82"/>
-    <mergeCell ref="A83:XFD83"/>
-    <mergeCell ref="A72:XFD72"/>
-    <mergeCell ref="A73:XFD73"/>
-    <mergeCell ref="A74:XFD74"/>
-    <mergeCell ref="A75:XFD75"/>
-    <mergeCell ref="A76:XFD76"/>
-    <mergeCell ref="A77:XFD77"/>
-    <mergeCell ref="A66:XFD66"/>
-    <mergeCell ref="A67:XFD67"/>
-    <mergeCell ref="A68:XFD68"/>
-    <mergeCell ref="A69:XFD69"/>
-    <mergeCell ref="A70:XFD70"/>
-    <mergeCell ref="A71:XFD71"/>
-    <mergeCell ref="A60:XFD60"/>
-    <mergeCell ref="A61:XFD61"/>
-    <mergeCell ref="A62:XFD62"/>
-    <mergeCell ref="A63:XFD63"/>
-    <mergeCell ref="A64:XFD64"/>
-    <mergeCell ref="A65:XFD65"/>
-    <mergeCell ref="A54:XFD54"/>
-    <mergeCell ref="A55:XFD55"/>
-    <mergeCell ref="A56:XFD56"/>
-    <mergeCell ref="A57:XFD57"/>
-    <mergeCell ref="A58:XFD58"/>
-    <mergeCell ref="A59:XFD59"/>
-    <mergeCell ref="A48:XFD48"/>
-    <mergeCell ref="A49:XFD49"/>
-    <mergeCell ref="A50:XFD50"/>
-    <mergeCell ref="A51:XFD51"/>
-    <mergeCell ref="A52:XFD52"/>
-    <mergeCell ref="A53:XFD53"/>
-    <mergeCell ref="A42:XFD42"/>
-    <mergeCell ref="A43:XFD43"/>
-    <mergeCell ref="A44:XFD44"/>
-    <mergeCell ref="A45:XFD45"/>
-    <mergeCell ref="A46:XFD46"/>
-    <mergeCell ref="A47:XFD47"/>
-    <mergeCell ref="A36:XFD36"/>
-    <mergeCell ref="A37:XFD37"/>
-    <mergeCell ref="A38:XFD38"/>
-    <mergeCell ref="A39:XFD39"/>
-    <mergeCell ref="A40:XFD40"/>
-    <mergeCell ref="A41:XFD41"/>
-    <mergeCell ref="A30:XFD30"/>
-    <mergeCell ref="A31:XFD31"/>
-    <mergeCell ref="A32:XFD32"/>
-    <mergeCell ref="A33:XFD33"/>
-    <mergeCell ref="A34:XFD34"/>
-    <mergeCell ref="A35:XFD35"/>
-    <mergeCell ref="A24:XFD24"/>
-    <mergeCell ref="A25:XFD25"/>
-    <mergeCell ref="A26:XFD26"/>
-    <mergeCell ref="A27:XFD27"/>
-    <mergeCell ref="A28:XFD28"/>
-    <mergeCell ref="A29:XFD29"/>
-    <mergeCell ref="A18:XFD18"/>
-    <mergeCell ref="A19:XFD19"/>
-    <mergeCell ref="A20:XFD20"/>
-    <mergeCell ref="A21:XFD21"/>
-    <mergeCell ref="A22:XFD22"/>
-    <mergeCell ref="A23:XFD23"/>
-    <mergeCell ref="A12:XFD12"/>
-    <mergeCell ref="A13:XFD13"/>
-    <mergeCell ref="A14:XFD14"/>
-    <mergeCell ref="A15:XFD15"/>
-    <mergeCell ref="A16:XFD16"/>
-    <mergeCell ref="A17:XFD17"/>
-    <mergeCell ref="A3:XFD3"/>
-    <mergeCell ref="A4:XFD4"/>
-    <mergeCell ref="A5:XFD5"/>
-    <mergeCell ref="A6:XFD6"/>
-    <mergeCell ref="A7:XFD7"/>
-    <mergeCell ref="A8:XFD8"/>
-    <mergeCell ref="A9:XFD9"/>
-    <mergeCell ref="A10:XFD10"/>
-    <mergeCell ref="A11:XFD11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Tomodachi Life Living the Dream island dating analysis.xlsx
+++ b/Tomodachi Life Living the Dream island dating analysis.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Robin\OneDrive\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Robin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{915F2B4A-D86F-42D6-82DC-5E64C225F5CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2BCDA5E-3D75-4B8F-8EE2-7110AF3D93A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18700" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18700" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mii List" sheetId="1" r:id="rId1"/>
@@ -1853,13 +1853,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Calculation" xfId="1" builtinId="22"/>
@@ -2200,13 +2200,8 @@
         <f>COUNTA(A2:A200)</f>
         <v>49</v>
       </c>
-      <c r="I2" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="8">
-        <f>COUNTIF(C2:C49,"✓")</f>
-        <v>24</v>
-      </c>
+      <c r="I2" s="7"/>
+      <c r="J2" s="8"/>
     </row>
     <row r="3" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
@@ -2232,11 +2227,11 @@
         <v>23</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J3" s="13">
-        <f>COUNTIF(D2:D49,"✓")</f>
-        <v>23</v>
+        <f>COUNTIF(C2:C49,"✓")</f>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -2263,11 +2258,11 @@
         <v>15</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J4" s="8">
-        <f>COUNTIF(E2:E49,"✓")</f>
-        <v>19</v>
+        <f>COUNTIF(D2:D49,"✓")</f>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -2293,8 +2288,13 @@
         <f>COUNTIF(B:B,"Nonbinary")</f>
         <v>11</v>
       </c>
-      <c r="I5" s="14"/>
-      <c r="J5" s="13"/>
+      <c r="I5" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="13">
+        <f>COUNTIF(E2:E49,"✓")</f>
+        <v>19</v>
+      </c>
     </row>
     <row r="6" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
@@ -21577,12 +21577,12 @@
     <col min="1" max="16384" width="8.7265625" style="64"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="65" t="s">
+    <row r="1" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="67" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="2" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="66" t="s">
         <v>147</v>
@@ -21593,7 +21593,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="5" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="6" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="66" t="s">
         <v>149</v>
@@ -21614,13 +21614,13 @@
         <v>152</v>
       </c>
     </row>
-    <row r="10" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="10" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="11" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="66" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="12" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="12" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="13" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="66" t="s">
         <v>154</v>
@@ -21666,7 +21666,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="22" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="22" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="23" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="66" t="s">
         <v>163</v>
@@ -21697,7 +21697,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="29" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="29" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="30" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="66" t="s">
         <v>169</v>
@@ -21718,7 +21718,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="34" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="34" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="35" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="66" t="s">
         <v>173</v>
@@ -21744,7 +21744,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="40" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="40" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="41" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="66" t="s">
         <v>178</v>
@@ -21760,7 +21760,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="44" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="44" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="45" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="66" t="s">
         <v>181</v>
@@ -21791,7 +21791,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="51" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="51" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="52" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="66" t="s">
         <v>187</v>
@@ -21817,7 +21817,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="57" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="57" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="58" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="66" t="s">
         <v>192</v>
@@ -21828,7 +21828,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="60" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="60" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="61" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="66" t="s">
         <v>147</v>
@@ -21839,7 +21839,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="63" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="63" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="64" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="66" t="s">
         <v>195</v>
@@ -21885,7 +21885,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="73" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="73" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="74" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="66" t="s">
         <v>204</v>
@@ -21916,7 +21916,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="80" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="80" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="81" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="66" t="s">
         <v>210</v>
@@ -21952,7 +21952,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="88" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="88" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="89" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="66" t="s">
         <v>217</v>
@@ -21963,7 +21963,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="91" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="91" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="92" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="66" t="s">
         <v>219</v>
@@ -21984,7 +21984,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="96" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="96" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="97" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="66" t="s">
         <v>223</v>
@@ -21995,7 +21995,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="99" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="99" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="100" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="66" t="s">
         <v>225</v>
@@ -22016,7 +22016,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="104" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="104" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="105" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="66" t="s">
         <v>229</v>
@@ -22067,7 +22067,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="115" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="115" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="116" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="66" t="s">
         <v>239</v>
@@ -22113,7 +22113,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="125" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="125" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="126" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="66" t="s">
         <v>248</v>
@@ -22134,7 +22134,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="130" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="130" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="131" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="66" t="s">
         <v>252</v>
@@ -22155,7 +22155,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="135" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="135" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="136" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="66" t="s">
         <v>256</v>
@@ -22171,7 +22171,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="139" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="139" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="140" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="66" t="s">
         <v>259</v>
@@ -22187,7 +22187,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="143" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="143" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="144" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="66" t="s">
         <v>262</v>
@@ -22218,7 +22218,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="150" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="150" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="151" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="66" t="s">
         <v>268</v>
@@ -22244,7 +22244,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="156" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="156" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="157" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="66" t="s">
         <v>273</v>
@@ -22295,7 +22295,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="167" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="167" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="168" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="66" t="s">
         <v>283</v>
@@ -22321,7 +22321,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="173" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="173" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="174" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="66" t="s">
         <v>288</v>
@@ -22357,7 +22357,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="181" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="181" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="182" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="66" t="s">
         <v>295</v>
@@ -22398,7 +22398,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="190" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="190" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="191" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="66" t="s">
         <v>303</v>
@@ -22434,7 +22434,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="198" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="198" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="199" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="66" t="s">
         <v>310</v>
@@ -22495,7 +22495,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="211" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="211" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="212" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" s="66" t="s">
         <v>322</v>
@@ -22516,7 +22516,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="216" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="216" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="217" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A217" s="66" t="s">
         <v>326</v>
@@ -22567,7 +22567,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="227" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="227" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="228" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" s="66" t="s">
         <v>336</v>
@@ -22578,7 +22578,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="230" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="230" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="231" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" s="66" t="s">
         <v>338</v>
@@ -22614,7 +22614,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="238" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="238" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="239" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A239" s="66" t="s">
         <v>345</v>
@@ -22635,7 +22635,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="243" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="243" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="244" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A244" s="66" t="s">
         <v>349</v>
@@ -22671,7 +22671,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="251" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="251" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="252" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A252" s="66" t="s">
         <v>356</v>
@@ -22707,13 +22707,13 @@
         <v>362</v>
       </c>
     </row>
-    <row r="259" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="259" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="260" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A260" s="66" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="261" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="261" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="262" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A262" s="66" t="s">
         <v>364</v>
@@ -22759,7 +22759,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="271" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="271" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="272" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A272" s="66" t="s">
         <v>373</v>
@@ -22805,19 +22805,19 @@
         <v>381</v>
       </c>
     </row>
-    <row r="281" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="281" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="282" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A282" s="66" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="283" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="283" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="284" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A284" s="66" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="285" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="285" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="286" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A286" s="66" t="s">
         <v>384</v>
@@ -22833,7 +22833,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="289" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="289" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="290" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A290" s="66" t="s">
         <v>387</v>
@@ -22854,7 +22854,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="294" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="294" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="295" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A295" s="66" t="s">
         <v>391</v>
@@ -22865,7 +22865,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="297" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="297" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="298" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A298" s="66" t="s">
         <v>393</v>
@@ -22886,7 +22886,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="302" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="302" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="303" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A303" s="66" t="s">
         <v>397</v>
@@ -22907,7 +22907,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="307" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="307" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="308" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A308" s="66" t="s">
         <v>401</v>
@@ -22918,13 +22918,13 @@
         <v>402</v>
       </c>
     </row>
-    <row r="310" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="310" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="311" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A311" s="66" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="312" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="312" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="313" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A313" s="66" t="s">
         <v>404</v>
@@ -22935,7 +22935,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="315" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="315" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="316" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A316" s="66" t="s">
         <v>406</v>
@@ -22956,7 +22956,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="320" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="320" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="321" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A321" s="66" t="s">
         <v>410</v>
@@ -22977,7 +22977,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="325" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="325" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="326" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A326" s="66" t="s">
         <v>414</v>
@@ -22993,7 +22993,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="329" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="329" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="330" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A330" s="66" t="s">
         <v>417</v>
@@ -23004,7 +23004,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="332" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="332" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="333" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A333" s="66" t="s">
         <v>419</v>
@@ -23015,7 +23015,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="335" spans="1:1" s="67" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="335" spans="1:1" s="65" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="336" spans="1:1" s="66" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A336" s="66" t="s">
         <v>421</v>
@@ -23043,322 +23043,6 @@
     </row>
   </sheetData>
   <mergeCells count="340">
-    <mergeCell ref="A12:XFD12"/>
-    <mergeCell ref="A13:XFD13"/>
-    <mergeCell ref="A14:XFD14"/>
-    <mergeCell ref="A15:XFD15"/>
-    <mergeCell ref="A16:XFD16"/>
-    <mergeCell ref="A17:XFD17"/>
-    <mergeCell ref="A3:XFD3"/>
-    <mergeCell ref="A4:XFD4"/>
-    <mergeCell ref="A5:XFD5"/>
-    <mergeCell ref="A6:XFD6"/>
-    <mergeCell ref="A7:XFD7"/>
-    <mergeCell ref="A8:XFD8"/>
-    <mergeCell ref="A9:XFD9"/>
-    <mergeCell ref="A10:XFD10"/>
-    <mergeCell ref="A11:XFD11"/>
-    <mergeCell ref="A24:XFD24"/>
-    <mergeCell ref="A25:XFD25"/>
-    <mergeCell ref="A26:XFD26"/>
-    <mergeCell ref="A27:XFD27"/>
-    <mergeCell ref="A28:XFD28"/>
-    <mergeCell ref="A29:XFD29"/>
-    <mergeCell ref="A18:XFD18"/>
-    <mergeCell ref="A19:XFD19"/>
-    <mergeCell ref="A20:XFD20"/>
-    <mergeCell ref="A21:XFD21"/>
-    <mergeCell ref="A22:XFD22"/>
-    <mergeCell ref="A23:XFD23"/>
-    <mergeCell ref="A36:XFD36"/>
-    <mergeCell ref="A37:XFD37"/>
-    <mergeCell ref="A38:XFD38"/>
-    <mergeCell ref="A39:XFD39"/>
-    <mergeCell ref="A40:XFD40"/>
-    <mergeCell ref="A41:XFD41"/>
-    <mergeCell ref="A30:XFD30"/>
-    <mergeCell ref="A31:XFD31"/>
-    <mergeCell ref="A32:XFD32"/>
-    <mergeCell ref="A33:XFD33"/>
-    <mergeCell ref="A34:XFD34"/>
-    <mergeCell ref="A35:XFD35"/>
-    <mergeCell ref="A48:XFD48"/>
-    <mergeCell ref="A49:XFD49"/>
-    <mergeCell ref="A50:XFD50"/>
-    <mergeCell ref="A51:XFD51"/>
-    <mergeCell ref="A52:XFD52"/>
-    <mergeCell ref="A53:XFD53"/>
-    <mergeCell ref="A42:XFD42"/>
-    <mergeCell ref="A43:XFD43"/>
-    <mergeCell ref="A44:XFD44"/>
-    <mergeCell ref="A45:XFD45"/>
-    <mergeCell ref="A46:XFD46"/>
-    <mergeCell ref="A47:XFD47"/>
-    <mergeCell ref="A60:XFD60"/>
-    <mergeCell ref="A61:XFD61"/>
-    <mergeCell ref="A62:XFD62"/>
-    <mergeCell ref="A63:XFD63"/>
-    <mergeCell ref="A64:XFD64"/>
-    <mergeCell ref="A65:XFD65"/>
-    <mergeCell ref="A54:XFD54"/>
-    <mergeCell ref="A55:XFD55"/>
-    <mergeCell ref="A56:XFD56"/>
-    <mergeCell ref="A57:XFD57"/>
-    <mergeCell ref="A58:XFD58"/>
-    <mergeCell ref="A59:XFD59"/>
-    <mergeCell ref="A72:XFD72"/>
-    <mergeCell ref="A73:XFD73"/>
-    <mergeCell ref="A74:XFD74"/>
-    <mergeCell ref="A75:XFD75"/>
-    <mergeCell ref="A76:XFD76"/>
-    <mergeCell ref="A77:XFD77"/>
-    <mergeCell ref="A66:XFD66"/>
-    <mergeCell ref="A67:XFD67"/>
-    <mergeCell ref="A68:XFD68"/>
-    <mergeCell ref="A69:XFD69"/>
-    <mergeCell ref="A70:XFD70"/>
-    <mergeCell ref="A71:XFD71"/>
-    <mergeCell ref="A84:XFD84"/>
-    <mergeCell ref="A85:XFD85"/>
-    <mergeCell ref="A86:XFD86"/>
-    <mergeCell ref="A87:XFD87"/>
-    <mergeCell ref="A88:XFD88"/>
-    <mergeCell ref="A89:XFD89"/>
-    <mergeCell ref="A78:XFD78"/>
-    <mergeCell ref="A79:XFD79"/>
-    <mergeCell ref="A80:XFD80"/>
-    <mergeCell ref="A81:XFD81"/>
-    <mergeCell ref="A82:XFD82"/>
-    <mergeCell ref="A83:XFD83"/>
-    <mergeCell ref="A96:XFD96"/>
-    <mergeCell ref="A97:XFD97"/>
-    <mergeCell ref="A98:XFD98"/>
-    <mergeCell ref="A99:XFD99"/>
-    <mergeCell ref="A100:XFD100"/>
-    <mergeCell ref="A101:XFD101"/>
-    <mergeCell ref="A90:XFD90"/>
-    <mergeCell ref="A91:XFD91"/>
-    <mergeCell ref="A92:XFD92"/>
-    <mergeCell ref="A93:XFD93"/>
-    <mergeCell ref="A94:XFD94"/>
-    <mergeCell ref="A95:XFD95"/>
-    <mergeCell ref="A108:XFD108"/>
-    <mergeCell ref="A109:XFD109"/>
-    <mergeCell ref="A110:XFD110"/>
-    <mergeCell ref="A111:XFD111"/>
-    <mergeCell ref="A112:XFD112"/>
-    <mergeCell ref="A113:XFD113"/>
-    <mergeCell ref="A102:XFD102"/>
-    <mergeCell ref="A103:XFD103"/>
-    <mergeCell ref="A104:XFD104"/>
-    <mergeCell ref="A105:XFD105"/>
-    <mergeCell ref="A106:XFD106"/>
-    <mergeCell ref="A107:XFD107"/>
-    <mergeCell ref="A120:XFD120"/>
-    <mergeCell ref="A121:XFD121"/>
-    <mergeCell ref="A122:XFD122"/>
-    <mergeCell ref="A123:XFD123"/>
-    <mergeCell ref="A124:XFD124"/>
-    <mergeCell ref="A125:XFD125"/>
-    <mergeCell ref="A114:XFD114"/>
-    <mergeCell ref="A115:XFD115"/>
-    <mergeCell ref="A116:XFD116"/>
-    <mergeCell ref="A117:XFD117"/>
-    <mergeCell ref="A118:XFD118"/>
-    <mergeCell ref="A119:XFD119"/>
-    <mergeCell ref="A132:XFD132"/>
-    <mergeCell ref="A133:XFD133"/>
-    <mergeCell ref="A134:XFD134"/>
-    <mergeCell ref="A135:XFD135"/>
-    <mergeCell ref="A136:XFD136"/>
-    <mergeCell ref="A137:XFD137"/>
-    <mergeCell ref="A126:XFD126"/>
-    <mergeCell ref="A127:XFD127"/>
-    <mergeCell ref="A128:XFD128"/>
-    <mergeCell ref="A129:XFD129"/>
-    <mergeCell ref="A130:XFD130"/>
-    <mergeCell ref="A131:XFD131"/>
-    <mergeCell ref="A144:XFD144"/>
-    <mergeCell ref="A145:XFD145"/>
-    <mergeCell ref="A146:XFD146"/>
-    <mergeCell ref="A147:XFD147"/>
-    <mergeCell ref="A148:XFD148"/>
-    <mergeCell ref="A149:XFD149"/>
-    <mergeCell ref="A138:XFD138"/>
-    <mergeCell ref="A139:XFD139"/>
-    <mergeCell ref="A140:XFD140"/>
-    <mergeCell ref="A141:XFD141"/>
-    <mergeCell ref="A142:XFD142"/>
-    <mergeCell ref="A143:XFD143"/>
-    <mergeCell ref="A156:XFD156"/>
-    <mergeCell ref="A157:XFD157"/>
-    <mergeCell ref="A158:XFD158"/>
-    <mergeCell ref="A159:XFD159"/>
-    <mergeCell ref="A160:XFD160"/>
-    <mergeCell ref="A161:XFD161"/>
-    <mergeCell ref="A150:XFD150"/>
-    <mergeCell ref="A151:XFD151"/>
-    <mergeCell ref="A152:XFD152"/>
-    <mergeCell ref="A153:XFD153"/>
-    <mergeCell ref="A154:XFD154"/>
-    <mergeCell ref="A155:XFD155"/>
-    <mergeCell ref="A168:XFD168"/>
-    <mergeCell ref="A169:XFD169"/>
-    <mergeCell ref="A170:XFD170"/>
-    <mergeCell ref="A171:XFD171"/>
-    <mergeCell ref="A172:XFD172"/>
-    <mergeCell ref="A173:XFD173"/>
-    <mergeCell ref="A162:XFD162"/>
-    <mergeCell ref="A163:XFD163"/>
-    <mergeCell ref="A164:XFD164"/>
-    <mergeCell ref="A165:XFD165"/>
-    <mergeCell ref="A166:XFD166"/>
-    <mergeCell ref="A167:XFD167"/>
-    <mergeCell ref="A180:XFD180"/>
-    <mergeCell ref="A181:XFD181"/>
-    <mergeCell ref="A182:XFD182"/>
-    <mergeCell ref="A183:XFD183"/>
-    <mergeCell ref="A184:XFD184"/>
-    <mergeCell ref="A185:XFD185"/>
-    <mergeCell ref="A174:XFD174"/>
-    <mergeCell ref="A175:XFD175"/>
-    <mergeCell ref="A176:XFD176"/>
-    <mergeCell ref="A177:XFD177"/>
-    <mergeCell ref="A178:XFD178"/>
-    <mergeCell ref="A179:XFD179"/>
-    <mergeCell ref="A192:XFD192"/>
-    <mergeCell ref="A193:XFD193"/>
-    <mergeCell ref="A194:XFD194"/>
-    <mergeCell ref="A195:XFD195"/>
-    <mergeCell ref="A196:XFD196"/>
-    <mergeCell ref="A197:XFD197"/>
-    <mergeCell ref="A186:XFD186"/>
-    <mergeCell ref="A187:XFD187"/>
-    <mergeCell ref="A188:XFD188"/>
-    <mergeCell ref="A189:XFD189"/>
-    <mergeCell ref="A190:XFD190"/>
-    <mergeCell ref="A191:XFD191"/>
-    <mergeCell ref="A204:XFD204"/>
-    <mergeCell ref="A205:XFD205"/>
-    <mergeCell ref="A206:XFD206"/>
-    <mergeCell ref="A207:XFD207"/>
-    <mergeCell ref="A208:XFD208"/>
-    <mergeCell ref="A209:XFD209"/>
-    <mergeCell ref="A198:XFD198"/>
-    <mergeCell ref="A199:XFD199"/>
-    <mergeCell ref="A200:XFD200"/>
-    <mergeCell ref="A201:XFD201"/>
-    <mergeCell ref="A202:XFD202"/>
-    <mergeCell ref="A203:XFD203"/>
-    <mergeCell ref="A216:XFD216"/>
-    <mergeCell ref="A217:XFD217"/>
-    <mergeCell ref="A218:XFD218"/>
-    <mergeCell ref="A219:XFD219"/>
-    <mergeCell ref="A220:XFD220"/>
-    <mergeCell ref="A221:XFD221"/>
-    <mergeCell ref="A210:XFD210"/>
-    <mergeCell ref="A211:XFD211"/>
-    <mergeCell ref="A212:XFD212"/>
-    <mergeCell ref="A213:XFD213"/>
-    <mergeCell ref="A214:XFD214"/>
-    <mergeCell ref="A215:XFD215"/>
-    <mergeCell ref="A228:XFD228"/>
-    <mergeCell ref="A229:XFD229"/>
-    <mergeCell ref="A230:XFD230"/>
-    <mergeCell ref="A231:XFD231"/>
-    <mergeCell ref="A232:XFD232"/>
-    <mergeCell ref="A233:XFD233"/>
-    <mergeCell ref="A222:XFD222"/>
-    <mergeCell ref="A223:XFD223"/>
-    <mergeCell ref="A224:XFD224"/>
-    <mergeCell ref="A225:XFD225"/>
-    <mergeCell ref="A226:XFD226"/>
-    <mergeCell ref="A227:XFD227"/>
-    <mergeCell ref="A240:XFD240"/>
-    <mergeCell ref="A241:XFD241"/>
-    <mergeCell ref="A242:XFD242"/>
-    <mergeCell ref="A243:XFD243"/>
-    <mergeCell ref="A244:XFD244"/>
-    <mergeCell ref="A245:XFD245"/>
-    <mergeCell ref="A234:XFD234"/>
-    <mergeCell ref="A235:XFD235"/>
-    <mergeCell ref="A236:XFD236"/>
-    <mergeCell ref="A237:XFD237"/>
-    <mergeCell ref="A238:XFD238"/>
-    <mergeCell ref="A239:XFD239"/>
-    <mergeCell ref="A252:XFD252"/>
-    <mergeCell ref="A253:XFD253"/>
-    <mergeCell ref="A254:XFD254"/>
-    <mergeCell ref="A255:XFD255"/>
-    <mergeCell ref="A256:XFD256"/>
-    <mergeCell ref="A257:XFD257"/>
-    <mergeCell ref="A246:XFD246"/>
-    <mergeCell ref="A247:XFD247"/>
-    <mergeCell ref="A248:XFD248"/>
-    <mergeCell ref="A249:XFD249"/>
-    <mergeCell ref="A250:XFD250"/>
-    <mergeCell ref="A251:XFD251"/>
-    <mergeCell ref="A264:XFD264"/>
-    <mergeCell ref="A265:XFD265"/>
-    <mergeCell ref="A266:XFD266"/>
-    <mergeCell ref="A267:XFD267"/>
-    <mergeCell ref="A268:XFD268"/>
-    <mergeCell ref="A269:XFD269"/>
-    <mergeCell ref="A258:XFD258"/>
-    <mergeCell ref="A259:XFD259"/>
-    <mergeCell ref="A260:XFD260"/>
-    <mergeCell ref="A261:XFD261"/>
-    <mergeCell ref="A262:XFD262"/>
-    <mergeCell ref="A263:XFD263"/>
-    <mergeCell ref="A276:XFD276"/>
-    <mergeCell ref="A277:XFD277"/>
-    <mergeCell ref="A278:XFD278"/>
-    <mergeCell ref="A279:XFD279"/>
-    <mergeCell ref="A280:XFD280"/>
-    <mergeCell ref="A281:XFD281"/>
-    <mergeCell ref="A270:XFD270"/>
-    <mergeCell ref="A271:XFD271"/>
-    <mergeCell ref="A272:XFD272"/>
-    <mergeCell ref="A273:XFD273"/>
-    <mergeCell ref="A274:XFD274"/>
-    <mergeCell ref="A275:XFD275"/>
-    <mergeCell ref="A288:XFD288"/>
-    <mergeCell ref="A289:XFD289"/>
-    <mergeCell ref="A290:XFD290"/>
-    <mergeCell ref="A291:XFD291"/>
-    <mergeCell ref="A292:XFD292"/>
-    <mergeCell ref="A293:XFD293"/>
-    <mergeCell ref="A282:XFD282"/>
-    <mergeCell ref="A283:XFD283"/>
-    <mergeCell ref="A284:XFD284"/>
-    <mergeCell ref="A285:XFD285"/>
-    <mergeCell ref="A286:XFD286"/>
-    <mergeCell ref="A287:XFD287"/>
-    <mergeCell ref="A300:XFD300"/>
-    <mergeCell ref="A301:XFD301"/>
-    <mergeCell ref="A302:XFD302"/>
-    <mergeCell ref="A303:XFD303"/>
-    <mergeCell ref="A304:XFD304"/>
-    <mergeCell ref="A305:XFD305"/>
-    <mergeCell ref="A294:XFD294"/>
-    <mergeCell ref="A295:XFD295"/>
-    <mergeCell ref="A296:XFD296"/>
-    <mergeCell ref="A297:XFD297"/>
-    <mergeCell ref="A298:XFD298"/>
-    <mergeCell ref="A299:XFD299"/>
-    <mergeCell ref="A323:XFD323"/>
-    <mergeCell ref="A312:XFD312"/>
-    <mergeCell ref="A313:XFD313"/>
-    <mergeCell ref="A314:XFD314"/>
-    <mergeCell ref="A315:XFD315"/>
-    <mergeCell ref="A316:XFD316"/>
-    <mergeCell ref="A317:XFD317"/>
-    <mergeCell ref="A306:XFD306"/>
-    <mergeCell ref="A307:XFD307"/>
-    <mergeCell ref="A308:XFD308"/>
-    <mergeCell ref="A309:XFD309"/>
-    <mergeCell ref="A310:XFD310"/>
-    <mergeCell ref="A311:XFD311"/>
     <mergeCell ref="A1:XFD1"/>
     <mergeCell ref="A336:XFD336"/>
     <mergeCell ref="A337:XFD337"/>
@@ -23383,6 +23067,322 @@
     <mergeCell ref="A320:XFD320"/>
     <mergeCell ref="A321:XFD321"/>
     <mergeCell ref="A322:XFD322"/>
+    <mergeCell ref="A323:XFD323"/>
+    <mergeCell ref="A312:XFD312"/>
+    <mergeCell ref="A313:XFD313"/>
+    <mergeCell ref="A314:XFD314"/>
+    <mergeCell ref="A315:XFD315"/>
+    <mergeCell ref="A316:XFD316"/>
+    <mergeCell ref="A317:XFD317"/>
+    <mergeCell ref="A306:XFD306"/>
+    <mergeCell ref="A307:XFD307"/>
+    <mergeCell ref="A308:XFD308"/>
+    <mergeCell ref="A309:XFD309"/>
+    <mergeCell ref="A310:XFD310"/>
+    <mergeCell ref="A311:XFD311"/>
+    <mergeCell ref="A300:XFD300"/>
+    <mergeCell ref="A301:XFD301"/>
+    <mergeCell ref="A302:XFD302"/>
+    <mergeCell ref="A303:XFD303"/>
+    <mergeCell ref="A304:XFD304"/>
+    <mergeCell ref="A305:XFD305"/>
+    <mergeCell ref="A294:XFD294"/>
+    <mergeCell ref="A295:XFD295"/>
+    <mergeCell ref="A296:XFD296"/>
+    <mergeCell ref="A297:XFD297"/>
+    <mergeCell ref="A298:XFD298"/>
+    <mergeCell ref="A299:XFD299"/>
+    <mergeCell ref="A288:XFD288"/>
+    <mergeCell ref="A289:XFD289"/>
+    <mergeCell ref="A290:XFD290"/>
+    <mergeCell ref="A291:XFD291"/>
+    <mergeCell ref="A292:XFD292"/>
+    <mergeCell ref="A293:XFD293"/>
+    <mergeCell ref="A282:XFD282"/>
+    <mergeCell ref="A283:XFD283"/>
+    <mergeCell ref="A284:XFD284"/>
+    <mergeCell ref="A285:XFD285"/>
+    <mergeCell ref="A286:XFD286"/>
+    <mergeCell ref="A287:XFD287"/>
+    <mergeCell ref="A276:XFD276"/>
+    <mergeCell ref="A277:XFD277"/>
+    <mergeCell ref="A278:XFD278"/>
+    <mergeCell ref="A279:XFD279"/>
+    <mergeCell ref="A280:XFD280"/>
+    <mergeCell ref="A281:XFD281"/>
+    <mergeCell ref="A270:XFD270"/>
+    <mergeCell ref="A271:XFD271"/>
+    <mergeCell ref="A272:XFD272"/>
+    <mergeCell ref="A273:XFD273"/>
+    <mergeCell ref="A274:XFD274"/>
+    <mergeCell ref="A275:XFD275"/>
+    <mergeCell ref="A264:XFD264"/>
+    <mergeCell ref="A265:XFD265"/>
+    <mergeCell ref="A266:XFD266"/>
+    <mergeCell ref="A267:XFD267"/>
+    <mergeCell ref="A268:XFD268"/>
+    <mergeCell ref="A269:XFD269"/>
+    <mergeCell ref="A258:XFD258"/>
+    <mergeCell ref="A259:XFD259"/>
+    <mergeCell ref="A260:XFD260"/>
+    <mergeCell ref="A261:XFD261"/>
+    <mergeCell ref="A262:XFD262"/>
+    <mergeCell ref="A263:XFD263"/>
+    <mergeCell ref="A252:XFD252"/>
+    <mergeCell ref="A253:XFD253"/>
+    <mergeCell ref="A254:XFD254"/>
+    <mergeCell ref="A255:XFD255"/>
+    <mergeCell ref="A256:XFD256"/>
+    <mergeCell ref="A257:XFD257"/>
+    <mergeCell ref="A246:XFD246"/>
+    <mergeCell ref="A247:XFD247"/>
+    <mergeCell ref="A248:XFD248"/>
+    <mergeCell ref="A249:XFD249"/>
+    <mergeCell ref="A250:XFD250"/>
+    <mergeCell ref="A251:XFD251"/>
+    <mergeCell ref="A240:XFD240"/>
+    <mergeCell ref="A241:XFD241"/>
+    <mergeCell ref="A242:XFD242"/>
+    <mergeCell ref="A243:XFD243"/>
+    <mergeCell ref="A244:XFD244"/>
+    <mergeCell ref="A245:XFD245"/>
+    <mergeCell ref="A234:XFD234"/>
+    <mergeCell ref="A235:XFD235"/>
+    <mergeCell ref="A236:XFD236"/>
+    <mergeCell ref="A237:XFD237"/>
+    <mergeCell ref="A238:XFD238"/>
+    <mergeCell ref="A239:XFD239"/>
+    <mergeCell ref="A228:XFD228"/>
+    <mergeCell ref="A229:XFD229"/>
+    <mergeCell ref="A230:XFD230"/>
+    <mergeCell ref="A231:XFD231"/>
+    <mergeCell ref="A232:XFD232"/>
+    <mergeCell ref="A233:XFD233"/>
+    <mergeCell ref="A222:XFD222"/>
+    <mergeCell ref="A223:XFD223"/>
+    <mergeCell ref="A224:XFD224"/>
+    <mergeCell ref="A225:XFD225"/>
+    <mergeCell ref="A226:XFD226"/>
+    <mergeCell ref="A227:XFD227"/>
+    <mergeCell ref="A216:XFD216"/>
+    <mergeCell ref="A217:XFD217"/>
+    <mergeCell ref="A218:XFD218"/>
+    <mergeCell ref="A219:XFD219"/>
+    <mergeCell ref="A220:XFD220"/>
+    <mergeCell ref="A221:XFD221"/>
+    <mergeCell ref="A210:XFD210"/>
+    <mergeCell ref="A211:XFD211"/>
+    <mergeCell ref="A212:XFD212"/>
+    <mergeCell ref="A213:XFD213"/>
+    <mergeCell ref="A214:XFD214"/>
+    <mergeCell ref="A215:XFD215"/>
+    <mergeCell ref="A204:XFD204"/>
+    <mergeCell ref="A205:XFD205"/>
+    <mergeCell ref="A206:XFD206"/>
+    <mergeCell ref="A207:XFD207"/>
+    <mergeCell ref="A208:XFD208"/>
+    <mergeCell ref="A209:XFD209"/>
+    <mergeCell ref="A198:XFD198"/>
+    <mergeCell ref="A199:XFD199"/>
+    <mergeCell ref="A200:XFD200"/>
+    <mergeCell ref="A201:XFD201"/>
+    <mergeCell ref="A202:XFD202"/>
+    <mergeCell ref="A203:XFD203"/>
+    <mergeCell ref="A192:XFD192"/>
+    <mergeCell ref="A193:XFD193"/>
+    <mergeCell ref="A194:XFD194"/>
+    <mergeCell ref="A195:XFD195"/>
+    <mergeCell ref="A196:XFD196"/>
+    <mergeCell ref="A197:XFD197"/>
+    <mergeCell ref="A186:XFD186"/>
+    <mergeCell ref="A187:XFD187"/>
+    <mergeCell ref="A188:XFD188"/>
+    <mergeCell ref="A189:XFD189"/>
+    <mergeCell ref="A190:XFD190"/>
+    <mergeCell ref="A191:XFD191"/>
+    <mergeCell ref="A180:XFD180"/>
+    <mergeCell ref="A181:XFD181"/>
+    <mergeCell ref="A182:XFD182"/>
+    <mergeCell ref="A183:XFD183"/>
+    <mergeCell ref="A184:XFD184"/>
+    <mergeCell ref="A185:XFD185"/>
+    <mergeCell ref="A174:XFD174"/>
+    <mergeCell ref="A175:XFD175"/>
+    <mergeCell ref="A176:XFD176"/>
+    <mergeCell ref="A177:XFD177"/>
+    <mergeCell ref="A178:XFD178"/>
+    <mergeCell ref="A179:XFD179"/>
+    <mergeCell ref="A168:XFD168"/>
+    <mergeCell ref="A169:XFD169"/>
+    <mergeCell ref="A170:XFD170"/>
+    <mergeCell ref="A171:XFD171"/>
+    <mergeCell ref="A172:XFD172"/>
+    <mergeCell ref="A173:XFD173"/>
+    <mergeCell ref="A162:XFD162"/>
+    <mergeCell ref="A163:XFD163"/>
+    <mergeCell ref="A164:XFD164"/>
+    <mergeCell ref="A165:XFD165"/>
+    <mergeCell ref="A166:XFD166"/>
+    <mergeCell ref="A167:XFD167"/>
+    <mergeCell ref="A156:XFD156"/>
+    <mergeCell ref="A157:XFD157"/>
+    <mergeCell ref="A158:XFD158"/>
+    <mergeCell ref="A159:XFD159"/>
+    <mergeCell ref="A160:XFD160"/>
+    <mergeCell ref="A161:XFD161"/>
+    <mergeCell ref="A150:XFD150"/>
+    <mergeCell ref="A151:XFD151"/>
+    <mergeCell ref="A152:XFD152"/>
+    <mergeCell ref="A153:XFD153"/>
+    <mergeCell ref="A154:XFD154"/>
+    <mergeCell ref="A155:XFD155"/>
+    <mergeCell ref="A144:XFD144"/>
+    <mergeCell ref="A145:XFD145"/>
+    <mergeCell ref="A146:XFD146"/>
+    <mergeCell ref="A147:XFD147"/>
+    <mergeCell ref="A148:XFD148"/>
+    <mergeCell ref="A149:XFD149"/>
+    <mergeCell ref="A138:XFD138"/>
+    <mergeCell ref="A139:XFD139"/>
+    <mergeCell ref="A140:XFD140"/>
+    <mergeCell ref="A141:XFD141"/>
+    <mergeCell ref="A142:XFD142"/>
+    <mergeCell ref="A143:XFD143"/>
+    <mergeCell ref="A132:XFD132"/>
+    <mergeCell ref="A133:XFD133"/>
+    <mergeCell ref="A134:XFD134"/>
+    <mergeCell ref="A135:XFD135"/>
+    <mergeCell ref="A136:XFD136"/>
+    <mergeCell ref="A137:XFD137"/>
+    <mergeCell ref="A126:XFD126"/>
+    <mergeCell ref="A127:XFD127"/>
+    <mergeCell ref="A128:XFD128"/>
+    <mergeCell ref="A129:XFD129"/>
+    <mergeCell ref="A130:XFD130"/>
+    <mergeCell ref="A131:XFD131"/>
+    <mergeCell ref="A120:XFD120"/>
+    <mergeCell ref="A121:XFD121"/>
+    <mergeCell ref="A122:XFD122"/>
+    <mergeCell ref="A123:XFD123"/>
+    <mergeCell ref="A124:XFD124"/>
+    <mergeCell ref="A125:XFD125"/>
+    <mergeCell ref="A114:XFD114"/>
+    <mergeCell ref="A115:XFD115"/>
+    <mergeCell ref="A116:XFD116"/>
+    <mergeCell ref="A117:XFD117"/>
+    <mergeCell ref="A118:XFD118"/>
+    <mergeCell ref="A119:XFD119"/>
+    <mergeCell ref="A108:XFD108"/>
+    <mergeCell ref="A109:XFD109"/>
+    <mergeCell ref="A110:XFD110"/>
+    <mergeCell ref="A111:XFD111"/>
+    <mergeCell ref="A112:XFD112"/>
+    <mergeCell ref="A113:XFD113"/>
+    <mergeCell ref="A102:XFD102"/>
+    <mergeCell ref="A103:XFD103"/>
+    <mergeCell ref="A104:XFD104"/>
+    <mergeCell ref="A105:XFD105"/>
+    <mergeCell ref="A106:XFD106"/>
+    <mergeCell ref="A107:XFD107"/>
+    <mergeCell ref="A96:XFD96"/>
+    <mergeCell ref="A97:XFD97"/>
+    <mergeCell ref="A98:XFD98"/>
+    <mergeCell ref="A99:XFD99"/>
+    <mergeCell ref="A100:XFD100"/>
+    <mergeCell ref="A101:XFD101"/>
+    <mergeCell ref="A90:XFD90"/>
+    <mergeCell ref="A91:XFD91"/>
+    <mergeCell ref="A92:XFD92"/>
+    <mergeCell ref="A93:XFD93"/>
+    <mergeCell ref="A94:XFD94"/>
+    <mergeCell ref="A95:XFD95"/>
+    <mergeCell ref="A84:XFD84"/>
+    <mergeCell ref="A85:XFD85"/>
+    <mergeCell ref="A86:XFD86"/>
+    <mergeCell ref="A87:XFD87"/>
+    <mergeCell ref="A88:XFD88"/>
+    <mergeCell ref="A89:XFD89"/>
+    <mergeCell ref="A78:XFD78"/>
+    <mergeCell ref="A79:XFD79"/>
+    <mergeCell ref="A80:XFD80"/>
+    <mergeCell ref="A81:XFD81"/>
+    <mergeCell ref="A82:XFD82"/>
+    <mergeCell ref="A83:XFD83"/>
+    <mergeCell ref="A72:XFD72"/>
+    <mergeCell ref="A73:XFD73"/>
+    <mergeCell ref="A74:XFD74"/>
+    <mergeCell ref="A75:XFD75"/>
+    <mergeCell ref="A76:XFD76"/>
+    <mergeCell ref="A77:XFD77"/>
+    <mergeCell ref="A66:XFD66"/>
+    <mergeCell ref="A67:XFD67"/>
+    <mergeCell ref="A68:XFD68"/>
+    <mergeCell ref="A69:XFD69"/>
+    <mergeCell ref="A70:XFD70"/>
+    <mergeCell ref="A71:XFD71"/>
+    <mergeCell ref="A60:XFD60"/>
+    <mergeCell ref="A61:XFD61"/>
+    <mergeCell ref="A62:XFD62"/>
+    <mergeCell ref="A63:XFD63"/>
+    <mergeCell ref="A64:XFD64"/>
+    <mergeCell ref="A65:XFD65"/>
+    <mergeCell ref="A54:XFD54"/>
+    <mergeCell ref="A55:XFD55"/>
+    <mergeCell ref="A56:XFD56"/>
+    <mergeCell ref="A57:XFD57"/>
+    <mergeCell ref="A58:XFD58"/>
+    <mergeCell ref="A59:XFD59"/>
+    <mergeCell ref="A48:XFD48"/>
+    <mergeCell ref="A49:XFD49"/>
+    <mergeCell ref="A50:XFD50"/>
+    <mergeCell ref="A51:XFD51"/>
+    <mergeCell ref="A52:XFD52"/>
+    <mergeCell ref="A53:XFD53"/>
+    <mergeCell ref="A42:XFD42"/>
+    <mergeCell ref="A43:XFD43"/>
+    <mergeCell ref="A44:XFD44"/>
+    <mergeCell ref="A45:XFD45"/>
+    <mergeCell ref="A46:XFD46"/>
+    <mergeCell ref="A47:XFD47"/>
+    <mergeCell ref="A36:XFD36"/>
+    <mergeCell ref="A37:XFD37"/>
+    <mergeCell ref="A38:XFD38"/>
+    <mergeCell ref="A39:XFD39"/>
+    <mergeCell ref="A40:XFD40"/>
+    <mergeCell ref="A41:XFD41"/>
+    <mergeCell ref="A30:XFD30"/>
+    <mergeCell ref="A31:XFD31"/>
+    <mergeCell ref="A32:XFD32"/>
+    <mergeCell ref="A33:XFD33"/>
+    <mergeCell ref="A34:XFD34"/>
+    <mergeCell ref="A35:XFD35"/>
+    <mergeCell ref="A24:XFD24"/>
+    <mergeCell ref="A25:XFD25"/>
+    <mergeCell ref="A26:XFD26"/>
+    <mergeCell ref="A27:XFD27"/>
+    <mergeCell ref="A28:XFD28"/>
+    <mergeCell ref="A29:XFD29"/>
+    <mergeCell ref="A18:XFD18"/>
+    <mergeCell ref="A19:XFD19"/>
+    <mergeCell ref="A20:XFD20"/>
+    <mergeCell ref="A21:XFD21"/>
+    <mergeCell ref="A22:XFD22"/>
+    <mergeCell ref="A23:XFD23"/>
+    <mergeCell ref="A12:XFD12"/>
+    <mergeCell ref="A13:XFD13"/>
+    <mergeCell ref="A14:XFD14"/>
+    <mergeCell ref="A15:XFD15"/>
+    <mergeCell ref="A16:XFD16"/>
+    <mergeCell ref="A17:XFD17"/>
+    <mergeCell ref="A3:XFD3"/>
+    <mergeCell ref="A4:XFD4"/>
+    <mergeCell ref="A5:XFD5"/>
+    <mergeCell ref="A6:XFD6"/>
+    <mergeCell ref="A7:XFD7"/>
+    <mergeCell ref="A8:XFD8"/>
+    <mergeCell ref="A9:XFD9"/>
+    <mergeCell ref="A10:XFD10"/>
+    <mergeCell ref="A11:XFD11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Tomodachi Life Living the Dream island dating analysis.xlsx
+++ b/Tomodachi Life Living the Dream island dating analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Robin\OneDrive\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{371CC4DD-453B-4401-A541-8F23F836CD92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCD26421-64C9-440D-A7DC-B909456069A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18700" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18700" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mii List" sheetId="1" r:id="rId1"/>
@@ -1862,7 +1862,23 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00070"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0070C0"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -6151,6 +6167,29 @@
       <c r="E490" s="16"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:B200">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"Male"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:B200">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"Female"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:B200">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+      <formula>"Nonbinary"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid entry" error="Please enter only ✗ or ✓" promptTitle="Input Required" prompt="Select ✗ or ✓ from the dropdown" sqref="C2:E200" xr:uid="{AEF1802F-0A93-46BF-B429-58403F8AC1D8}">
+      <formula1>"✗,✓"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid entry" error="Please enter a valid gender" promptTitle="Input Required" prompt="Select Male, Female, or Nonbinary from the dropdown" sqref="B2:B200" xr:uid="{EC06DB7A-81CC-48F4-BAF6-5F2E83418525}">
+      <formula1>"Male,Female,Nonbinary"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/Tomodachi Life Living the Dream island dating analysis.xlsx
+++ b/Tomodachi Life Living the Dream island dating analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Robin\OneDrive\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCD26421-64C9-440D-A7DC-B909456069A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74CEC80B-D449-4049-85B4-05D0902A75B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18700" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="431">
   <si>
     <t>Name</t>
   </si>
@@ -1351,6 +1351,9 @@
   </si>
   <si>
     <t>Nny</t>
+  </si>
+  <si>
+    <t>Wayward Vagabond</t>
   </si>
 </sst>
 </file>
@@ -1849,20 +1852,61 @@
     <xf numFmtId="0" fontId="12" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Calculation" xfId="1" builtinId="22"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="10">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00070"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF0070C0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF548235"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF7030A0"/>
@@ -2213,7 +2257,7 @@
       </c>
       <c r="H2" s="7">
         <f>COUNTA(A2:A200)</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
@@ -2239,7 +2283,7 @@
       </c>
       <c r="H3" s="9">
         <f>COUNTIF(B:B,"Male")</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I3" s="10" t="s">
         <v>9</v>
@@ -3094,11 +3138,21 @@
       </c>
     </row>
     <row r="52" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="15"/>
-      <c r="B52" s="16"/>
-      <c r="C52" s="16"/>
-      <c r="D52" s="16"/>
-      <c r="E52" s="16"/>
+      <c r="A52" s="15" t="s">
+        <v>430</v>
+      </c>
+      <c r="B52" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D52" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="E52" s="16" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="53" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="13"/>
@@ -6168,18 +6222,39 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B200">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
       <formula>"Male"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
+      <formula>"Female"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
+      <formula>"Nonbinary"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:E200">
+    <cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="✓">
+      <formula>NOT(ISERROR(SEARCH("✓",C2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:E200">
+    <cfRule type="containsText" dxfId="3" priority="5" operator="containsText" text="✗">
+      <formula>NOT(ISERROR(SEARCH("✗",C2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:B200">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>"Female"</formula>
+    <cfRule type="containsText" dxfId="2" priority="6" operator="containsText" text="Male">
+      <formula>NOT(ISERROR(SEARCH("Male",B2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:B200">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
-      <formula>"Nonbinary"</formula>
+    <cfRule type="containsText" dxfId="1" priority="7" operator="containsText" text="Female">
+      <formula>NOT(ISERROR(SEARCH("Female",B2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:B200">
+    <cfRule type="containsText" dxfId="0" priority="8" operator="containsText" text="Nonbinary">
+      <formula>NOT(ISERROR(SEARCH("Nonbinary",B2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
@@ -6241,7 +6316,7 @@
       </c>
       <c r="B6" s="22">
         <f>COUNTA('Mii List'!A2:A200)</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C6" s="22" t="s">
         <v>21</v>
@@ -6253,11 +6328,11 @@
       </c>
       <c r="B7" s="22">
         <f>COUNTIF('Mii List'!B2:B200,"Male")</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C7" s="23">
         <f>B7/B6</f>
-        <v>0.64</v>
+        <v>0.6470588235294118</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -6270,7 +6345,7 @@
       </c>
       <c r="C8" s="23">
         <f>B8/B6</f>
-        <v>0.32</v>
+        <v>0.31372549019607843</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -6283,7 +6358,7 @@
       </c>
       <c r="C9" s="23">
         <f>B9/B6</f>
-        <v>0.04</v>
+        <v>3.9215686274509803E-2</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -6314,7 +6389,7 @@
       </c>
       <c r="C13" s="23">
         <f>B13/B6</f>
-        <v>0.66</v>
+        <v>0.6470588235294118</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -6323,11 +6398,11 @@
       </c>
       <c r="B14" s="22">
         <f>SUM('Matching Engine'!G2:G201)</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C14" s="23">
         <f>B14/B6</f>
-        <v>0.78</v>
+        <v>0.78431372549019607</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -6340,7 +6415,7 @@
       </c>
       <c r="C15" s="23">
         <f>B15/B6</f>
-        <v>0.48</v>
+        <v>0.47058823529411764</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -6353,7 +6428,7 @@
       </c>
       <c r="C16" s="26">
         <f>B16/B6</f>
-        <v>0.02</v>
+        <v>1.9607843137254902E-2</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -6419,7 +6494,7 @@
       </c>
       <c r="B22" s="28">
         <f>SUMPRODUCT(('Matching Engine'!I2:I201=1)*('Matching Engine'!F2:F201=0)*('Matching Engine'!G2:G201=1)*('Matching Engine'!H2:H201=0))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C22" s="28">
         <f>SUMPRODUCT(('Matching Engine'!J2:J201=1)*('Matching Engine'!F2:F201=1))</f>
@@ -6602,7 +6677,7 @@
       </c>
       <c r="C32" s="28">
         <f>SUMPRODUCT(('Matching Engine'!I2:I201=1)*('Matching Engine'!G2:G201=1))</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D32" s="28">
         <f t="shared" si="0"/>
@@ -6620,7 +6695,7 @@
       </c>
       <c r="C33" s="28">
         <f>SUMPRODUCT(('Matching Engine'!I2:I201=1)*('Matching Engine'!G2:G201=1))+SUMPRODUCT(('Matching Engine'!K2:K201=1)*('Matching Engine'!G2:G201=1))</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D33" s="28">
         <f t="shared" si="0"/>
@@ -6638,7 +6713,7 @@
       </c>
       <c r="C34" s="28">
         <f>SUMPRODUCT(('Matching Engine'!I2:I201=1)*('Matching Engine'!G2:G201=1))+SUMPRODUCT(('Matching Engine'!J2:J201=1)*('Matching Engine'!G2:G201=1))</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D34" s="28">
         <f t="shared" si="0"/>
@@ -6656,7 +6731,7 @@
       </c>
       <c r="C35" s="28">
         <f>SUMPRODUCT(('Matching Engine'!I2:I201=1)*('Matching Engine'!G2:G201=1))+SUMPRODUCT(('Matching Engine'!J2:J201=1)*('Matching Engine'!G2:G201=1))+SUMPRODUCT(('Matching Engine'!K2:K201=1)*('Matching Engine'!G2:G201=1))</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D35" s="28">
         <f t="shared" si="0"/>
@@ -6862,7 +6937,7 @@
       </c>
       <c r="B50" s="40">
         <f>IF(MOD(B6-B48-B49,2)=1,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C50" s="39" t="s">
         <v>68</v>
@@ -6874,7 +6949,7 @@
       </c>
       <c r="B51" s="42">
         <f>B48+B49+B50</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C51" s="39" t="s">
         <v>70</v>
@@ -6886,7 +6961,7 @@
       </c>
       <c r="B52" s="40">
         <f>INT((B6-B51)/2)</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C52" s="39" t="s">
         <v>71</v>
@@ -6898,7 +6973,7 @@
       </c>
       <c r="B53" s="47">
         <f>(B6-B51)/B6</f>
-        <v>0.96</v>
+        <v>0.98039215686274506</v>
       </c>
       <c r="C53" s="39" t="s">
         <v>72</v>
@@ -6910,7 +6985,7 @@
       </c>
       <c r="B54" s="43" cm="1">
         <f t="array" aca="1" ref="B54" ca="1">_xlfn.LET(_xlpm.a,'Matching Engine'!N2:N51,_xlpm.b,'Matching Engine'!L2:L51,_xlpm.c,B6,_xlpm.s,'Matching Engine'!P2:P51,_xlpm.d,_xlpm.c/2,_xlpm.e,SUMPRODUCT(IF(_xlpm.b=0,1,EXP(-(_xlpm.a+_xlpm.b*_xlpm.s*_xlpm.d/_xlpm.c)))),_xlpm.f,(_xlpm.e+_xlpm.d)/2,_xlpm.g,SUMPRODUCT(IF(_xlpm.b=0,1,EXP(-(_xlpm.a+_xlpm.b*_xlpm.s*_xlpm.f/_xlpm.c)))),_xlpm.h,(_xlpm.g+_xlpm.f)/2,_xlpm.i,SUMPRODUCT(IF(_xlpm.b=0,1,EXP(-(_xlpm.a+_xlpm.b*_xlpm.s*_xlpm.h/_xlpm.c)))),_xlpm.j,(_xlpm.i+_xlpm.h)/2,_xlpm.k,SUMPRODUCT(IF(_xlpm.b=0,1,EXP(-(_xlpm.a+_xlpm.b*_xlpm.s*_xlpm.j/_xlpm.c)))),_xlpm.l,(_xlpm.k+_xlpm.j)/2,_xlpm.m,SUMPRODUCT(IF(_xlpm.b=0,1,EXP(-(_xlpm.a+_xlpm.b*_xlpm.s*_xlpm.l/_xlpm.c)))),_xlpm.n,(_xlpm.m+_xlpm.l)/2,(_xlpm.c-_xlpm.n)/2)</f>
-        <v>21.555298788499762</v>
+        <v>21.979892660010357</v>
       </c>
       <c r="C54" s="39" t="s">
         <v>377</v>
@@ -6922,7 +6997,7 @@
       </c>
       <c r="B55" s="47">
         <f ca="1">B54*2/B6</f>
-        <v>0.86221195153999053</v>
+        <v>0.86195657490236699</v>
       </c>
       <c r="C55" s="39" t="s">
         <v>94</v>
@@ -7229,7 +7304,7 @@
       </c>
       <c r="E73" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>22% — 11 of 49 compatible</v>
+        <v>22% — 11 of 50 compatible</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -7251,7 +7326,7 @@
       </c>
       <c r="E74" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>22% — 11 of 49 compatible</v>
+        <v>22% — 11 of 50 compatible</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -7273,7 +7348,7 @@
       </c>
       <c r="E75" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>29% — 14 of 49 compatible</v>
+        <v>28% — 14 of 50 compatible</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -7295,7 +7370,7 @@
       </c>
       <c r="E76" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>29% — 14 of 49 compatible</v>
+        <v>28% — 14 of 50 compatible</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -7317,7 +7392,7 @@
       </c>
       <c r="E77" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>29% — 14 of 49 compatible</v>
+        <v>28% — 14 of 50 compatible</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -7339,7 +7414,7 @@
       </c>
       <c r="E78" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>29% — 14 of 49 compatible</v>
+        <v>28% — 14 of 50 compatible</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -7361,7 +7436,7 @@
       </c>
       <c r="E79" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>29% — 14 of 49 compatible</v>
+        <v>28% — 14 of 50 compatible</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -7383,7 +7458,7 @@
       </c>
       <c r="E80" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>29% — 14 of 49 compatible</v>
+        <v>28% — 14 of 50 compatible</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -7405,7 +7480,7 @@
       </c>
       <c r="E81" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>29% — 14 of 49 compatible</v>
+        <v>28% — 14 of 50 compatible</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -7427,7 +7502,7 @@
       </c>
       <c r="E82" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>29% — 14 of 49 compatible</v>
+        <v>28% — 14 of 50 compatible</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -7449,7 +7524,7 @@
       </c>
       <c r="E83" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>29% — 14 of 49 compatible</v>
+        <v>28% — 14 of 50 compatible</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -7471,7 +7546,7 @@
       </c>
       <c r="E84" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>29% — 14 of 49 compatible</v>
+        <v>28% — 14 of 50 compatible</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -7493,7 +7568,7 @@
       </c>
       <c r="E85" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>29% — 14 of 49 compatible</v>
+        <v>28% — 14 of 50 compatible</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -7515,13 +7590,13 @@
       </c>
       <c r="E86" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>29% — 14 of 49 compatible</v>
+        <v>28% — 14 of 50 compatible</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Yoshiaki Koizumi</v>
+        <v>Wayward Vagabond</v>
       </c>
       <c r="B87" s="22" t="str">
         <f>IF(A87="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A87,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7537,13 +7612,13 @@
       </c>
       <c r="E87" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>29% — 14 of 49 compatible</v>
+        <v>28% — 14 of 50 compatible</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Huey Freeman</v>
+        <v>Yoshiaki Koizumi</v>
       </c>
       <c r="B88" s="22" t="str">
         <f>IF(A88="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A88,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7551,21 +7626,21 @@
       </c>
       <c r="C88" s="22" t="str">
         <f>IF(A88="","",IF(AND(INDEX('Matching Engine'!F$2:F$201,MATCH(A88,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!G$2:G$201,MATCH(A88,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!H$2:H$201,MATCH(A88,'Matching Engine'!A$2:A$201,0))=0),"None",IF(INDEX('Matching Engine'!F$2:F$201,MATCH(A88,'Matching Engine'!A$2:A$201,0))=1,"♂ ","")&amp;IF(INDEX('Matching Engine'!G$2:G$201,MATCH(A88,'Matching Engine'!A$2:A$201,0))=1,"♀ ","")&amp;IF(INDEX('Matching Engine'!H$2:H$201,MATCH(A88,'Matching Engine'!A$2:A$201,0))=1,"⚧","")))</f>
-        <v>♀ ⚧</v>
+        <v xml:space="preserve">♀ </v>
       </c>
       <c r="D88" s="22">
         <f>IF(A88="","",INDEX('Matching Engine'!L$2:L$201,MATCH(A88,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E88" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>31% — 15 of 49 compatible</v>
+        <v>28% — 14 of 50 compatible</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Chuck</v>
+        <v>Huey Freeman</v>
       </c>
       <c r="B89" s="22" t="str">
         <f>IF(A89="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A89,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7573,21 +7648,21 @@
       </c>
       <c r="C89" s="22" t="str">
         <f>IF(A89="","",IF(AND(INDEX('Matching Engine'!F$2:F$201,MATCH(A89,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!G$2:G$201,MATCH(A89,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!H$2:H$201,MATCH(A89,'Matching Engine'!A$2:A$201,0))=0),"None",IF(INDEX('Matching Engine'!F$2:F$201,MATCH(A89,'Matching Engine'!A$2:A$201,0))=1,"♂ ","")&amp;IF(INDEX('Matching Engine'!G$2:G$201,MATCH(A89,'Matching Engine'!A$2:A$201,0))=1,"♀ ","")&amp;IF(INDEX('Matching Engine'!H$2:H$201,MATCH(A89,'Matching Engine'!A$2:A$201,0))=1,"⚧","")))</f>
-        <v xml:space="preserve">♂ </v>
+        <v>♀ ⚧</v>
       </c>
       <c r="D89" s="22">
         <f>IF(A89="","",INDEX('Matching Engine'!L$2:L$201,MATCH(A89,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E89" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>35% — 17 of 49 compatible</v>
+        <v>30% — 15 of 50 compatible</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>House</v>
+        <v>Chuck</v>
       </c>
       <c r="B90" s="22" t="str">
         <f>IF(A90="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A90,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7603,13 +7678,13 @@
       </c>
       <c r="E90" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>35% — 17 of 49 compatible</v>
+        <v>34% — 17 of 50 compatible</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Larry</v>
+        <v>House</v>
       </c>
       <c r="B91" s="22" t="str">
         <f>IF(A91="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A91,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7625,13 +7700,13 @@
       </c>
       <c r="E91" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>35% — 17 of 49 compatible</v>
+        <v>34% — 17 of 50 compatible</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Morty</v>
+        <v>Larry</v>
       </c>
       <c r="B92" s="22" t="str">
         <f>IF(A92="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A92,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7647,13 +7722,13 @@
       </c>
       <c r="E92" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>35% — 17 of 49 compatible</v>
+        <v>34% — 17 of 50 compatible</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Wilson</v>
+        <v>Morty</v>
       </c>
       <c r="B93" s="22" t="str">
         <f>IF(A93="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A93,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7669,13 +7744,13 @@
       </c>
       <c r="E93" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>35% — 17 of 49 compatible</v>
+        <v>34% — 17 of 50 compatible</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Alvie</v>
+        <v>Wilson</v>
       </c>
       <c r="B94" s="22" t="str">
         <f>IF(A94="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A94,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7683,65 +7758,65 @@
       </c>
       <c r="C94" s="22" t="str">
         <f>IF(A94="","",IF(AND(INDEX('Matching Engine'!F$2:F$201,MATCH(A94,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!G$2:G$201,MATCH(A94,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!H$2:H$201,MATCH(A94,'Matching Engine'!A$2:A$201,0))=0),"None",IF(INDEX('Matching Engine'!F$2:F$201,MATCH(A94,'Matching Engine'!A$2:A$201,0))=1,"♂ ","")&amp;IF(INDEX('Matching Engine'!G$2:G$201,MATCH(A94,'Matching Engine'!A$2:A$201,0))=1,"♀ ","")&amp;IF(INDEX('Matching Engine'!H$2:H$201,MATCH(A94,'Matching Engine'!A$2:A$201,0))=1,"⚧","")))</f>
-        <v>♂ ⚧</v>
+        <v xml:space="preserve">♂ </v>
       </c>
       <c r="D94" s="22">
         <f>IF(A94="","",INDEX('Matching Engine'!L$2:L$201,MATCH(A94,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E94" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>37% — 18 of 49 compatible</v>
+        <v>34% — 17 of 50 compatible</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Robin</v>
+        <v>Alvie</v>
       </c>
       <c r="B95" s="22" t="str">
         <f>IF(A95="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A95,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>Nonbinary</v>
+        <v>Male</v>
       </c>
       <c r="C95" s="22" t="str">
         <f>IF(A95="","",IF(AND(INDEX('Matching Engine'!F$2:F$201,MATCH(A95,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!G$2:G$201,MATCH(A95,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!H$2:H$201,MATCH(A95,'Matching Engine'!A$2:A$201,0))=0),"None",IF(INDEX('Matching Engine'!F$2:F$201,MATCH(A95,'Matching Engine'!A$2:A$201,0))=1,"♂ ","")&amp;IF(INDEX('Matching Engine'!G$2:G$201,MATCH(A95,'Matching Engine'!A$2:A$201,0))=1,"♀ ","")&amp;IF(INDEX('Matching Engine'!H$2:H$201,MATCH(A95,'Matching Engine'!A$2:A$201,0))=1,"⚧","")))</f>
-        <v>♂ ♀ ⚧</v>
+        <v>♂ ⚧</v>
       </c>
       <c r="D95" s="22">
         <f>IF(A95="","",INDEX('Matching Engine'!L$2:L$201,MATCH(A95,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E95" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>47% — 23 of 49 compatible</v>
+        <v>36% — 18 of 50 compatible</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Bea</v>
+        <v>Robin</v>
       </c>
       <c r="B96" s="22" t="str">
         <f>IF(A96="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A96,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>Female</v>
+        <v>Nonbinary</v>
       </c>
       <c r="C96" s="22" t="str">
         <f>IF(A96="","",IF(AND(INDEX('Matching Engine'!F$2:F$201,MATCH(A96,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!G$2:G$201,MATCH(A96,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!H$2:H$201,MATCH(A96,'Matching Engine'!A$2:A$201,0))=0),"None",IF(INDEX('Matching Engine'!F$2:F$201,MATCH(A96,'Matching Engine'!A$2:A$201,0))=1,"♂ ","")&amp;IF(INDEX('Matching Engine'!G$2:G$201,MATCH(A96,'Matching Engine'!A$2:A$201,0))=1,"♀ ","")&amp;IF(INDEX('Matching Engine'!H$2:H$201,MATCH(A96,'Matching Engine'!A$2:A$201,0))=1,"⚧","")))</f>
-        <v xml:space="preserve">♂ </v>
+        <v>♂ ♀ ⚧</v>
       </c>
       <c r="D96" s="22">
         <f>IF(A96="","",INDEX('Matching Engine'!L$2:L$201,MATCH(A96,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E96" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>53% — 26 of 49 compatible</v>
+        <v>46% — 23 of 50 compatible</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Cameron</v>
+        <v>Bea</v>
       </c>
       <c r="B97" s="22" t="str">
         <f>IF(A97="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A97,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7753,17 +7828,17 @@
       </c>
       <c r="D97" s="22">
         <f>IF(A97="","",INDEX('Matching Engine'!L$2:L$201,MATCH(A97,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E97" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>53% — 26 of 49 compatible</v>
+        <v>54% — 27 of 50 compatible</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Cuddy</v>
+        <v>Cameron</v>
       </c>
       <c r="B98" s="22" t="str">
         <f>IF(A98="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A98,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7775,17 +7850,17 @@
       </c>
       <c r="D98" s="22">
         <f>IF(A98="","",INDEX('Matching Engine'!L$2:L$201,MATCH(A98,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E98" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>53% — 26 of 49 compatible</v>
+        <v>54% — 27 of 50 compatible</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Katy Perry</v>
+        <v>Cuddy</v>
       </c>
       <c r="B99" s="22" t="str">
         <f>IF(A99="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A99,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7797,39 +7872,39 @@
       </c>
       <c r="D99" s="22">
         <f>IF(A99="","",INDEX('Matching Engine'!L$2:L$201,MATCH(A99,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E99" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>53% — 26 of 49 compatible</v>
+        <v>54% — 27 of 50 compatible</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Chase</v>
+        <v>Katy Perry</v>
       </c>
       <c r="B100" s="22" t="str">
         <f>IF(A100="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A100,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="C100" s="22" t="str">
         <f>IF(A100="","",IF(AND(INDEX('Matching Engine'!F$2:F$201,MATCH(A100,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!G$2:G$201,MATCH(A100,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!H$2:H$201,MATCH(A100,'Matching Engine'!A$2:A$201,0))=0),"None",IF(INDEX('Matching Engine'!F$2:F$201,MATCH(A100,'Matching Engine'!A$2:A$201,0))=1,"♂ ","")&amp;IF(INDEX('Matching Engine'!G$2:G$201,MATCH(A100,'Matching Engine'!A$2:A$201,0))=1,"♀ ","")&amp;IF(INDEX('Matching Engine'!H$2:H$201,MATCH(A100,'Matching Engine'!A$2:A$201,0))=1,"⚧","")))</f>
-        <v>♂ ♀ ⚧</v>
+        <v xml:space="preserve">♂ </v>
       </c>
       <c r="D100" s="22">
         <f>IF(A100="","",INDEX('Matching Engine'!L$2:L$201,MATCH(A100,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E100" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>65% — 32 of 49 compatible</v>
+        <v>54% — 27 of 50 compatible</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Dave Strider</v>
+        <v>Chase</v>
       </c>
       <c r="B101" s="22" t="str">
         <f>IF(A101="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A101,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7845,13 +7920,13 @@
       </c>
       <c r="E101" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>65% — 32 of 49 compatible</v>
+        <v>64% — 32 of 50 compatible</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Equius Zahhak</v>
+        <v>Dave Strider</v>
       </c>
       <c r="B102" s="22" t="str">
         <f>IF(A102="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A102,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7867,13 +7942,13 @@
       </c>
       <c r="E102" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>65% — 32 of 49 compatible</v>
+        <v>64% — 32 of 50 compatible</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Eridan Ampora</v>
+        <v>Equius Zahhak</v>
       </c>
       <c r="B103" s="22" t="str">
         <f>IF(A103="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A103,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7889,13 +7964,13 @@
       </c>
       <c r="E103" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>65% — 32 of 49 compatible</v>
+        <v>64% — 32 of 50 compatible</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Gamzee Makara</v>
+        <v>Eridan Ampora</v>
       </c>
       <c r="B104" s="22" t="str">
         <f>IF(A104="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A104,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7911,13 +7986,13 @@
       </c>
       <c r="E104" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>65% — 32 of 49 compatible</v>
+        <v>64% — 32 of 50 compatible</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Hugh Morris</v>
+        <v>Gamzee Makara</v>
       </c>
       <c r="B105" s="22" t="str">
         <f>IF(A105="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A105,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7933,13 +8008,13 @@
       </c>
       <c r="E105" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>65% — 32 of 49 compatible</v>
+        <v>64% — 32 of 50 compatible</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Jason Speer</v>
+        <v>Hugh Morris</v>
       </c>
       <c r="B106" s="22" t="str">
         <f>IF(A106="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A106,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7955,13 +8030,13 @@
       </c>
       <c r="E106" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>65% — 32 of 49 compatible</v>
+        <v>64% — 32 of 50 compatible</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Karkat Vantas</v>
+        <v>Jason Speer</v>
       </c>
       <c r="B107" s="22" t="str">
         <f>IF(A107="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A107,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7977,13 +8052,13 @@
       </c>
       <c r="E107" s="22" t="str">
         <f t="shared" ref="E107:E138" si="3">IF(A107="","",IF(D107=0,"0% — no compatible partners",TEXT(D107/($B$6-1),"0%")&amp;" — "&amp;D107&amp;" of "&amp;($B$6-1)&amp;" compatible"))</f>
-        <v>65% — 32 of 49 compatible</v>
+        <v>64% — 32 of 50 compatible</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Michael Newman</v>
+        <v>Karkat Vantas</v>
       </c>
       <c r="B108" s="22" t="str">
         <f>IF(A108="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A108,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7999,13 +8074,13 @@
       </c>
       <c r="E108" s="22" t="str">
         <f t="shared" si="3"/>
-        <v>65% — 32 of 49 compatible</v>
+        <v>64% — 32 of 50 compatible</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Randy Sexton</v>
+        <v>Michael Newman</v>
       </c>
       <c r="B109" s="22" t="str">
         <f>IF(A109="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A109,'Matching Engine'!A$2:A$201,0)))</f>
@@ -8021,13 +8096,13 @@
       </c>
       <c r="E109" s="22" t="str">
         <f t="shared" si="3"/>
-        <v>65% — 32 of 49 compatible</v>
+        <v>64% — 32 of 50 compatible</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Sollux Captor</v>
+        <v>Randy Sexton</v>
       </c>
       <c r="B110" s="22" t="str">
         <f>IF(A110="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A110,'Matching Engine'!A$2:A$201,0)))</f>
@@ -8043,13 +8118,13 @@
       </c>
       <c r="E110" s="22" t="str">
         <f t="shared" si="3"/>
-        <v>65% — 32 of 49 compatible</v>
+        <v>64% — 32 of 50 compatible</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Tavros Nitram</v>
+        <v>Sollux Captor</v>
       </c>
       <c r="B111" s="22" t="str">
         <f>IF(A111="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A111,'Matching Engine'!A$2:A$201,0)))</f>
@@ -8065,35 +8140,35 @@
       </c>
       <c r="E111" s="22" t="str">
         <f t="shared" si="3"/>
-        <v>65% — 32 of 49 compatible</v>
+        <v>64% — 32 of 50 compatible</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Thirteen</v>
+        <v>Tavros Nitram</v>
       </c>
       <c r="B112" s="22" t="str">
         <f>IF(A112="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A112,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="C112" s="22" t="str">
         <f>IF(A112="","",IF(AND(INDEX('Matching Engine'!F$2:F$201,MATCH(A112,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!G$2:G$201,MATCH(A112,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!H$2:H$201,MATCH(A112,'Matching Engine'!A$2:A$201,0))=0),"None",IF(INDEX('Matching Engine'!F$2:F$201,MATCH(A112,'Matching Engine'!A$2:A$201,0))=1,"♂ ","")&amp;IF(INDEX('Matching Engine'!G$2:G$201,MATCH(A112,'Matching Engine'!A$2:A$201,0))=1,"♀ ","")&amp;IF(INDEX('Matching Engine'!H$2:H$201,MATCH(A112,'Matching Engine'!A$2:A$201,0))=1,"⚧","")))</f>
-        <v xml:space="preserve">♂ ♀ </v>
+        <v>♂ ♀ ⚧</v>
       </c>
       <c r="D112" s="22">
         <f>IF(A112="","",INDEX('Matching Engine'!L$2:L$201,MATCH(A112,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E112" s="22" t="str">
         <f t="shared" si="3"/>
-        <v>76% — 37 of 49 compatible</v>
+        <v>64% — 32 of 50 compatible</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Aradia Megido</v>
+        <v>Thirteen</v>
       </c>
       <c r="B113" s="22" t="str">
         <f>IF(A113="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A113,'Matching Engine'!A$2:A$201,0)))</f>
@@ -8101,7 +8176,7 @@
       </c>
       <c r="C113" s="22" t="str">
         <f>IF(A113="","",IF(AND(INDEX('Matching Engine'!F$2:F$201,MATCH(A113,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!G$2:G$201,MATCH(A113,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!H$2:H$201,MATCH(A113,'Matching Engine'!A$2:A$201,0))=0),"None",IF(INDEX('Matching Engine'!F$2:F$201,MATCH(A113,'Matching Engine'!A$2:A$201,0))=1,"♂ ","")&amp;IF(INDEX('Matching Engine'!G$2:G$201,MATCH(A113,'Matching Engine'!A$2:A$201,0))=1,"♀ ","")&amp;IF(INDEX('Matching Engine'!H$2:H$201,MATCH(A113,'Matching Engine'!A$2:A$201,0))=1,"⚧","")))</f>
-        <v>♂ ♀ ⚧</v>
+        <v xml:space="preserve">♂ ♀ </v>
       </c>
       <c r="D113" s="22">
         <f>IF(A113="","",INDEX('Matching Engine'!L$2:L$201,MATCH(A113,'Matching Engine'!A$2:A$201,0)))</f>
@@ -8109,13 +8184,13 @@
       </c>
       <c r="E113" s="22" t="str">
         <f t="shared" si="3"/>
-        <v>78% — 38 of 49 compatible</v>
+        <v>76% — 38 of 50 compatible</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Dr. Winters</v>
+        <v>Aradia Megido</v>
       </c>
       <c r="B114" s="22" t="str">
         <f>IF(A114="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A114,'Matching Engine'!A$2:A$201,0)))</f>
@@ -8127,17 +8202,17 @@
       </c>
       <c r="D114" s="22">
         <f>IF(A114="","",INDEX('Matching Engine'!L$2:L$201,MATCH(A114,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E114" s="22" t="str">
         <f t="shared" si="3"/>
-        <v>78% — 38 of 49 compatible</v>
+        <v>78% — 39 of 50 compatible</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Feferi Peixes</v>
+        <v>Dr. Winters</v>
       </c>
       <c r="B115" s="22" t="str">
         <f>IF(A115="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A115,'Matching Engine'!A$2:A$201,0)))</f>
@@ -8149,17 +8224,17 @@
       </c>
       <c r="D115" s="22">
         <f>IF(A115="","",INDEX('Matching Engine'!L$2:L$201,MATCH(A115,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E115" s="22" t="str">
         <f t="shared" si="3"/>
-        <v>78% — 38 of 49 compatible</v>
+        <v>78% — 39 of 50 compatible</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Jade Harley</v>
+        <v>Feferi Peixes</v>
       </c>
       <c r="B116" s="22" t="str">
         <f>IF(A116="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A116,'Matching Engine'!A$2:A$201,0)))</f>
@@ -8171,17 +8246,17 @@
       </c>
       <c r="D116" s="22">
         <f>IF(A116="","",INDEX('Matching Engine'!L$2:L$201,MATCH(A116,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E116" s="22" t="str">
         <f t="shared" si="3"/>
-        <v>78% — 38 of 49 compatible</v>
+        <v>78% — 39 of 50 compatible</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>June Egbert</v>
+        <v>Jade Harley</v>
       </c>
       <c r="B117" s="22" t="str">
         <f>IF(A117="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A117,'Matching Engine'!A$2:A$201,0)))</f>
@@ -8193,17 +8268,17 @@
       </c>
       <c r="D117" s="22">
         <f>IF(A117="","",INDEX('Matching Engine'!L$2:L$201,MATCH(A117,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E117" s="22" t="str">
         <f t="shared" si="3"/>
-        <v>78% — 38 of 49 compatible</v>
+        <v>78% — 39 of 50 compatible</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Nepeta Leijon</v>
+        <v>June Egbert</v>
       </c>
       <c r="B118" s="22" t="str">
         <f>IF(A118="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A118,'Matching Engine'!A$2:A$201,0)))</f>
@@ -8215,17 +8290,17 @@
       </c>
       <c r="D118" s="22">
         <f>IF(A118="","",INDEX('Matching Engine'!L$2:L$201,MATCH(A118,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E118" s="22" t="str">
         <f t="shared" si="3"/>
-        <v>78% — 38 of 49 compatible</v>
+        <v>78% — 39 of 50 compatible</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Nikki</v>
+        <v>Nepeta Leijon</v>
       </c>
       <c r="B119" s="22" t="str">
         <f>IF(A119="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A119,'Matching Engine'!A$2:A$201,0)))</f>
@@ -8237,17 +8312,17 @@
       </c>
       <c r="D119" s="22">
         <f>IF(A119="","",INDEX('Matching Engine'!L$2:L$201,MATCH(A119,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E119" s="22" t="str">
         <f t="shared" si="3"/>
-        <v>78% — 38 of 49 compatible</v>
+        <v>78% — 39 of 50 compatible</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Terezi Pyrope</v>
+        <v>Nikki</v>
       </c>
       <c r="B120" s="22" t="str">
         <f>IF(A120="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A120,'Matching Engine'!A$2:A$201,0)))</f>
@@ -8259,11 +8334,11 @@
       </c>
       <c r="D120" s="22">
         <f>IF(A120="","",INDEX('Matching Engine'!L$2:L$201,MATCH(A120,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E120" s="22" t="str">
         <f t="shared" si="3"/>
-        <v>78% — 38 of 49 compatible</v>
+        <v>78% — 39 of 50 compatible</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -9878,19 +9953,19 @@
       </c>
       <c r="M2" s="46" cm="1">
         <f t="array" ref="M2">IF(A2="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L2))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L2)*(A$2:A$201&lt;A2))+1)</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N2" s="46" cm="1">
         <f t="array" aca="1" ref="N2" ca="1">IF(A2="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I2+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J2+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K2)&gt;0)*((F2*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G2*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H2*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>0.73406432748537997</v>
+        <v>0.72799145299145307</v>
       </c>
       <c r="O2" s="46" cm="1">
         <f t="array" aca="1" ref="O2" ca="1">IF(A2="","",IF(L2=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I2+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J2+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K2)&gt;0)*((F2*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G2*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H2*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L2))</f>
-        <v>33</v>
+        <v>33.391304347826086</v>
       </c>
       <c r="P2" s="46">
         <f ca="1">IF(A2="","",IF(L2*O2&gt;0,MIN(1,L2/O2),0))</f>
-        <v>0.69696969696969702</v>
+        <v>0.68880208333333337</v>
       </c>
     </row>
     <row r="3" spans="1:16" s="31" customFormat="1" x14ac:dyDescent="0.35">
@@ -10014,15 +10089,15 @@
       </c>
       <c r="N4" s="46" cm="1">
         <f t="array" aca="1" ref="N4" ca="1">IF(A4="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I4+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J4+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K4)&gt;0)*((F4*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G4*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H4*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>0.41771528613633857</v>
+        <v>0.40523316839106321</v>
       </c>
       <c r="O4" s="46" cm="1">
         <f t="array" aca="1" ref="O4" ca="1">IF(A4="","",IF(L4=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I4+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J4+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K4)&gt;0)*((F4*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G4*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H4*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L4))</f>
-        <v>34.5</v>
+        <v>35.5</v>
       </c>
       <c r="P4" s="46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.40579710144927539</v>
+        <v>0.39436619718309857</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.35">
@@ -10076,15 +10151,15 @@
       </c>
       <c r="M5" s="46" cm="1">
         <f t="array" ref="M5">IF(A5="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L5))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L5)*(A$2:A$201&lt;A5))+1)</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N5" s="46" cm="1">
         <f t="array" aca="1" ref="N5" ca="1">IF(A5="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I5+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J5+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K5)&gt;0)*((F5*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G5*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H5*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.154616749620283</v>
+        <v>1.1421346318750076</v>
       </c>
       <c r="O5" s="46" cm="1">
         <f t="array" aca="1" ref="O5" ca="1">IF(A5="","",IF(L5=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I5+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J5+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K5)&gt;0)*((F5*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G5*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H5*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L5))</f>
-        <v>30.03125</v>
+        <v>30.46875</v>
       </c>
       <c r="P5" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -10146,15 +10221,15 @@
       </c>
       <c r="N6" s="46" cm="1">
         <f t="array" aca="1" ref="N6" ca="1">IF(A6="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I6+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J6+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K6)&gt;0)*((F6*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G6*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H6*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>0.41771528613633857</v>
+        <v>0.40523316839106321</v>
       </c>
       <c r="O6" s="46" cm="1">
         <f t="array" aca="1" ref="O6" ca="1">IF(A6="","",IF(L6=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I6+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J6+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K6)&gt;0)*((F6*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G6*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H6*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L6))</f>
-        <v>34.5</v>
+        <v>35.5</v>
       </c>
       <c r="P6" s="46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.40579710144927539</v>
+        <v>0.39436619718309857</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.35">
@@ -10208,15 +10283,15 @@
       </c>
       <c r="M7" s="46" cm="1">
         <f t="array" ref="M7">IF(A7="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L7))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L7)*(A$2:A$201&lt;A7))+1)</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N7" s="46" cm="1">
         <f t="array" aca="1" ref="N7" ca="1">IF(A7="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I7+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J7+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K7)&gt;0)*((F7*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G7*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H7*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.154616749620283</v>
+        <v>1.1421346318750076</v>
       </c>
       <c r="O7" s="46" cm="1">
         <f t="array" aca="1" ref="O7" ca="1">IF(A7="","",IF(L7=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I7+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J7+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K7)&gt;0)*((F7*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G7*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H7*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L7))</f>
-        <v>30.03125</v>
+        <v>30.46875</v>
       </c>
       <c r="P7" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -10274,7 +10349,7 @@
       </c>
       <c r="M8" s="46" cm="1">
         <f t="array" ref="M8">IF(A8="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L8))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L8)*(A$2:A$201&lt;A8))+1)</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N8" s="46" cm="1">
         <f t="array" aca="1" ref="N8" ca="1">IF(A8="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I8+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J8+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K8)&gt;0)*((F8*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G8*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H8*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
@@ -10344,15 +10419,15 @@
       </c>
       <c r="N9" s="46" cm="1">
         <f t="array" aca="1" ref="N9" ca="1">IF(A9="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I9+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J9+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K9)&gt;0)*((F9*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G9*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H9*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>0.41771528613633857</v>
+        <v>0.40523316839106321</v>
       </c>
       <c r="O9" s="46" cm="1">
         <f t="array" aca="1" ref="O9" ca="1">IF(A9="","",IF(L9=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I9+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J9+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K9)&gt;0)*((F9*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G9*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H9*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L9))</f>
-        <v>34.5</v>
+        <v>35.5</v>
       </c>
       <c r="P9" s="46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.40579710144927539</v>
+        <v>0.39436619718309857</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.35">
@@ -10402,19 +10477,19 @@
       </c>
       <c r="L10" s="46" cm="1">
         <f t="array" ref="L10">IF(A10="",0,SUMPRODUCT((A$2:A$201&lt;&gt;"")*((F$2:F$201*I10+G$2:G$201*J10+H$2:H$201*K10)&gt;0)*((F10*I$2:I$201+G10*J$2:J$201+H10*K$2:K$201)&gt;0))-IF(F10*I10+G10*J10+H10*K10&gt;0,1,0))</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M10" s="46" cm="1">
         <f t="array" ref="M10">IF(A10="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L10))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L10)*(A$2:A$201&lt;A10))+1)</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N10" s="46" cm="1">
         <f t="array" aca="1" ref="N10" ca="1">IF(A10="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I10+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J10+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K10)&gt;0)*((F10*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G10*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H10*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.3702380952380948</v>
+        <v>1.4416666666666662</v>
       </c>
       <c r="O10" s="46" cm="1">
         <f t="array" aca="1" ref="O10" ca="1">IF(A10="","",IF(L10=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I10+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J10+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K10)&gt;0)*((F10*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G10*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H10*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L10))</f>
-        <v>22.346153846153847</v>
+        <v>22.037037037037038</v>
       </c>
       <c r="P10" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -10476,15 +10551,15 @@
       </c>
       <c r="N11" s="46" cm="1">
         <f t="array" aca="1" ref="N11" ca="1">IF(A11="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I11+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J11+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K11)&gt;0)*((F11*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G11*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H11*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>0.41771528613633857</v>
+        <v>0.40523316839106321</v>
       </c>
       <c r="O11" s="46" cm="1">
         <f t="array" aca="1" ref="O11" ca="1">IF(A11="","",IF(L11=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I11+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J11+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K11)&gt;0)*((F11*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G11*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H11*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L11))</f>
-        <v>34.5</v>
+        <v>35.5</v>
       </c>
       <c r="P11" s="46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.40579710144927539</v>
+        <v>0.39436619718309857</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.35">
@@ -10542,15 +10617,15 @@
       </c>
       <c r="N12" s="46" cm="1">
         <f t="array" aca="1" ref="N12" ca="1">IF(A12="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I12+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J12+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K12)&gt;0)*((F12*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G12*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H12*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>0.41771528613633857</v>
+        <v>0.40523316839106321</v>
       </c>
       <c r="O12" s="46" cm="1">
         <f t="array" aca="1" ref="O12" ca="1">IF(A12="","",IF(L12=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I12+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J12+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K12)&gt;0)*((F12*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G12*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H12*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L12))</f>
-        <v>34.5</v>
+        <v>35.5</v>
       </c>
       <c r="P12" s="46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.40579710144927539</v>
+        <v>0.39436619718309857</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.35">
@@ -10600,19 +10675,19 @@
       </c>
       <c r="L13" s="46" cm="1">
         <f t="array" ref="L13">IF(A13="",0,SUMPRODUCT((A$2:A$201&lt;&gt;"")*((F$2:F$201*I13+G$2:G$201*J13+H$2:H$201*K13)&gt;0)*((F13*I$2:I$201+G13*J$2:J$201+H13*K$2:K$201)&gt;0))-IF(F13*I13+G13*J13+H13*K13&gt;0,1,0))</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M13" s="46" cm="1">
         <f t="array" ref="M13">IF(A13="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L13))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L13)*(A$2:A$201&lt;A13))+1)</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N13" s="46" cm="1">
         <f t="array" aca="1" ref="N13" ca="1">IF(A13="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I13+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J13+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K13)&gt;0)*((F13*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G13*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H13*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.3702380952380948</v>
+        <v>1.4416666666666662</v>
       </c>
       <c r="O13" s="46" cm="1">
         <f t="array" aca="1" ref="O13" ca="1">IF(A13="","",IF(L13=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I13+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J13+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K13)&gt;0)*((F13*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G13*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H13*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L13))</f>
-        <v>22.346153846153847</v>
+        <v>22.037037037037038</v>
       </c>
       <c r="P13" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -10670,7 +10745,7 @@
       </c>
       <c r="M14" s="46" cm="1">
         <f t="array" ref="M14">IF(A14="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L14))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L14)*(A$2:A$201&lt;A14))+1)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N14" s="46" cm="1">
         <f t="array" aca="1" ref="N14" ca="1">IF(A14="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I14+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J14+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K14)&gt;0)*((F14*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G14*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H14*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
@@ -10736,7 +10811,7 @@
       </c>
       <c r="M15" s="46" cm="1">
         <f t="array" ref="M15">IF(A15="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L15))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L15)*(A$2:A$201&lt;A15))+1)</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N15" s="46" cm="1">
         <f t="array" aca="1" ref="N15" ca="1">IF(A15="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I15+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J15+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K15)&gt;0)*((F15*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G15*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H15*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
@@ -10798,19 +10873,19 @@
       </c>
       <c r="L16" s="46" cm="1">
         <f t="array" ref="L16">IF(A16="",0,SUMPRODUCT((A$2:A$201&lt;&gt;"")*((F$2:F$201*I16+G$2:G$201*J16+H$2:H$201*K16)&gt;0)*((F16*I$2:I$201+G16*J$2:J$201+H16*K$2:K$201)&gt;0))-IF(F16*I16+G16*J16+H16*K16&gt;0,1,0))</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M16" s="46" cm="1">
         <f t="array" ref="M16">IF(A16="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L16))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L16)*(A$2:A$201&lt;A16))+1)</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N16" s="46" cm="1">
         <f t="array" aca="1" ref="N16" ca="1">IF(A16="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I16+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J16+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K16)&gt;0)*((F16*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G16*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H16*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.3702380952380948</v>
+        <v>1.4416666666666662</v>
       </c>
       <c r="O16" s="46" cm="1">
         <f t="array" aca="1" ref="O16" ca="1">IF(A16="","",IF(L16=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I16+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J16+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K16)&gt;0)*((F16*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G16*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H16*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L16))</f>
-        <v>22.346153846153847</v>
+        <v>22.037037037037038</v>
       </c>
       <c r="P16" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -10864,19 +10939,19 @@
       </c>
       <c r="L17" s="46" cm="1">
         <f t="array" ref="L17">IF(A17="",0,SUMPRODUCT((A$2:A$201&lt;&gt;"")*((F$2:F$201*I17+G$2:G$201*J17+H$2:H$201*K17)&gt;0)*((F17*I$2:I$201+G17*J$2:J$201+H17*K$2:K$201)&gt;0))-IF(F17*I17+G17*J17+H17*K17&gt;0,1,0))</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M17" s="46" cm="1">
         <f t="array" ref="M17">IF(A17="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L17))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L17)*(A$2:A$201&lt;A17))+1)</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N17" s="46" cm="1">
         <f t="array" aca="1" ref="N17" ca="1">IF(A17="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I17+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J17+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K17)&gt;0)*((F17*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G17*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H17*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.3702380952380948</v>
+        <v>1.4416666666666662</v>
       </c>
       <c r="O17" s="46" cm="1">
         <f t="array" aca="1" ref="O17" ca="1">IF(A17="","",IF(L17=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I17+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J17+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K17)&gt;0)*((F17*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G17*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H17*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L17))</f>
-        <v>22.346153846153847</v>
+        <v>22.037037037037038</v>
       </c>
       <c r="P17" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -10934,15 +11009,15 @@
       </c>
       <c r="M18" s="46" cm="1">
         <f t="array" ref="M18">IF(A18="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L18))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L18)*(A$2:A$201&lt;A18))+1)</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N18" s="46" cm="1">
         <f t="array" aca="1" ref="N18" ca="1">IF(A18="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I18+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J18+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K18)&gt;0)*((F18*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G18*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H18*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.154616749620283</v>
+        <v>1.1421346318750076</v>
       </c>
       <c r="O18" s="46" cm="1">
         <f t="array" aca="1" ref="O18" ca="1">IF(A18="","",IF(L18=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I18+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J18+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K18)&gt;0)*((F18*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G18*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H18*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L18))</f>
-        <v>30.03125</v>
+        <v>30.46875</v>
       </c>
       <c r="P18" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -11004,15 +11079,15 @@
       </c>
       <c r="N19" s="46" cm="1">
         <f t="array" aca="1" ref="N19" ca="1">IF(A19="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I19+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J19+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K19)&gt;0)*((F19*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G19*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H19*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>0.41771528613633857</v>
+        <v>0.40523316839106321</v>
       </c>
       <c r="O19" s="46" cm="1">
         <f t="array" aca="1" ref="O19" ca="1">IF(A19="","",IF(L19=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I19+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J19+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K19)&gt;0)*((F19*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G19*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H19*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L19))</f>
-        <v>34.5</v>
+        <v>35.5</v>
       </c>
       <c r="P19" s="46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.40579710144927539</v>
+        <v>0.39436619718309857</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.35">
@@ -11062,19 +11137,19 @@
       </c>
       <c r="L20" s="46" cm="1">
         <f t="array" ref="L20">IF(A20="",0,SUMPRODUCT((A$2:A$201&lt;&gt;"")*((F$2:F$201*I20+G$2:G$201*J20+H$2:H$201*K20)&gt;0)*((F20*I$2:I$201+G20*J$2:J$201+H20*K$2:K$201)&gt;0))-IF(F20*I20+G20*J20+H20*K20&gt;0,1,0))</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M20" s="46" cm="1">
         <f t="array" ref="M20">IF(A20="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L20))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L20)*(A$2:A$201&lt;A20))+1)</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N20" s="46" cm="1">
         <f t="array" aca="1" ref="N20" ca="1">IF(A20="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I20+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J20+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K20)&gt;0)*((F20*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G20*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H20*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.7888983823194351</v>
+        <v>1.8542540792540783</v>
       </c>
       <c r="O20" s="46" cm="1">
         <f t="array" aca="1" ref="O20" ca="1">IF(A20="","",IF(L20=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I20+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J20+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K20)&gt;0)*((F20*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G20*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H20*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L20))</f>
-        <v>25.54054054054054</v>
+        <v>25.473684210526315</v>
       </c>
       <c r="P20" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -11136,15 +11211,15 @@
       </c>
       <c r="N21" s="46" cm="1">
         <f t="array" aca="1" ref="N21" ca="1">IF(A21="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I21+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J21+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K21)&gt;0)*((F21*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G21*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H21*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>0.41771528613633857</v>
+        <v>0.40523316839106321</v>
       </c>
       <c r="O21" s="46" cm="1">
         <f t="array" aca="1" ref="O21" ca="1">IF(A21="","",IF(L21=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I21+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J21+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K21)&gt;0)*((F21*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G21*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H21*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L21))</f>
-        <v>34.5</v>
+        <v>35.5</v>
       </c>
       <c r="P21" s="46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.40579710144927539</v>
+        <v>0.39436619718309857</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.35">
@@ -11202,15 +11277,15 @@
       </c>
       <c r="N22" s="46" cm="1">
         <f t="array" aca="1" ref="N22" ca="1">IF(A22="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I22+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J22+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K22)&gt;0)*((F22*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G22*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H22*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>0.41771528613633857</v>
+        <v>0.40523316839106321</v>
       </c>
       <c r="O22" s="46" cm="1">
         <f t="array" aca="1" ref="O22" ca="1">IF(A22="","",IF(L22=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I22+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J22+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K22)&gt;0)*((F22*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G22*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H22*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L22))</f>
-        <v>34.5</v>
+        <v>35.5</v>
       </c>
       <c r="P22" s="46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.40579710144927539</v>
+        <v>0.39436619718309857</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.35">
@@ -11260,19 +11335,19 @@
       </c>
       <c r="L23" s="46" cm="1">
         <f t="array" ref="L23">IF(A23="",0,SUMPRODUCT((A$2:A$201&lt;&gt;"")*((F$2:F$201*I23+G$2:G$201*J23+H$2:H$201*K23)&gt;0)*((F23*I$2:I$201+G23*J$2:J$201+H23*K$2:K$201)&gt;0))-IF(F23*I23+G23*J23+H23*K23&gt;0,1,0))</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M23" s="46" cm="1">
         <f t="array" ref="M23">IF(A23="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L23))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L23)*(A$2:A$201&lt;A23))+1)</f>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N23" s="46" cm="1">
         <f t="array" aca="1" ref="N23" ca="1">IF(A23="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I23+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J23+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K23)&gt;0)*((F23*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G23*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H23*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.8330878807423432</v>
+        <v>1.898407103956302</v>
       </c>
       <c r="O23" s="46" cm="1">
         <f t="array" aca="1" ref="O23" ca="1">IF(A23="","",IF(L23=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I23+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J23+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K23)&gt;0)*((F23*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G23*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H23*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L23))</f>
-        <v>25.44736842105263</v>
+        <v>25.384615384615383</v>
       </c>
       <c r="P23" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -11334,15 +11409,15 @@
       </c>
       <c r="N24" s="46" cm="1">
         <f t="array" aca="1" ref="N24" ca="1">IF(A24="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I24+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J24+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K24)&gt;0)*((F24*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G24*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H24*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>0.35477822319927577</v>
+        <v>0.34799411115200596</v>
       </c>
       <c r="O24" s="46" cm="1">
         <f t="array" aca="1" ref="O24" ca="1">IF(A24="","",IF(L24=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I24+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J24+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K24)&gt;0)*((F24*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G24*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H24*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L24))</f>
-        <v>35.454545454545453</v>
+        <v>36.363636363636367</v>
       </c>
       <c r="P24" s="46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.31025641025641026</v>
+        <v>0.30249999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.35">
@@ -11392,19 +11467,19 @@
       </c>
       <c r="L25" s="46" cm="1">
         <f t="array" ref="L25">IF(A25="",0,SUMPRODUCT((A$2:A$201&lt;&gt;"")*((F$2:F$201*I25+G$2:G$201*J25+H$2:H$201*K25)&gt;0)*((F25*I$2:I$201+G25*J$2:J$201+H25*K$2:K$201)&gt;0))-IF(F25*I25+G25*J25+H25*K25&gt;0,1,0))</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M25" s="46" cm="1">
         <f t="array" ref="M25">IF(A25="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L25))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L25)*(A$2:A$201&lt;A25))+1)</f>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N25" s="46" cm="1">
         <f t="array" aca="1" ref="N25" ca="1">IF(A25="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I25+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J25+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K25)&gt;0)*((F25*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G25*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H25*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.8330878807423432</v>
+        <v>1.898407103956302</v>
       </c>
       <c r="O25" s="46" cm="1">
         <f t="array" aca="1" ref="O25" ca="1">IF(A25="","",IF(L25=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I25+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J25+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K25)&gt;0)*((F25*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G25*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H25*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L25))</f>
-        <v>25.44736842105263</v>
+        <v>25.384615384615383</v>
       </c>
       <c r="P25" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -11462,15 +11537,15 @@
       </c>
       <c r="M26" s="46" cm="1">
         <f t="array" ref="M26">IF(A26="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L26))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L26)*(A$2:A$201&lt;A26))+1)</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N26" s="46" cm="1">
         <f t="array" aca="1" ref="N26" ca="1">IF(A26="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I26+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J26+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K26)&gt;0)*((F26*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G26*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H26*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.154616749620283</v>
+        <v>1.1421346318750076</v>
       </c>
       <c r="O26" s="46" cm="1">
         <f t="array" aca="1" ref="O26" ca="1">IF(A26="","",IF(L26=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I26+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J26+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K26)&gt;0)*((F26*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G26*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H26*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L26))</f>
-        <v>30.03125</v>
+        <v>30.46875</v>
       </c>
       <c r="P26" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -11532,15 +11607,15 @@
       </c>
       <c r="N27" s="46" cm="1">
         <f t="array" aca="1" ref="N27" ca="1">IF(A27="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I27+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J27+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K27)&gt;0)*((F27*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G27*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H27*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>0.41771528613633857</v>
+        <v>0.40523316839106321</v>
       </c>
       <c r="O27" s="46" cm="1">
         <f t="array" aca="1" ref="O27" ca="1">IF(A27="","",IF(L27=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I27+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J27+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K27)&gt;0)*((F27*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G27*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H27*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L27))</f>
-        <v>34.5</v>
+        <v>35.5</v>
       </c>
       <c r="P27" s="46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.40579710144927539</v>
+        <v>0.39436619718309857</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.35">
@@ -11598,15 +11673,15 @@
       </c>
       <c r="N28" s="46" cm="1">
         <f t="array" aca="1" ref="N28" ca="1">IF(A28="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I28+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J28+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K28)&gt;0)*((F28*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G28*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H28*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>0.41771528613633857</v>
+        <v>0.40523316839106321</v>
       </c>
       <c r="O28" s="46" cm="1">
         <f t="array" aca="1" ref="O28" ca="1">IF(A28="","",IF(L28=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I28+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J28+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K28)&gt;0)*((F28*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G28*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H28*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L28))</f>
-        <v>34.5</v>
+        <v>35.5</v>
       </c>
       <c r="P28" s="46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.40579710144927539</v>
+        <v>0.39436619718309857</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.35">
@@ -11660,19 +11735,19 @@
       </c>
       <c r="M29" s="46" cm="1">
         <f t="array" ref="M29">IF(A29="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L29))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L29)*(A$2:A$201&lt;A29))+1)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N29" s="46" cm="1">
         <f t="array" aca="1" ref="N29" ca="1">IF(A29="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I29+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J29+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K29)&gt;0)*((F29*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G29*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H29*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>0.46119354700590376</v>
+        <v>0.44871142926062846</v>
       </c>
       <c r="O29" s="46" cm="1">
         <f t="array" aca="1" ref="O29" ca="1">IF(A29="","",IF(L29=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I29+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J29+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K29)&gt;0)*((F29*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G29*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H29*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L29))</f>
-        <v>33.733333333333334</v>
+        <v>34.666666666666664</v>
       </c>
       <c r="P29" s="46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.44466403162055335</v>
+        <v>0.43269230769230771</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.35">
@@ -11730,15 +11805,15 @@
       </c>
       <c r="N30" s="46" cm="1">
         <f t="array" aca="1" ref="N30" ca="1">IF(A30="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I30+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J30+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K30)&gt;0)*((F30*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G30*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H30*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>0.41771528613633857</v>
+        <v>0.40523316839106321</v>
       </c>
       <c r="O30" s="46" cm="1">
         <f t="array" aca="1" ref="O30" ca="1">IF(A30="","",IF(L30=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I30+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J30+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K30)&gt;0)*((F30*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G30*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H30*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L30))</f>
-        <v>34.5</v>
+        <v>35.5</v>
       </c>
       <c r="P30" s="46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.40579710144927539</v>
+        <v>0.39436619718309857</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.35">
@@ -11792,7 +11867,7 @@
       </c>
       <c r="M31" s="46" cm="1">
         <f t="array" ref="M31">IF(A31="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L31))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L31)*(A$2:A$201&lt;A31))+1)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N31" s="46" cm="1">
         <f t="array" aca="1" ref="N31" ca="1">IF(A31="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I31+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J31+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K31)&gt;0)*((F31*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G31*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H31*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
@@ -11858,7 +11933,7 @@
       </c>
       <c r="M32" s="46" cm="1">
         <f t="array" ref="M32">IF(A32="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L32))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L32)*(A$2:A$201&lt;A32))+1)</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N32" s="46" cm="1">
         <f t="array" aca="1" ref="N32" ca="1">IF(A32="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I32+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J32+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K32)&gt;0)*((F32*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G32*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H32*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
@@ -11924,15 +11999,15 @@
       </c>
       <c r="M33" s="46" cm="1">
         <f t="array" ref="M33">IF(A33="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L33))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L33)*(A$2:A$201&lt;A33))+1)</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N33" s="46" cm="1">
         <f t="array" aca="1" ref="N33" ca="1">IF(A33="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I33+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J33+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K33)&gt;0)*((F33*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G33*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H33*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.154616749620283</v>
+        <v>1.1421346318750076</v>
       </c>
       <c r="O33" s="46" cm="1">
         <f t="array" aca="1" ref="O33" ca="1">IF(A33="","",IF(L33=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I33+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J33+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K33)&gt;0)*((F33*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G33*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H33*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L33))</f>
-        <v>30.03125</v>
+        <v>30.46875</v>
       </c>
       <c r="P33" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -11990,15 +12065,15 @@
       </c>
       <c r="M34" s="46" cm="1">
         <f t="array" ref="M34">IF(A34="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L34))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L34)*(A$2:A$201&lt;A34))+1)</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N34" s="46" cm="1">
         <f t="array" aca="1" ref="N34" ca="1">IF(A34="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I34+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J34+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K34)&gt;0)*((F34*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G34*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H34*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.154616749620283</v>
+        <v>1.1421346318750076</v>
       </c>
       <c r="O34" s="46" cm="1">
         <f t="array" aca="1" ref="O34" ca="1">IF(A34="","",IF(L34=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I34+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J34+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K34)&gt;0)*((F34*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G34*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H34*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L34))</f>
-        <v>30.03125</v>
+        <v>30.46875</v>
       </c>
       <c r="P34" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -12052,19 +12127,19 @@
       </c>
       <c r="L35" s="46" cm="1">
         <f t="array" ref="L35">IF(A35="",0,SUMPRODUCT((A$2:A$201&lt;&gt;"")*((F$2:F$201*I35+G$2:G$201*J35+H$2:H$201*K35)&gt;0)*((F35*I$2:I$201+G35*J$2:J$201+H35*K$2:K$201)&gt;0))-IF(F35*I35+G35*J35+H35*K35&gt;0,1,0))</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M35" s="46" cm="1">
         <f t="array" ref="M35">IF(A35="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L35))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L35)*(A$2:A$201&lt;A35))+1)</f>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N35" s="46" cm="1">
         <f t="array" aca="1" ref="N35" ca="1">IF(A35="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I35+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J35+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K35)&gt;0)*((F35*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G35*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H35*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.8330878807423432</v>
+        <v>1.8984071039563022</v>
       </c>
       <c r="O35" s="46" cm="1">
         <f t="array" aca="1" ref="O35" ca="1">IF(A35="","",IF(L35=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I35+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J35+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K35)&gt;0)*((F35*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G35*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H35*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L35))</f>
-        <v>25.44736842105263</v>
+        <v>25.384615384615383</v>
       </c>
       <c r="P35" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -12118,19 +12193,19 @@
       </c>
       <c r="L36" s="46" cm="1">
         <f t="array" ref="L36">IF(A36="",0,SUMPRODUCT((A$2:A$201&lt;&gt;"")*((F$2:F$201*I36+G$2:G$201*J36+H$2:H$201*K36)&gt;0)*((F36*I$2:I$201+G36*J$2:J$201+H36*K$2:K$201)&gt;0))-IF(F36*I36+G36*J36+H36*K36&gt;0,1,0))</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M36" s="46" cm="1">
         <f t="array" ref="M36">IF(A36="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L36))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L36)*(A$2:A$201&lt;A36))+1)</f>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N36" s="46" cm="1">
         <f t="array" aca="1" ref="N36" ca="1">IF(A36="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I36+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J36+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K36)&gt;0)*((F36*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G36*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H36*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.8330878807423432</v>
+        <v>1.8984071039563022</v>
       </c>
       <c r="O36" s="46" cm="1">
         <f t="array" aca="1" ref="O36" ca="1">IF(A36="","",IF(L36=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I36+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J36+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K36)&gt;0)*((F36*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G36*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H36*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L36))</f>
-        <v>25.44736842105263</v>
+        <v>25.384615384615383</v>
       </c>
       <c r="P36" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -12192,15 +12267,15 @@
       </c>
       <c r="N37" s="46" cm="1">
         <f t="array" aca="1" ref="N37" ca="1">IF(A37="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I37+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J37+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K37)&gt;0)*((F37*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G37*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H37*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>0.41771528613633857</v>
+        <v>0.40523316839106321</v>
       </c>
       <c r="O37" s="46" cm="1">
         <f t="array" aca="1" ref="O37" ca="1">IF(A37="","",IF(L37=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I37+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J37+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K37)&gt;0)*((F37*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G37*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H37*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L37))</f>
-        <v>34.5</v>
+        <v>35.5</v>
       </c>
       <c r="P37" s="46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.40579710144927539</v>
+        <v>0.39436619718309857</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.35">
@@ -12254,19 +12329,19 @@
       </c>
       <c r="M38" s="46" cm="1">
         <f t="array" ref="M38">IF(A38="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L38))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L38)*(A$2:A$201&lt;A38))+1)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N38" s="46" cm="1">
         <f t="array" aca="1" ref="N38" ca="1">IF(A38="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I38+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J38+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K38)&gt;0)*((F38*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G38*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H38*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>0.41771528613633857</v>
+        <v>0.40523316839106321</v>
       </c>
       <c r="O38" s="46" cm="1">
         <f t="array" aca="1" ref="O38" ca="1">IF(A38="","",IF(L38=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I38+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J38+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K38)&gt;0)*((F38*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G38*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H38*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L38))</f>
-        <v>34.5</v>
+        <v>35.5</v>
       </c>
       <c r="P38" s="46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.40579710144927539</v>
+        <v>0.39436619718309857</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.35">
@@ -12316,19 +12391,19 @@
       </c>
       <c r="L39" s="46" cm="1">
         <f t="array" ref="L39">IF(A39="",0,SUMPRODUCT((A$2:A$201&lt;&gt;"")*((F$2:F$201*I39+G$2:G$201*J39+H$2:H$201*K39)&gt;0)*((F39*I$2:I$201+G39*J$2:J$201+H39*K$2:K$201)&gt;0))-IF(F39*I39+G39*J39+H39*K39&gt;0,1,0))</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M39" s="46" cm="1">
         <f t="array" ref="M39">IF(A39="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L39))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L39)*(A$2:A$201&lt;A39))+1)</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N39" s="46" cm="1">
         <f t="array" aca="1" ref="N39" ca="1">IF(A39="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I39+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J39+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K39)&gt;0)*((F39*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G39*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H39*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.8330878807423432</v>
+        <v>1.8984071039563022</v>
       </c>
       <c r="O39" s="46" cm="1">
         <f t="array" aca="1" ref="O39" ca="1">IF(A39="","",IF(L39=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I39+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J39+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K39)&gt;0)*((F39*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G39*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H39*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L39))</f>
-        <v>25.44736842105263</v>
+        <v>25.384615384615383</v>
       </c>
       <c r="P39" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -12386,15 +12461,15 @@
       </c>
       <c r="M40" s="46" cm="1">
         <f t="array" ref="M40">IF(A40="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L40))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L40)*(A$2:A$201&lt;A40))+1)</f>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N40" s="46" cm="1">
         <f t="array" aca="1" ref="N40" ca="1">IF(A40="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I40+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J40+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K40)&gt;0)*((F40*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G40*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H40*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.154616749620283</v>
+        <v>1.1421346318750076</v>
       </c>
       <c r="O40" s="46" cm="1">
         <f t="array" aca="1" ref="O40" ca="1">IF(A40="","",IF(L40=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I40+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J40+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K40)&gt;0)*((F40*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G40*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H40*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L40))</f>
-        <v>30.03125</v>
+        <v>30.46875</v>
       </c>
       <c r="P40" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -12452,15 +12527,15 @@
       </c>
       <c r="M41" s="46" cm="1">
         <f t="array" ref="M41">IF(A41="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L41))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L41)*(A$2:A$201&lt;A41))+1)</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N41" s="46" cm="1">
         <f t="array" aca="1" ref="N41" ca="1">IF(A41="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I41+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J41+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K41)&gt;0)*((F41*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G41*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H41*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.154616749620283</v>
+        <v>1.1421346318750076</v>
       </c>
       <c r="O41" s="46" cm="1">
         <f t="array" aca="1" ref="O41" ca="1">IF(A41="","",IF(L41=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I41+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J41+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K41)&gt;0)*((F41*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G41*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H41*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L41))</f>
-        <v>30.03125</v>
+        <v>30.46875</v>
       </c>
       <c r="P41" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -12518,15 +12593,15 @@
       </c>
       <c r="M42" s="46" cm="1">
         <f t="array" ref="M42">IF(A42="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L42))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L42)*(A$2:A$201&lt;A42))+1)</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N42" s="46" cm="1">
         <f t="array" aca="1" ref="N42" ca="1">IF(A42="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I42+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J42+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K42)&gt;0)*((F42*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G42*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H42*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.154616749620283</v>
+        <v>1.1421346318750076</v>
       </c>
       <c r="O42" s="46" cm="1">
         <f t="array" aca="1" ref="O42" ca="1">IF(A42="","",IF(L42=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I42+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J42+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K42)&gt;0)*((F42*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G42*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H42*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L42))</f>
-        <v>30.03125</v>
+        <v>30.46875</v>
       </c>
       <c r="P42" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -12580,19 +12655,19 @@
       </c>
       <c r="L43" s="46" cm="1">
         <f t="array" ref="L43">IF(A43="",0,SUMPRODUCT((A$2:A$201&lt;&gt;"")*((F$2:F$201*I43+G$2:G$201*J43+H$2:H$201*K43)&gt;0)*((F43*I$2:I$201+G43*J$2:J$201+H43*K$2:K$201)&gt;0))-IF(F43*I43+G43*J43+H43*K43&gt;0,1,0))</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M43" s="46" cm="1">
         <f t="array" ref="M43">IF(A43="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L43))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L43)*(A$2:A$201&lt;A43))+1)</f>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N43" s="46" cm="1">
         <f t="array" aca="1" ref="N43" ca="1">IF(A43="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I43+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J43+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K43)&gt;0)*((F43*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G43*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H43*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.8330878807423432</v>
+        <v>1.8984071039563022</v>
       </c>
       <c r="O43" s="46" cm="1">
         <f t="array" aca="1" ref="O43" ca="1">IF(A43="","",IF(L43=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I43+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J43+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K43)&gt;0)*((F43*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G43*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H43*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L43))</f>
-        <v>25.44736842105263</v>
+        <v>25.384615384615383</v>
       </c>
       <c r="P43" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -12654,15 +12729,15 @@
       </c>
       <c r="N44" s="46" cm="1">
         <f t="array" aca="1" ref="N44" ca="1">IF(A44="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I44+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J44+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K44)&gt;0)*((F44*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G44*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H44*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>0.35477822319927577</v>
+        <v>0.3479941111520059</v>
       </c>
       <c r="O44" s="46" cm="1">
         <f t="array" aca="1" ref="O44" ca="1">IF(A44="","",IF(L44=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I44+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J44+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K44)&gt;0)*((F44*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G44*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H44*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L44))</f>
-        <v>35.454545454545453</v>
+        <v>36.363636363636367</v>
       </c>
       <c r="P44" s="46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.31025641025641026</v>
+        <v>0.30249999999999999</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.35">
@@ -12712,19 +12787,19 @@
       </c>
       <c r="L45" s="46" cm="1">
         <f t="array" ref="L45">IF(A45="",0,SUMPRODUCT((A$2:A$201&lt;&gt;"")*((F$2:F$201*I45+G$2:G$201*J45+H$2:H$201*K45)&gt;0)*((F45*I$2:I$201+G45*J$2:J$201+H45*K$2:K$201)&gt;0))-IF(F45*I45+G45*J45+H45*K45&gt;0,1,0))</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M45" s="46" cm="1">
         <f t="array" ref="M45">IF(A45="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L45))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L45)*(A$2:A$201&lt;A45))+1)</f>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N45" s="46" cm="1">
         <f t="array" aca="1" ref="N45" ca="1">IF(A45="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I45+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J45+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K45)&gt;0)*((F45*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G45*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H45*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.8330878807423432</v>
+        <v>1.8984071039563022</v>
       </c>
       <c r="O45" s="46" cm="1">
         <f t="array" aca="1" ref="O45" ca="1">IF(A45="","",IF(L45=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I45+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J45+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K45)&gt;0)*((F45*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G45*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H45*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L45))</f>
-        <v>25.44736842105263</v>
+        <v>25.384615384615383</v>
       </c>
       <c r="P45" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -12778,19 +12853,19 @@
       </c>
       <c r="L46" s="46" cm="1">
         <f t="array" ref="L46">IF(A46="",0,SUMPRODUCT((A$2:A$201&lt;&gt;"")*((F$2:F$201*I46+G$2:G$201*J46+H$2:H$201*K46)&gt;0)*((F46*I$2:I$201+G46*J$2:J$201+H46*K$2:K$201)&gt;0))-IF(F46*I46+G46*J46+H46*K46&gt;0,1,0))</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M46" s="46" cm="1">
         <f t="array" ref="M46">IF(A46="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L46))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L46)*(A$2:A$201&lt;A46))+1)</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N46" s="46" cm="1">
         <f t="array" aca="1" ref="N46" ca="1">IF(A46="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I46+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J46+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K46)&gt;0)*((F46*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G46*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H46*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.8330878807423432</v>
+        <v>1.8984071039563022</v>
       </c>
       <c r="O46" s="46" cm="1">
         <f t="array" aca="1" ref="O46" ca="1">IF(A46="","",IF(L46=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I46+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J46+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K46)&gt;0)*((F46*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G46*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H46*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L46))</f>
-        <v>25.44736842105263</v>
+        <v>25.384615384615383</v>
       </c>
       <c r="P46" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -12848,15 +12923,15 @@
       </c>
       <c r="M47" s="46" cm="1">
         <f t="array" ref="M47">IF(A47="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L47))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L47)*(A$2:A$201&lt;A47))+1)</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N47" s="46" cm="1">
         <f t="array" aca="1" ref="N47" ca="1">IF(A47="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I47+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J47+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K47)&gt;0)*((F47*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G47*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H47*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.154616749620283</v>
+        <v>1.1421346318750076</v>
       </c>
       <c r="O47" s="46" cm="1">
         <f t="array" aca="1" ref="O47" ca="1">IF(A47="","",IF(L47=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I47+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J47+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K47)&gt;0)*((F47*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G47*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H47*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L47))</f>
-        <v>30.03125</v>
+        <v>30.46875</v>
       </c>
       <c r="P47" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -12914,15 +12989,15 @@
       </c>
       <c r="M48" s="46" cm="1">
         <f t="array" ref="M48">IF(A48="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L48))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L48)*(A$2:A$201&lt;A48))+1)</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N48" s="46" cm="1">
         <f t="array" aca="1" ref="N48" ca="1">IF(A48="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I48+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J48+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K48)&gt;0)*((F48*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G48*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H48*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.154616749620283</v>
+        <v>1.1421346318750076</v>
       </c>
       <c r="O48" s="46" cm="1">
         <f t="array" aca="1" ref="O48" ca="1">IF(A48="","",IF(L48=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I48+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J48+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K48)&gt;0)*((F48*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G48*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H48*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L48))</f>
-        <v>30.03125</v>
+        <v>30.46875</v>
       </c>
       <c r="P48" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -12980,15 +13055,15 @@
       </c>
       <c r="M49" s="46" cm="1">
         <f t="array" ref="M49">IF(A49="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L49))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L49)*(A$2:A$201&lt;A49))+1)</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N49" s="46" cm="1">
         <f t="array" aca="1" ref="N49" ca="1">IF(A49="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I49+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J49+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K49)&gt;0)*((F49*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G49*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H49*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.154616749620283</v>
+        <v>1.1421346318750076</v>
       </c>
       <c r="O49" s="46" cm="1">
         <f t="array" aca="1" ref="O49" ca="1">IF(A49="","",IF(L49=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I49+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J49+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K49)&gt;0)*((F49*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G49*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H49*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L49))</f>
-        <v>30.03125</v>
+        <v>30.46875</v>
       </c>
       <c r="P49" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -13042,19 +13117,19 @@
       </c>
       <c r="L50" s="46" cm="1">
         <f t="array" ref="L50">IF(A50="",0,SUMPRODUCT((A$2:A$201&lt;&gt;"")*((F$2:F$201*I50+G$2:G$201*J50+H$2:H$201*K50)&gt;0)*((F50*I$2:I$201+G50*J$2:J$201+H50*K$2:K$201)&gt;0))-IF(F50*I50+G50*J50+H50*K50&gt;0,1,0))</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M50" s="46" cm="1">
         <f t="array" ref="M50">IF(A50="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L50))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L50)*(A$2:A$201&lt;A50))+1)</f>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N50" s="46" cm="1">
         <f t="array" aca="1" ref="N50" ca="1">IF(A50="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I50+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J50+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K50)&gt;0)*((F50*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G50*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H50*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.8330878807423432</v>
+        <v>1.8984071039563022</v>
       </c>
       <c r="O50" s="46" cm="1">
         <f t="array" aca="1" ref="O50" ca="1">IF(A50="","",IF(L50=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I50+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J50+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K50)&gt;0)*((F50*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G50*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H50*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L50))</f>
-        <v>25.44736842105263</v>
+        <v>25.384615384615383</v>
       </c>
       <c r="P50" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -13112,7 +13187,7 @@
       </c>
       <c r="M51" s="46" cm="1">
         <f t="array" ref="M51">IF(A51="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L51))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L51)*(A$2:A$201&lt;A51))+1)</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N51" s="46" cm="1">
         <f t="array" aca="1" ref="N51" ca="1">IF(A51="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I51+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J51+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K51)&gt;0)*((F51*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G51*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H51*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
@@ -13130,23 +13205,23 @@
     <row r="52" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A52" s="46" t="str" cm="1">
         <f t="array" ref="A52">IF(ROW()-1&gt;COUNTA('Mii List'!A$2:A$200),"",INDEX('Mii List'!A$2:A$200,ROW()-1))</f>
-        <v/>
+        <v>Wayward Vagabond</v>
       </c>
       <c r="B52" s="46" t="str">
         <f>IF(A52="","",INDEX('Mii List'!B$2:B$200,MATCH(A52,'Mii List'!A$2:A$200,0)))</f>
-        <v/>
+        <v>Male</v>
       </c>
       <c r="C52" s="46" t="str">
         <f>IF(A52="","",INDEX('Mii List'!C$2:C$200,MATCH(A52,'Mii List'!A$2:A$200,0)))</f>
-        <v/>
+        <v>✗</v>
       </c>
       <c r="D52" s="46" t="str">
         <f>IF(A52="","",INDEX('Mii List'!D$2:D$200,MATCH(A52,'Mii List'!A$2:A$200,0)))</f>
-        <v/>
+        <v>✓</v>
       </c>
       <c r="E52" s="46" t="str">
         <f>IF(A52="","",INDEX('Mii List'!E$2:E$200,MATCH(A52,'Mii List'!A$2:A$200,0)))</f>
-        <v/>
+        <v>✗</v>
       </c>
       <c r="F52" s="46">
         <f t="shared" si="0"/>
@@ -13154,7 +13229,7 @@
       </c>
       <c r="G52" s="46">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H52" s="46">
         <f t="shared" si="2"/>
@@ -13162,7 +13237,7 @@
       </c>
       <c r="I52" s="46">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" s="46">
         <f t="shared" si="4"/>
@@ -13174,23 +13249,23 @@
       </c>
       <c r="L52" s="46" cm="1">
         <f t="array" ref="L52">IF(A52="",0,SUMPRODUCT((A$2:A$201&lt;&gt;"")*((F$2:F$201*I52+G$2:G$201*J52+H$2:H$201*K52)&gt;0)*((F52*I$2:I$201+G52*J$2:J$201+H52*K$2:K$201)&gt;0))-IF(F52*I52+G52*J52+H52*K52&gt;0,1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="M52" s="46" t="str" cm="1">
+        <v>14</v>
+      </c>
+      <c r="M52" s="46" cm="1">
         <f t="array" ref="M52">IF(A52="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L52))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L52)*(A$2:A$201&lt;A52))+1)</f>
-        <v/>
-      </c>
-      <c r="N52" s="46" t="str" cm="1">
+        <v>16</v>
+      </c>
+      <c r="N52" s="46" cm="1">
         <f t="array" aca="1" ref="N52" ca="1">IF(A52="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I52+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J52+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K52)&gt;0)*((F52*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G52*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H52*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v/>
-      </c>
-      <c r="O52" s="46" t="str" cm="1">
+        <v>0.40523316839106321</v>
+      </c>
+      <c r="O52" s="46" cm="1">
         <f t="array" aca="1" ref="O52" ca="1">IF(A52="","",IF(L52=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I52+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J52+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K52)&gt;0)*((F52*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G52*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H52*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L52))</f>
-        <v/>
-      </c>
-      <c r="P52" s="46" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <v>35.5</v>
+      </c>
+      <c r="P52" s="46">
+        <f t="shared" ca="1" si="6"/>
+        <v>0.39436619718309857</v>
       </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.35">
@@ -23028,6 +23103,16 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="C2:E200">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
+      <formula>"✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:E200">
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
+      <formula>"✗"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -23041,12 +23126,12 @@
     <col min="1" max="16384" width="8.7265625" style="48"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="66" t="s">
+    <row r="1" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="64" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="2" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="65" t="s">
         <v>98</v>
@@ -23057,7 +23142,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="6" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="65" t="s">
         <v>100</v>
@@ -23078,13 +23163,13 @@
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="10" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="11" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="65" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="12" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="12" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="13" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="65" t="s">
         <v>105</v>
@@ -23130,7 +23215,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="22" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="22" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="23" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="65" t="s">
         <v>114</v>
@@ -23161,7 +23246,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="29" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="29" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="30" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="65" t="s">
         <v>120</v>
@@ -23182,7 +23267,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="34" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="34" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="35" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="65" t="s">
         <v>124</v>
@@ -23208,7 +23293,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="40" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="40" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="41" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="65" t="s">
         <v>129</v>
@@ -23224,7 +23309,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="44" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="44" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="45" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="65" t="s">
         <v>132</v>
@@ -23255,7 +23340,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="51" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="51" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="52" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="65" t="s">
         <v>138</v>
@@ -23281,7 +23366,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="57" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="57" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="58" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="65" t="s">
         <v>143</v>
@@ -23292,7 +23377,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="60" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="60" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="61" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="65" t="s">
         <v>98</v>
@@ -23303,7 +23388,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="63" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="63" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="64" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="65" t="s">
         <v>146</v>
@@ -23349,7 +23434,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="73" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="73" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="74" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="65" t="s">
         <v>155</v>
@@ -23380,7 +23465,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="80" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="80" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="81" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="65" t="s">
         <v>161</v>
@@ -23416,7 +23501,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="88" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="88" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="89" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="65" t="s">
         <v>168</v>
@@ -23427,7 +23512,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="91" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="91" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="92" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="65" t="s">
         <v>170</v>
@@ -23448,7 +23533,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="96" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="96" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="97" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="65" t="s">
         <v>174</v>
@@ -23459,7 +23544,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="99" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="99" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="100" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="65" t="s">
         <v>176</v>
@@ -23480,7 +23565,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="104" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="104" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="105" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="65" t="s">
         <v>180</v>
@@ -23531,7 +23616,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="115" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="115" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="116" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="65" t="s">
         <v>190</v>
@@ -23577,7 +23662,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="125" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="125" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="126" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="65" t="s">
         <v>199</v>
@@ -23598,7 +23683,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="130" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="130" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="131" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="65" t="s">
         <v>203</v>
@@ -23619,7 +23704,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="135" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="135" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="136" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="65" t="s">
         <v>207</v>
@@ -23635,7 +23720,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="139" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="139" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="140" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="65" t="s">
         <v>210</v>
@@ -23651,7 +23736,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="143" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="143" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="144" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="65" t="s">
         <v>213</v>
@@ -23682,7 +23767,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="150" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="150" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="151" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="65" t="s">
         <v>219</v>
@@ -23708,7 +23793,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="156" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="156" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="157" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="65" t="s">
         <v>224</v>
@@ -23759,7 +23844,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="167" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="167" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="168" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="65" t="s">
         <v>234</v>
@@ -23785,7 +23870,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="173" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="173" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="174" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="65" t="s">
         <v>239</v>
@@ -23821,7 +23906,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="181" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="181" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="182" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="65" t="s">
         <v>246</v>
@@ -23862,7 +23947,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="190" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="190" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="191" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="65" t="s">
         <v>254</v>
@@ -23898,7 +23983,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="198" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="198" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="199" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="65" t="s">
         <v>261</v>
@@ -23959,7 +24044,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="211" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="211" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="212" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" s="65" t="s">
         <v>273</v>
@@ -23980,7 +24065,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="216" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="216" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="217" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A217" s="65" t="s">
         <v>277</v>
@@ -24031,7 +24116,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="227" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="227" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="228" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" s="65" t="s">
         <v>287</v>
@@ -24042,7 +24127,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="230" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="230" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="231" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" s="65" t="s">
         <v>289</v>
@@ -24078,7 +24163,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="238" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="238" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="239" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A239" s="65" t="s">
         <v>296</v>
@@ -24099,7 +24184,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="243" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="243" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="244" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A244" s="65" t="s">
         <v>300</v>
@@ -24135,7 +24220,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="251" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="251" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="252" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A252" s="65" t="s">
         <v>307</v>
@@ -24171,13 +24256,13 @@
         <v>313</v>
       </c>
     </row>
-    <row r="259" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="259" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="260" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A260" s="65" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="261" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="261" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="262" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A262" s="65" t="s">
         <v>315</v>
@@ -24223,7 +24308,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="271" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="271" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="272" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A272" s="65" t="s">
         <v>324</v>
@@ -24269,19 +24354,19 @@
         <v>332</v>
       </c>
     </row>
-    <row r="281" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="281" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="282" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A282" s="65" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="283" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="283" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="284" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A284" s="65" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="285" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="285" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="286" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A286" s="65" t="s">
         <v>335</v>
@@ -24297,7 +24382,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="289" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="289" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="290" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A290" s="65" t="s">
         <v>338</v>
@@ -24318,7 +24403,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="294" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="294" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="295" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A295" s="65" t="s">
         <v>342</v>
@@ -24329,7 +24414,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="297" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="297" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="298" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A298" s="65" t="s">
         <v>344</v>
@@ -24350,7 +24435,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="302" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="302" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="303" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A303" s="65" t="s">
         <v>348</v>
@@ -24371,7 +24456,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="307" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="307" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="308" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A308" s="65" t="s">
         <v>352</v>
@@ -24382,13 +24467,13 @@
         <v>353</v>
       </c>
     </row>
-    <row r="310" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="310" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="311" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A311" s="65" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="312" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="312" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="313" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A313" s="65" t="s">
         <v>355</v>
@@ -24399,7 +24484,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="315" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="315" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="316" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A316" s="65" t="s">
         <v>357</v>
@@ -24420,7 +24505,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="320" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="320" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="321" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A321" s="65" t="s">
         <v>361</v>
@@ -24441,7 +24526,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="325" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="325" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="326" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A326" s="65" t="s">
         <v>365</v>
@@ -24457,7 +24542,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="329" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="329" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="330" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A330" s="65" t="s">
         <v>368</v>
@@ -24468,7 +24553,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="332" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="332" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="333" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A333" s="65" t="s">
         <v>370</v>
@@ -24479,7 +24564,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="335" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="335" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="336" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A336" s="65" t="s">
         <v>372</v>
@@ -24507,6 +24592,322 @@
     </row>
   </sheetData>
   <mergeCells count="340">
+    <mergeCell ref="A12:XFD12"/>
+    <mergeCell ref="A13:XFD13"/>
+    <mergeCell ref="A14:XFD14"/>
+    <mergeCell ref="A15:XFD15"/>
+    <mergeCell ref="A16:XFD16"/>
+    <mergeCell ref="A17:XFD17"/>
+    <mergeCell ref="A3:XFD3"/>
+    <mergeCell ref="A4:XFD4"/>
+    <mergeCell ref="A5:XFD5"/>
+    <mergeCell ref="A6:XFD6"/>
+    <mergeCell ref="A7:XFD7"/>
+    <mergeCell ref="A8:XFD8"/>
+    <mergeCell ref="A9:XFD9"/>
+    <mergeCell ref="A10:XFD10"/>
+    <mergeCell ref="A11:XFD11"/>
+    <mergeCell ref="A24:XFD24"/>
+    <mergeCell ref="A25:XFD25"/>
+    <mergeCell ref="A26:XFD26"/>
+    <mergeCell ref="A27:XFD27"/>
+    <mergeCell ref="A28:XFD28"/>
+    <mergeCell ref="A29:XFD29"/>
+    <mergeCell ref="A18:XFD18"/>
+    <mergeCell ref="A19:XFD19"/>
+    <mergeCell ref="A20:XFD20"/>
+    <mergeCell ref="A21:XFD21"/>
+    <mergeCell ref="A22:XFD22"/>
+    <mergeCell ref="A23:XFD23"/>
+    <mergeCell ref="A36:XFD36"/>
+    <mergeCell ref="A37:XFD37"/>
+    <mergeCell ref="A38:XFD38"/>
+    <mergeCell ref="A39:XFD39"/>
+    <mergeCell ref="A40:XFD40"/>
+    <mergeCell ref="A41:XFD41"/>
+    <mergeCell ref="A30:XFD30"/>
+    <mergeCell ref="A31:XFD31"/>
+    <mergeCell ref="A32:XFD32"/>
+    <mergeCell ref="A33:XFD33"/>
+    <mergeCell ref="A34:XFD34"/>
+    <mergeCell ref="A35:XFD35"/>
+    <mergeCell ref="A48:XFD48"/>
+    <mergeCell ref="A49:XFD49"/>
+    <mergeCell ref="A50:XFD50"/>
+    <mergeCell ref="A51:XFD51"/>
+    <mergeCell ref="A52:XFD52"/>
+    <mergeCell ref="A53:XFD53"/>
+    <mergeCell ref="A42:XFD42"/>
+    <mergeCell ref="A43:XFD43"/>
+    <mergeCell ref="A44:XFD44"/>
+    <mergeCell ref="A45:XFD45"/>
+    <mergeCell ref="A46:XFD46"/>
+    <mergeCell ref="A47:XFD47"/>
+    <mergeCell ref="A60:XFD60"/>
+    <mergeCell ref="A61:XFD61"/>
+    <mergeCell ref="A62:XFD62"/>
+    <mergeCell ref="A63:XFD63"/>
+    <mergeCell ref="A64:XFD64"/>
+    <mergeCell ref="A65:XFD65"/>
+    <mergeCell ref="A54:XFD54"/>
+    <mergeCell ref="A55:XFD55"/>
+    <mergeCell ref="A56:XFD56"/>
+    <mergeCell ref="A57:XFD57"/>
+    <mergeCell ref="A58:XFD58"/>
+    <mergeCell ref="A59:XFD59"/>
+    <mergeCell ref="A72:XFD72"/>
+    <mergeCell ref="A73:XFD73"/>
+    <mergeCell ref="A74:XFD74"/>
+    <mergeCell ref="A75:XFD75"/>
+    <mergeCell ref="A76:XFD76"/>
+    <mergeCell ref="A77:XFD77"/>
+    <mergeCell ref="A66:XFD66"/>
+    <mergeCell ref="A67:XFD67"/>
+    <mergeCell ref="A68:XFD68"/>
+    <mergeCell ref="A69:XFD69"/>
+    <mergeCell ref="A70:XFD70"/>
+    <mergeCell ref="A71:XFD71"/>
+    <mergeCell ref="A84:XFD84"/>
+    <mergeCell ref="A85:XFD85"/>
+    <mergeCell ref="A86:XFD86"/>
+    <mergeCell ref="A87:XFD87"/>
+    <mergeCell ref="A88:XFD88"/>
+    <mergeCell ref="A89:XFD89"/>
+    <mergeCell ref="A78:XFD78"/>
+    <mergeCell ref="A79:XFD79"/>
+    <mergeCell ref="A80:XFD80"/>
+    <mergeCell ref="A81:XFD81"/>
+    <mergeCell ref="A82:XFD82"/>
+    <mergeCell ref="A83:XFD83"/>
+    <mergeCell ref="A96:XFD96"/>
+    <mergeCell ref="A97:XFD97"/>
+    <mergeCell ref="A98:XFD98"/>
+    <mergeCell ref="A99:XFD99"/>
+    <mergeCell ref="A100:XFD100"/>
+    <mergeCell ref="A101:XFD101"/>
+    <mergeCell ref="A90:XFD90"/>
+    <mergeCell ref="A91:XFD91"/>
+    <mergeCell ref="A92:XFD92"/>
+    <mergeCell ref="A93:XFD93"/>
+    <mergeCell ref="A94:XFD94"/>
+    <mergeCell ref="A95:XFD95"/>
+    <mergeCell ref="A108:XFD108"/>
+    <mergeCell ref="A109:XFD109"/>
+    <mergeCell ref="A110:XFD110"/>
+    <mergeCell ref="A111:XFD111"/>
+    <mergeCell ref="A112:XFD112"/>
+    <mergeCell ref="A113:XFD113"/>
+    <mergeCell ref="A102:XFD102"/>
+    <mergeCell ref="A103:XFD103"/>
+    <mergeCell ref="A104:XFD104"/>
+    <mergeCell ref="A105:XFD105"/>
+    <mergeCell ref="A106:XFD106"/>
+    <mergeCell ref="A107:XFD107"/>
+    <mergeCell ref="A120:XFD120"/>
+    <mergeCell ref="A121:XFD121"/>
+    <mergeCell ref="A122:XFD122"/>
+    <mergeCell ref="A123:XFD123"/>
+    <mergeCell ref="A124:XFD124"/>
+    <mergeCell ref="A125:XFD125"/>
+    <mergeCell ref="A114:XFD114"/>
+    <mergeCell ref="A115:XFD115"/>
+    <mergeCell ref="A116:XFD116"/>
+    <mergeCell ref="A117:XFD117"/>
+    <mergeCell ref="A118:XFD118"/>
+    <mergeCell ref="A119:XFD119"/>
+    <mergeCell ref="A132:XFD132"/>
+    <mergeCell ref="A133:XFD133"/>
+    <mergeCell ref="A134:XFD134"/>
+    <mergeCell ref="A135:XFD135"/>
+    <mergeCell ref="A136:XFD136"/>
+    <mergeCell ref="A137:XFD137"/>
+    <mergeCell ref="A126:XFD126"/>
+    <mergeCell ref="A127:XFD127"/>
+    <mergeCell ref="A128:XFD128"/>
+    <mergeCell ref="A129:XFD129"/>
+    <mergeCell ref="A130:XFD130"/>
+    <mergeCell ref="A131:XFD131"/>
+    <mergeCell ref="A144:XFD144"/>
+    <mergeCell ref="A145:XFD145"/>
+    <mergeCell ref="A146:XFD146"/>
+    <mergeCell ref="A147:XFD147"/>
+    <mergeCell ref="A148:XFD148"/>
+    <mergeCell ref="A149:XFD149"/>
+    <mergeCell ref="A138:XFD138"/>
+    <mergeCell ref="A139:XFD139"/>
+    <mergeCell ref="A140:XFD140"/>
+    <mergeCell ref="A141:XFD141"/>
+    <mergeCell ref="A142:XFD142"/>
+    <mergeCell ref="A143:XFD143"/>
+    <mergeCell ref="A156:XFD156"/>
+    <mergeCell ref="A157:XFD157"/>
+    <mergeCell ref="A158:XFD158"/>
+    <mergeCell ref="A159:XFD159"/>
+    <mergeCell ref="A160:XFD160"/>
+    <mergeCell ref="A161:XFD161"/>
+    <mergeCell ref="A150:XFD150"/>
+    <mergeCell ref="A151:XFD151"/>
+    <mergeCell ref="A152:XFD152"/>
+    <mergeCell ref="A153:XFD153"/>
+    <mergeCell ref="A154:XFD154"/>
+    <mergeCell ref="A155:XFD155"/>
+    <mergeCell ref="A168:XFD168"/>
+    <mergeCell ref="A169:XFD169"/>
+    <mergeCell ref="A170:XFD170"/>
+    <mergeCell ref="A171:XFD171"/>
+    <mergeCell ref="A172:XFD172"/>
+    <mergeCell ref="A173:XFD173"/>
+    <mergeCell ref="A162:XFD162"/>
+    <mergeCell ref="A163:XFD163"/>
+    <mergeCell ref="A164:XFD164"/>
+    <mergeCell ref="A165:XFD165"/>
+    <mergeCell ref="A166:XFD166"/>
+    <mergeCell ref="A167:XFD167"/>
+    <mergeCell ref="A180:XFD180"/>
+    <mergeCell ref="A181:XFD181"/>
+    <mergeCell ref="A182:XFD182"/>
+    <mergeCell ref="A183:XFD183"/>
+    <mergeCell ref="A184:XFD184"/>
+    <mergeCell ref="A185:XFD185"/>
+    <mergeCell ref="A174:XFD174"/>
+    <mergeCell ref="A175:XFD175"/>
+    <mergeCell ref="A176:XFD176"/>
+    <mergeCell ref="A177:XFD177"/>
+    <mergeCell ref="A178:XFD178"/>
+    <mergeCell ref="A179:XFD179"/>
+    <mergeCell ref="A192:XFD192"/>
+    <mergeCell ref="A193:XFD193"/>
+    <mergeCell ref="A194:XFD194"/>
+    <mergeCell ref="A195:XFD195"/>
+    <mergeCell ref="A196:XFD196"/>
+    <mergeCell ref="A197:XFD197"/>
+    <mergeCell ref="A186:XFD186"/>
+    <mergeCell ref="A187:XFD187"/>
+    <mergeCell ref="A188:XFD188"/>
+    <mergeCell ref="A189:XFD189"/>
+    <mergeCell ref="A190:XFD190"/>
+    <mergeCell ref="A191:XFD191"/>
+    <mergeCell ref="A204:XFD204"/>
+    <mergeCell ref="A205:XFD205"/>
+    <mergeCell ref="A206:XFD206"/>
+    <mergeCell ref="A207:XFD207"/>
+    <mergeCell ref="A208:XFD208"/>
+    <mergeCell ref="A209:XFD209"/>
+    <mergeCell ref="A198:XFD198"/>
+    <mergeCell ref="A199:XFD199"/>
+    <mergeCell ref="A200:XFD200"/>
+    <mergeCell ref="A201:XFD201"/>
+    <mergeCell ref="A202:XFD202"/>
+    <mergeCell ref="A203:XFD203"/>
+    <mergeCell ref="A216:XFD216"/>
+    <mergeCell ref="A217:XFD217"/>
+    <mergeCell ref="A218:XFD218"/>
+    <mergeCell ref="A219:XFD219"/>
+    <mergeCell ref="A220:XFD220"/>
+    <mergeCell ref="A221:XFD221"/>
+    <mergeCell ref="A210:XFD210"/>
+    <mergeCell ref="A211:XFD211"/>
+    <mergeCell ref="A212:XFD212"/>
+    <mergeCell ref="A213:XFD213"/>
+    <mergeCell ref="A214:XFD214"/>
+    <mergeCell ref="A215:XFD215"/>
+    <mergeCell ref="A228:XFD228"/>
+    <mergeCell ref="A229:XFD229"/>
+    <mergeCell ref="A230:XFD230"/>
+    <mergeCell ref="A231:XFD231"/>
+    <mergeCell ref="A232:XFD232"/>
+    <mergeCell ref="A233:XFD233"/>
+    <mergeCell ref="A222:XFD222"/>
+    <mergeCell ref="A223:XFD223"/>
+    <mergeCell ref="A224:XFD224"/>
+    <mergeCell ref="A225:XFD225"/>
+    <mergeCell ref="A226:XFD226"/>
+    <mergeCell ref="A227:XFD227"/>
+    <mergeCell ref="A240:XFD240"/>
+    <mergeCell ref="A241:XFD241"/>
+    <mergeCell ref="A242:XFD242"/>
+    <mergeCell ref="A243:XFD243"/>
+    <mergeCell ref="A244:XFD244"/>
+    <mergeCell ref="A245:XFD245"/>
+    <mergeCell ref="A234:XFD234"/>
+    <mergeCell ref="A235:XFD235"/>
+    <mergeCell ref="A236:XFD236"/>
+    <mergeCell ref="A237:XFD237"/>
+    <mergeCell ref="A238:XFD238"/>
+    <mergeCell ref="A239:XFD239"/>
+    <mergeCell ref="A252:XFD252"/>
+    <mergeCell ref="A253:XFD253"/>
+    <mergeCell ref="A254:XFD254"/>
+    <mergeCell ref="A255:XFD255"/>
+    <mergeCell ref="A256:XFD256"/>
+    <mergeCell ref="A257:XFD257"/>
+    <mergeCell ref="A246:XFD246"/>
+    <mergeCell ref="A247:XFD247"/>
+    <mergeCell ref="A248:XFD248"/>
+    <mergeCell ref="A249:XFD249"/>
+    <mergeCell ref="A250:XFD250"/>
+    <mergeCell ref="A251:XFD251"/>
+    <mergeCell ref="A264:XFD264"/>
+    <mergeCell ref="A265:XFD265"/>
+    <mergeCell ref="A266:XFD266"/>
+    <mergeCell ref="A267:XFD267"/>
+    <mergeCell ref="A268:XFD268"/>
+    <mergeCell ref="A269:XFD269"/>
+    <mergeCell ref="A258:XFD258"/>
+    <mergeCell ref="A259:XFD259"/>
+    <mergeCell ref="A260:XFD260"/>
+    <mergeCell ref="A261:XFD261"/>
+    <mergeCell ref="A262:XFD262"/>
+    <mergeCell ref="A263:XFD263"/>
+    <mergeCell ref="A276:XFD276"/>
+    <mergeCell ref="A277:XFD277"/>
+    <mergeCell ref="A278:XFD278"/>
+    <mergeCell ref="A279:XFD279"/>
+    <mergeCell ref="A280:XFD280"/>
+    <mergeCell ref="A281:XFD281"/>
+    <mergeCell ref="A270:XFD270"/>
+    <mergeCell ref="A271:XFD271"/>
+    <mergeCell ref="A272:XFD272"/>
+    <mergeCell ref="A273:XFD273"/>
+    <mergeCell ref="A274:XFD274"/>
+    <mergeCell ref="A275:XFD275"/>
+    <mergeCell ref="A288:XFD288"/>
+    <mergeCell ref="A289:XFD289"/>
+    <mergeCell ref="A290:XFD290"/>
+    <mergeCell ref="A291:XFD291"/>
+    <mergeCell ref="A292:XFD292"/>
+    <mergeCell ref="A293:XFD293"/>
+    <mergeCell ref="A282:XFD282"/>
+    <mergeCell ref="A283:XFD283"/>
+    <mergeCell ref="A284:XFD284"/>
+    <mergeCell ref="A285:XFD285"/>
+    <mergeCell ref="A286:XFD286"/>
+    <mergeCell ref="A287:XFD287"/>
+    <mergeCell ref="A300:XFD300"/>
+    <mergeCell ref="A301:XFD301"/>
+    <mergeCell ref="A302:XFD302"/>
+    <mergeCell ref="A303:XFD303"/>
+    <mergeCell ref="A304:XFD304"/>
+    <mergeCell ref="A305:XFD305"/>
+    <mergeCell ref="A294:XFD294"/>
+    <mergeCell ref="A295:XFD295"/>
+    <mergeCell ref="A296:XFD296"/>
+    <mergeCell ref="A297:XFD297"/>
+    <mergeCell ref="A298:XFD298"/>
+    <mergeCell ref="A299:XFD299"/>
+    <mergeCell ref="A323:XFD323"/>
+    <mergeCell ref="A312:XFD312"/>
+    <mergeCell ref="A313:XFD313"/>
+    <mergeCell ref="A314:XFD314"/>
+    <mergeCell ref="A315:XFD315"/>
+    <mergeCell ref="A316:XFD316"/>
+    <mergeCell ref="A317:XFD317"/>
+    <mergeCell ref="A306:XFD306"/>
+    <mergeCell ref="A307:XFD307"/>
+    <mergeCell ref="A308:XFD308"/>
+    <mergeCell ref="A309:XFD309"/>
+    <mergeCell ref="A310:XFD310"/>
+    <mergeCell ref="A311:XFD311"/>
     <mergeCell ref="A1:XFD1"/>
     <mergeCell ref="A336:XFD336"/>
     <mergeCell ref="A337:XFD337"/>
@@ -24531,322 +24932,6 @@
     <mergeCell ref="A320:XFD320"/>
     <mergeCell ref="A321:XFD321"/>
     <mergeCell ref="A322:XFD322"/>
-    <mergeCell ref="A323:XFD323"/>
-    <mergeCell ref="A312:XFD312"/>
-    <mergeCell ref="A313:XFD313"/>
-    <mergeCell ref="A314:XFD314"/>
-    <mergeCell ref="A315:XFD315"/>
-    <mergeCell ref="A316:XFD316"/>
-    <mergeCell ref="A317:XFD317"/>
-    <mergeCell ref="A306:XFD306"/>
-    <mergeCell ref="A307:XFD307"/>
-    <mergeCell ref="A308:XFD308"/>
-    <mergeCell ref="A309:XFD309"/>
-    <mergeCell ref="A310:XFD310"/>
-    <mergeCell ref="A311:XFD311"/>
-    <mergeCell ref="A300:XFD300"/>
-    <mergeCell ref="A301:XFD301"/>
-    <mergeCell ref="A302:XFD302"/>
-    <mergeCell ref="A303:XFD303"/>
-    <mergeCell ref="A304:XFD304"/>
-    <mergeCell ref="A305:XFD305"/>
-    <mergeCell ref="A294:XFD294"/>
-    <mergeCell ref="A295:XFD295"/>
-    <mergeCell ref="A296:XFD296"/>
-    <mergeCell ref="A297:XFD297"/>
-    <mergeCell ref="A298:XFD298"/>
-    <mergeCell ref="A299:XFD299"/>
-    <mergeCell ref="A288:XFD288"/>
-    <mergeCell ref="A289:XFD289"/>
-    <mergeCell ref="A290:XFD290"/>
-    <mergeCell ref="A291:XFD291"/>
-    <mergeCell ref="A292:XFD292"/>
-    <mergeCell ref="A293:XFD293"/>
-    <mergeCell ref="A282:XFD282"/>
-    <mergeCell ref="A283:XFD283"/>
-    <mergeCell ref="A284:XFD284"/>
-    <mergeCell ref="A285:XFD285"/>
-    <mergeCell ref="A286:XFD286"/>
-    <mergeCell ref="A287:XFD287"/>
-    <mergeCell ref="A276:XFD276"/>
-    <mergeCell ref="A277:XFD277"/>
-    <mergeCell ref="A278:XFD278"/>
-    <mergeCell ref="A279:XFD279"/>
-    <mergeCell ref="A280:XFD280"/>
-    <mergeCell ref="A281:XFD281"/>
-    <mergeCell ref="A270:XFD270"/>
-    <mergeCell ref="A271:XFD271"/>
-    <mergeCell ref="A272:XFD272"/>
-    <mergeCell ref="A273:XFD273"/>
-    <mergeCell ref="A274:XFD274"/>
-    <mergeCell ref="A275:XFD275"/>
-    <mergeCell ref="A264:XFD264"/>
-    <mergeCell ref="A265:XFD265"/>
-    <mergeCell ref="A266:XFD266"/>
-    <mergeCell ref="A267:XFD267"/>
-    <mergeCell ref="A268:XFD268"/>
-    <mergeCell ref="A269:XFD269"/>
-    <mergeCell ref="A258:XFD258"/>
-    <mergeCell ref="A259:XFD259"/>
-    <mergeCell ref="A260:XFD260"/>
-    <mergeCell ref="A261:XFD261"/>
-    <mergeCell ref="A262:XFD262"/>
-    <mergeCell ref="A263:XFD263"/>
-    <mergeCell ref="A252:XFD252"/>
-    <mergeCell ref="A253:XFD253"/>
-    <mergeCell ref="A254:XFD254"/>
-    <mergeCell ref="A255:XFD255"/>
-    <mergeCell ref="A256:XFD256"/>
-    <mergeCell ref="A257:XFD257"/>
-    <mergeCell ref="A246:XFD246"/>
-    <mergeCell ref="A247:XFD247"/>
-    <mergeCell ref="A248:XFD248"/>
-    <mergeCell ref="A249:XFD249"/>
-    <mergeCell ref="A250:XFD250"/>
-    <mergeCell ref="A251:XFD251"/>
-    <mergeCell ref="A240:XFD240"/>
-    <mergeCell ref="A241:XFD241"/>
-    <mergeCell ref="A242:XFD242"/>
-    <mergeCell ref="A243:XFD243"/>
-    <mergeCell ref="A244:XFD244"/>
-    <mergeCell ref="A245:XFD245"/>
-    <mergeCell ref="A234:XFD234"/>
-    <mergeCell ref="A235:XFD235"/>
-    <mergeCell ref="A236:XFD236"/>
-    <mergeCell ref="A237:XFD237"/>
-    <mergeCell ref="A238:XFD238"/>
-    <mergeCell ref="A239:XFD239"/>
-    <mergeCell ref="A228:XFD228"/>
-    <mergeCell ref="A229:XFD229"/>
-    <mergeCell ref="A230:XFD230"/>
-    <mergeCell ref="A231:XFD231"/>
-    <mergeCell ref="A232:XFD232"/>
-    <mergeCell ref="A233:XFD233"/>
-    <mergeCell ref="A222:XFD222"/>
-    <mergeCell ref="A223:XFD223"/>
-    <mergeCell ref="A224:XFD224"/>
-    <mergeCell ref="A225:XFD225"/>
-    <mergeCell ref="A226:XFD226"/>
-    <mergeCell ref="A227:XFD227"/>
-    <mergeCell ref="A216:XFD216"/>
-    <mergeCell ref="A217:XFD217"/>
-    <mergeCell ref="A218:XFD218"/>
-    <mergeCell ref="A219:XFD219"/>
-    <mergeCell ref="A220:XFD220"/>
-    <mergeCell ref="A221:XFD221"/>
-    <mergeCell ref="A210:XFD210"/>
-    <mergeCell ref="A211:XFD211"/>
-    <mergeCell ref="A212:XFD212"/>
-    <mergeCell ref="A213:XFD213"/>
-    <mergeCell ref="A214:XFD214"/>
-    <mergeCell ref="A215:XFD215"/>
-    <mergeCell ref="A204:XFD204"/>
-    <mergeCell ref="A205:XFD205"/>
-    <mergeCell ref="A206:XFD206"/>
-    <mergeCell ref="A207:XFD207"/>
-    <mergeCell ref="A208:XFD208"/>
-    <mergeCell ref="A209:XFD209"/>
-    <mergeCell ref="A198:XFD198"/>
-    <mergeCell ref="A199:XFD199"/>
-    <mergeCell ref="A200:XFD200"/>
-    <mergeCell ref="A201:XFD201"/>
-    <mergeCell ref="A202:XFD202"/>
-    <mergeCell ref="A203:XFD203"/>
-    <mergeCell ref="A192:XFD192"/>
-    <mergeCell ref="A193:XFD193"/>
-    <mergeCell ref="A194:XFD194"/>
-    <mergeCell ref="A195:XFD195"/>
-    <mergeCell ref="A196:XFD196"/>
-    <mergeCell ref="A197:XFD197"/>
-    <mergeCell ref="A186:XFD186"/>
-    <mergeCell ref="A187:XFD187"/>
-    <mergeCell ref="A188:XFD188"/>
-    <mergeCell ref="A189:XFD189"/>
-    <mergeCell ref="A190:XFD190"/>
-    <mergeCell ref="A191:XFD191"/>
-    <mergeCell ref="A180:XFD180"/>
-    <mergeCell ref="A181:XFD181"/>
-    <mergeCell ref="A182:XFD182"/>
-    <mergeCell ref="A183:XFD183"/>
-    <mergeCell ref="A184:XFD184"/>
-    <mergeCell ref="A185:XFD185"/>
-    <mergeCell ref="A174:XFD174"/>
-    <mergeCell ref="A175:XFD175"/>
-    <mergeCell ref="A176:XFD176"/>
-    <mergeCell ref="A177:XFD177"/>
-    <mergeCell ref="A178:XFD178"/>
-    <mergeCell ref="A179:XFD179"/>
-    <mergeCell ref="A168:XFD168"/>
-    <mergeCell ref="A169:XFD169"/>
-    <mergeCell ref="A170:XFD170"/>
-    <mergeCell ref="A171:XFD171"/>
-    <mergeCell ref="A172:XFD172"/>
-    <mergeCell ref="A173:XFD173"/>
-    <mergeCell ref="A162:XFD162"/>
-    <mergeCell ref="A163:XFD163"/>
-    <mergeCell ref="A164:XFD164"/>
-    <mergeCell ref="A165:XFD165"/>
-    <mergeCell ref="A166:XFD166"/>
-    <mergeCell ref="A167:XFD167"/>
-    <mergeCell ref="A156:XFD156"/>
-    <mergeCell ref="A157:XFD157"/>
-    <mergeCell ref="A158:XFD158"/>
-    <mergeCell ref="A159:XFD159"/>
-    <mergeCell ref="A160:XFD160"/>
-    <mergeCell ref="A161:XFD161"/>
-    <mergeCell ref="A150:XFD150"/>
-    <mergeCell ref="A151:XFD151"/>
-    <mergeCell ref="A152:XFD152"/>
-    <mergeCell ref="A153:XFD153"/>
-    <mergeCell ref="A154:XFD154"/>
-    <mergeCell ref="A155:XFD155"/>
-    <mergeCell ref="A144:XFD144"/>
-    <mergeCell ref="A145:XFD145"/>
-    <mergeCell ref="A146:XFD146"/>
-    <mergeCell ref="A147:XFD147"/>
-    <mergeCell ref="A148:XFD148"/>
-    <mergeCell ref="A149:XFD149"/>
-    <mergeCell ref="A138:XFD138"/>
-    <mergeCell ref="A139:XFD139"/>
-    <mergeCell ref="A140:XFD140"/>
-    <mergeCell ref="A141:XFD141"/>
-    <mergeCell ref="A142:XFD142"/>
-    <mergeCell ref="A143:XFD143"/>
-    <mergeCell ref="A132:XFD132"/>
-    <mergeCell ref="A133:XFD133"/>
-    <mergeCell ref="A134:XFD134"/>
-    <mergeCell ref="A135:XFD135"/>
-    <mergeCell ref="A136:XFD136"/>
-    <mergeCell ref="A137:XFD137"/>
-    <mergeCell ref="A126:XFD126"/>
-    <mergeCell ref="A127:XFD127"/>
-    <mergeCell ref="A128:XFD128"/>
-    <mergeCell ref="A129:XFD129"/>
-    <mergeCell ref="A130:XFD130"/>
-    <mergeCell ref="A131:XFD131"/>
-    <mergeCell ref="A120:XFD120"/>
-    <mergeCell ref="A121:XFD121"/>
-    <mergeCell ref="A122:XFD122"/>
-    <mergeCell ref="A123:XFD123"/>
-    <mergeCell ref="A124:XFD124"/>
-    <mergeCell ref="A125:XFD125"/>
-    <mergeCell ref="A114:XFD114"/>
-    <mergeCell ref="A115:XFD115"/>
-    <mergeCell ref="A116:XFD116"/>
-    <mergeCell ref="A117:XFD117"/>
-    <mergeCell ref="A118:XFD118"/>
-    <mergeCell ref="A119:XFD119"/>
-    <mergeCell ref="A108:XFD108"/>
-    <mergeCell ref="A109:XFD109"/>
-    <mergeCell ref="A110:XFD110"/>
-    <mergeCell ref="A111:XFD111"/>
-    <mergeCell ref="A112:XFD112"/>
-    <mergeCell ref="A113:XFD113"/>
-    <mergeCell ref="A102:XFD102"/>
-    <mergeCell ref="A103:XFD103"/>
-    <mergeCell ref="A104:XFD104"/>
-    <mergeCell ref="A105:XFD105"/>
-    <mergeCell ref="A106:XFD106"/>
-    <mergeCell ref="A107:XFD107"/>
-    <mergeCell ref="A96:XFD96"/>
-    <mergeCell ref="A97:XFD97"/>
-    <mergeCell ref="A98:XFD98"/>
-    <mergeCell ref="A99:XFD99"/>
-    <mergeCell ref="A100:XFD100"/>
-    <mergeCell ref="A101:XFD101"/>
-    <mergeCell ref="A90:XFD90"/>
-    <mergeCell ref="A91:XFD91"/>
-    <mergeCell ref="A92:XFD92"/>
-    <mergeCell ref="A93:XFD93"/>
-    <mergeCell ref="A94:XFD94"/>
-    <mergeCell ref="A95:XFD95"/>
-    <mergeCell ref="A84:XFD84"/>
-    <mergeCell ref="A85:XFD85"/>
-    <mergeCell ref="A86:XFD86"/>
-    <mergeCell ref="A87:XFD87"/>
-    <mergeCell ref="A88:XFD88"/>
-    <mergeCell ref="A89:XFD89"/>
-    <mergeCell ref="A78:XFD78"/>
-    <mergeCell ref="A79:XFD79"/>
-    <mergeCell ref="A80:XFD80"/>
-    <mergeCell ref="A81:XFD81"/>
-    <mergeCell ref="A82:XFD82"/>
-    <mergeCell ref="A83:XFD83"/>
-    <mergeCell ref="A72:XFD72"/>
-    <mergeCell ref="A73:XFD73"/>
-    <mergeCell ref="A74:XFD74"/>
-    <mergeCell ref="A75:XFD75"/>
-    <mergeCell ref="A76:XFD76"/>
-    <mergeCell ref="A77:XFD77"/>
-    <mergeCell ref="A66:XFD66"/>
-    <mergeCell ref="A67:XFD67"/>
-    <mergeCell ref="A68:XFD68"/>
-    <mergeCell ref="A69:XFD69"/>
-    <mergeCell ref="A70:XFD70"/>
-    <mergeCell ref="A71:XFD71"/>
-    <mergeCell ref="A60:XFD60"/>
-    <mergeCell ref="A61:XFD61"/>
-    <mergeCell ref="A62:XFD62"/>
-    <mergeCell ref="A63:XFD63"/>
-    <mergeCell ref="A64:XFD64"/>
-    <mergeCell ref="A65:XFD65"/>
-    <mergeCell ref="A54:XFD54"/>
-    <mergeCell ref="A55:XFD55"/>
-    <mergeCell ref="A56:XFD56"/>
-    <mergeCell ref="A57:XFD57"/>
-    <mergeCell ref="A58:XFD58"/>
-    <mergeCell ref="A59:XFD59"/>
-    <mergeCell ref="A48:XFD48"/>
-    <mergeCell ref="A49:XFD49"/>
-    <mergeCell ref="A50:XFD50"/>
-    <mergeCell ref="A51:XFD51"/>
-    <mergeCell ref="A52:XFD52"/>
-    <mergeCell ref="A53:XFD53"/>
-    <mergeCell ref="A42:XFD42"/>
-    <mergeCell ref="A43:XFD43"/>
-    <mergeCell ref="A44:XFD44"/>
-    <mergeCell ref="A45:XFD45"/>
-    <mergeCell ref="A46:XFD46"/>
-    <mergeCell ref="A47:XFD47"/>
-    <mergeCell ref="A36:XFD36"/>
-    <mergeCell ref="A37:XFD37"/>
-    <mergeCell ref="A38:XFD38"/>
-    <mergeCell ref="A39:XFD39"/>
-    <mergeCell ref="A40:XFD40"/>
-    <mergeCell ref="A41:XFD41"/>
-    <mergeCell ref="A30:XFD30"/>
-    <mergeCell ref="A31:XFD31"/>
-    <mergeCell ref="A32:XFD32"/>
-    <mergeCell ref="A33:XFD33"/>
-    <mergeCell ref="A34:XFD34"/>
-    <mergeCell ref="A35:XFD35"/>
-    <mergeCell ref="A24:XFD24"/>
-    <mergeCell ref="A25:XFD25"/>
-    <mergeCell ref="A26:XFD26"/>
-    <mergeCell ref="A27:XFD27"/>
-    <mergeCell ref="A28:XFD28"/>
-    <mergeCell ref="A29:XFD29"/>
-    <mergeCell ref="A18:XFD18"/>
-    <mergeCell ref="A19:XFD19"/>
-    <mergeCell ref="A20:XFD20"/>
-    <mergeCell ref="A21:XFD21"/>
-    <mergeCell ref="A22:XFD22"/>
-    <mergeCell ref="A23:XFD23"/>
-    <mergeCell ref="A12:XFD12"/>
-    <mergeCell ref="A13:XFD13"/>
-    <mergeCell ref="A14:XFD14"/>
-    <mergeCell ref="A15:XFD15"/>
-    <mergeCell ref="A16:XFD16"/>
-    <mergeCell ref="A17:XFD17"/>
-    <mergeCell ref="A3:XFD3"/>
-    <mergeCell ref="A4:XFD4"/>
-    <mergeCell ref="A5:XFD5"/>
-    <mergeCell ref="A6:XFD6"/>
-    <mergeCell ref="A7:XFD7"/>
-    <mergeCell ref="A8:XFD8"/>
-    <mergeCell ref="A9:XFD9"/>
-    <mergeCell ref="A10:XFD10"/>
-    <mergeCell ref="A11:XFD11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Tomodachi Life Living the Dream island dating analysis.xlsx
+++ b/Tomodachi Life Living the Dream island dating analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Robin\OneDrive\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74CEC80B-D449-4049-85B4-05D0902A75B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A685C16-0C10-420F-90FE-DC549909060F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18700" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18700" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mii List" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="433">
   <si>
     <t>Name</t>
   </si>
@@ -267,9 +267,6 @@
     <t>Parity adjustment (odd total)</t>
   </si>
   <si>
-    <t>Odd remaining Miis → 1 extra unpaired</t>
-  </si>
-  <si>
     <t>📛 MINIMUM UNPAIRED MIIS</t>
   </si>
   <si>
@@ -1353,7 +1350,16 @@
     <t>Nny</t>
   </si>
   <si>
-    <t>Wayward Vagabond</t>
+    <t>WV</t>
+  </si>
+  <si>
+    <t>Sophia</t>
+  </si>
+  <si>
+    <t>Rachel</t>
+  </si>
+  <si>
+    <t>If there are an odd number of remaining Miis, at least one must be unpaired</t>
   </si>
 </sst>
 </file>
@@ -1363,13 +1369,20 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="36" x14ac:knownFonts="1">
+  <fonts count="37" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1720,46 +1733,46 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1768,97 +1781,98 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="1" xfId="1"/>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="1" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="1" xfId="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="30" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="1" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="31" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="35" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="36" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Calculation" xfId="1" builtinId="22"/>
@@ -2238,7 +2252,7 @@
     </row>
     <row r="2" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="15" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B2" s="49" t="s">
         <v>6</v>
@@ -2257,14 +2271,14 @@
       </c>
       <c r="H2" s="7">
         <f>COUNTA(A2:A200)</f>
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
     </row>
     <row r="3" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="51" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B3" s="50" t="s">
         <v>6</v>
@@ -2295,7 +2309,7 @@
     </row>
     <row r="4" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="53" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B4" s="56" t="s">
         <v>10</v>
@@ -2314,7 +2328,7 @@
       </c>
       <c r="H4" s="7">
         <f>COUNTIF(B:B,"Female")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>12</v>
@@ -2326,7 +2340,7 @@
     </row>
     <row r="5" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="54" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B5" s="59" t="s">
         <v>10</v>
@@ -2345,7 +2359,7 @@
       </c>
       <c r="H5" s="9">
         <f>COUNTIF(B:B,"Nonbinary")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5" s="10" t="s">
         <v>14</v>
@@ -2357,7 +2371,7 @@
     </row>
     <row r="6" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="53" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B6" s="56" t="s">
         <v>10</v>
@@ -2374,7 +2388,7 @@
     </row>
     <row r="7" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="54" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B7" s="59" t="s">
         <v>10</v>
@@ -2391,7 +2405,7 @@
     </row>
     <row r="8" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="53" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B8" s="56" t="s">
         <v>10</v>
@@ -2408,7 +2422,7 @@
     </row>
     <row r="9" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="54" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B9" s="59" t="s">
         <v>10</v>
@@ -2425,7 +2439,7 @@
     </row>
     <row r="10" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="53" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B10" s="62" t="s">
         <v>13</v>
@@ -2442,7 +2456,7 @@
     </row>
     <row r="11" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="54" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B11" s="59" t="s">
         <v>10</v>
@@ -2459,7 +2473,7 @@
     </row>
     <row r="12" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="53" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B12" s="56" t="s">
         <v>10</v>
@@ -2476,7 +2490,7 @@
     </row>
     <row r="13" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="54" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B13" s="63" t="s">
         <v>13</v>
@@ -2493,7 +2507,7 @@
     </row>
     <row r="14" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="53" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B14" s="56" t="s">
         <v>10</v>
@@ -2510,7 +2524,7 @@
     </row>
     <row r="15" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="54" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B15" s="59" t="s">
         <v>10</v>
@@ -2527,7 +2541,7 @@
     </row>
     <row r="16" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="53" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B16" s="62" t="s">
         <v>13</v>
@@ -2544,7 +2558,7 @@
     </row>
     <row r="17" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="54" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B17" s="63" t="s">
         <v>13</v>
@@ -2561,7 +2575,7 @@
     </row>
     <row r="18" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="53" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B18" s="56" t="s">
         <v>10</v>
@@ -2578,7 +2592,7 @@
     </row>
     <row r="19" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="54" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B19" s="59" t="s">
         <v>10</v>
@@ -2595,7 +2609,7 @@
     </row>
     <row r="20" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="53" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B20" s="62" t="s">
         <v>13</v>
@@ -2612,7 +2626,7 @@
     </row>
     <row r="21" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="54" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B21" s="59" t="s">
         <v>10</v>
@@ -2629,7 +2643,7 @@
     </row>
     <row r="22" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="53" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B22" s="56" t="s">
         <v>10</v>
@@ -2646,7 +2660,7 @@
     </row>
     <row r="23" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="54" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B23" s="63" t="s">
         <v>13</v>
@@ -2663,7 +2677,7 @@
     </row>
     <row r="24" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="53" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B24" s="62" t="s">
         <v>13</v>
@@ -2680,7 +2694,7 @@
     </row>
     <row r="25" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="54" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B25" s="63" t="s">
         <v>13</v>
@@ -2697,7 +2711,7 @@
     </row>
     <row r="26" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="53" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B26" s="56" t="s">
         <v>10</v>
@@ -2714,7 +2728,7 @@
     </row>
     <row r="27" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="54" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B27" s="59" t="s">
         <v>10</v>
@@ -2731,7 +2745,7 @@
     </row>
     <row r="28" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="53" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B28" s="56" t="s">
         <v>10</v>
@@ -2748,7 +2762,7 @@
     </row>
     <row r="29" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="54" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B29" s="59" t="s">
         <v>10</v>
@@ -2765,7 +2779,7 @@
     </row>
     <row r="30" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="53" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B30" s="56" t="s">
         <v>10</v>
@@ -2782,7 +2796,7 @@
     </row>
     <row r="31" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="54" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B31" s="59" t="s">
         <v>10</v>
@@ -2799,7 +2813,7 @@
     </row>
     <row r="32" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="53" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B32" s="56" t="s">
         <v>10</v>
@@ -2816,7 +2830,7 @@
     </row>
     <row r="33" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="54" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B33" s="59" t="s">
         <v>10</v>
@@ -2833,7 +2847,7 @@
     </row>
     <row r="34" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="53" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B34" s="56" t="s">
         <v>10</v>
@@ -2850,7 +2864,7 @@
     </row>
     <row r="35" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="54" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B35" s="63" t="s">
         <v>13</v>
@@ -2867,7 +2881,7 @@
     </row>
     <row r="36" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="53" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B36" s="62" t="s">
         <v>13</v>
@@ -2884,7 +2898,7 @@
     </row>
     <row r="37" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="54" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B37" s="59" t="s">
         <v>10</v>
@@ -2901,7 +2915,7 @@
     </row>
     <row r="38" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="53" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B38" s="56" t="s">
         <v>10</v>
@@ -2918,7 +2932,7 @@
     </row>
     <row r="39" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="54" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B39" s="63" t="s">
         <v>13</v>
@@ -2935,7 +2949,7 @@
     </row>
     <row r="40" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="53" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B40" s="56" t="s">
         <v>10</v>
@@ -2952,7 +2966,7 @@
     </row>
     <row r="41" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="54" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B41" s="59" t="s">
         <v>10</v>
@@ -2969,7 +2983,7 @@
     </row>
     <row r="42" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="53" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B42" s="56" t="s">
         <v>10</v>
@@ -2986,7 +3000,7 @@
     </row>
     <row r="43" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="54" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B43" s="63" t="s">
         <v>13</v>
@@ -3003,7 +3017,7 @@
     </row>
     <row r="44" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="53" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B44" s="62" t="s">
         <v>13</v>
@@ -3020,7 +3034,7 @@
     </row>
     <row r="45" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="54" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B45" s="63" t="s">
         <v>13</v>
@@ -3037,7 +3051,7 @@
     </row>
     <row r="46" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="53" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B46" s="62" t="s">
         <v>13</v>
@@ -3054,7 +3068,7 @@
     </row>
     <row r="47" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="54" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B47" s="59" t="s">
         <v>10</v>
@@ -3071,7 +3085,7 @@
     </row>
     <row r="48" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="53" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B48" s="56" t="s">
         <v>10</v>
@@ -3088,7 +3102,7 @@
     </row>
     <row r="49" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="54" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B49" s="59" t="s">
         <v>10</v>
@@ -3105,7 +3119,7 @@
     </row>
     <row r="50" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="53" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B50" s="62" t="s">
         <v>13</v>
@@ -3122,7 +3136,7 @@
     </row>
     <row r="51" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="55" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B51" s="59" t="s">
         <v>10</v>
@@ -3139,7 +3153,7 @@
     </row>
     <row r="52" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="15" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B52" s="16" t="s">
         <v>10</v>
@@ -3155,18 +3169,38 @@
       </c>
     </row>
     <row r="53" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="13"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
+      <c r="A53" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="B53" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C53" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D53" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E53" s="14" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="54" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="15"/>
-      <c r="B54" s="16"/>
-      <c r="C54" s="16"/>
-      <c r="D54" s="16"/>
-      <c r="E54" s="16"/>
+      <c r="A54" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="B54" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D54" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="E54" s="16" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="55" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="13"/>
@@ -6316,7 +6350,7 @@
       </c>
       <c r="B6" s="22">
         <f>COUNTA('Mii List'!A2:A200)</f>
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C6" s="22" t="s">
         <v>21</v>
@@ -6332,7 +6366,7 @@
       </c>
       <c r="C7" s="23">
         <f>B7/B6</f>
-        <v>0.6470588235294118</v>
+        <v>0.62264150943396224</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -6341,11 +6375,11 @@
       </c>
       <c r="B8" s="22">
         <f>COUNTIF('Mii List'!B2:B200,"Female")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" s="23">
         <f>B8/B6</f>
-        <v>0.31372549019607843</v>
+        <v>0.32075471698113206</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -6354,11 +6388,11 @@
       </c>
       <c r="B9" s="22">
         <f>COUNTIF('Mii List'!B2:B200,"Nonbinary")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" s="23">
         <f>B9/B6</f>
-        <v>3.9215686274509803E-2</v>
+        <v>5.6603773584905662E-2</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -6389,7 +6423,7 @@
       </c>
       <c r="C13" s="23">
         <f>B13/B6</f>
-        <v>0.6470588235294118</v>
+        <v>0.62264150943396224</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -6398,11 +6432,11 @@
       </c>
       <c r="B14" s="22">
         <f>SUM('Matching Engine'!G2:G201)</f>
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C14" s="23">
         <f>B14/B6</f>
-        <v>0.78431372549019607</v>
+        <v>0.79245283018867929</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -6411,11 +6445,11 @@
       </c>
       <c r="B15" s="22">
         <f>SUM('Matching Engine'!H2:H201)</f>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C15" s="23">
         <f>B15/B6</f>
-        <v>0.47058823529411764</v>
+        <v>0.49056603773584906</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -6428,7 +6462,7 @@
       </c>
       <c r="C16" s="26">
         <f>B16/B6</f>
-        <v>1.9607843137254902E-2</v>
+        <v>1.8867924528301886E-2</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -6450,7 +6484,7 @@
         <v>34</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -6623,7 +6657,7 @@
       </c>
       <c r="C29" s="28">
         <f>SUMPRODUCT(('Matching Engine'!K2:K201=1)*('Matching Engine'!G2:G201=1))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29" s="28">
         <f t="shared" si="0"/>
@@ -6641,7 +6675,7 @@
       </c>
       <c r="C30" s="28">
         <f>SUMPRODUCT(('Matching Engine'!J2:J201=1)*('Matching Engine'!G2:G201=1))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D30" s="28">
         <f t="shared" si="0"/>
@@ -6655,11 +6689,11 @@
       </c>
       <c r="B31" s="28">
         <f>SUMPRODUCT(('Matching Engine'!J2:J201=1)*('Matching Engine'!F2:F201=0)*('Matching Engine'!G2:G201=1)*('Matching Engine'!H2:H201=1))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C31" s="28">
         <f>SUMPRODUCT(('Matching Engine'!J2:J201=1)*('Matching Engine'!G2:G201=1))+SUMPRODUCT(('Matching Engine'!K2:K201=1)*('Matching Engine'!G2:G201=1))</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D31" s="28">
         <f t="shared" si="0"/>
@@ -6695,7 +6729,7 @@
       </c>
       <c r="C33" s="28">
         <f>SUMPRODUCT(('Matching Engine'!I2:I201=1)*('Matching Engine'!G2:G201=1))+SUMPRODUCT(('Matching Engine'!K2:K201=1)*('Matching Engine'!G2:G201=1))</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D33" s="28">
         <f t="shared" si="0"/>
@@ -6713,7 +6747,7 @@
       </c>
       <c r="C34" s="28">
         <f>SUMPRODUCT(('Matching Engine'!I2:I201=1)*('Matching Engine'!G2:G201=1))+SUMPRODUCT(('Matching Engine'!J2:J201=1)*('Matching Engine'!G2:G201=1))</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D34" s="28">
         <f t="shared" si="0"/>
@@ -6731,7 +6765,7 @@
       </c>
       <c r="C35" s="28">
         <f>SUMPRODUCT(('Matching Engine'!I2:I201=1)*('Matching Engine'!G2:G201=1))+SUMPRODUCT(('Matching Engine'!J2:J201=1)*('Matching Engine'!G2:G201=1))+SUMPRODUCT(('Matching Engine'!K2:K201=1)*('Matching Engine'!G2:G201=1))</f>
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D35" s="28">
         <f t="shared" si="0"/>
@@ -6766,7 +6800,7 @@
       </c>
       <c r="C37" s="28">
         <f>SUMPRODUCT(('Matching Engine'!K2:K201=1)*('Matching Engine'!H2:H201=1))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D37" s="28">
         <f t="shared" si="0"/>
@@ -6784,7 +6818,7 @@
       </c>
       <c r="C38" s="28">
         <f>SUMPRODUCT(('Matching Engine'!J2:J201=1)*('Matching Engine'!H2:H201=1))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D38" s="28">
         <f t="shared" si="0"/>
@@ -6798,11 +6832,11 @@
       </c>
       <c r="B39" s="28">
         <f>SUMPRODUCT(('Matching Engine'!K2:K201=1)*('Matching Engine'!F2:F201=0)*('Matching Engine'!G2:G201=1)*('Matching Engine'!H2:H201=1))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C39" s="28">
         <f>SUMPRODUCT(('Matching Engine'!J2:J201=1)*('Matching Engine'!H2:H201=1))+SUMPRODUCT(('Matching Engine'!K2:K201=1)*('Matching Engine'!H2:H201=1))</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D39" s="28">
         <f t="shared" si="0"/>
@@ -6838,7 +6872,7 @@
       </c>
       <c r="C41" s="28">
         <f>SUMPRODUCT(('Matching Engine'!I2:I201=1)*('Matching Engine'!H2:H201=1))+SUMPRODUCT(('Matching Engine'!K2:K201=1)*('Matching Engine'!H2:H201=1))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D41" s="28">
         <f t="shared" si="0"/>
@@ -6856,7 +6890,7 @@
       </c>
       <c r="C42" s="28">
         <f>SUMPRODUCT(('Matching Engine'!I2:I201=1)*('Matching Engine'!H2:H201=1))+SUMPRODUCT(('Matching Engine'!J2:J201=1)*('Matching Engine'!H2:H201=1))</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D42" s="28">
         <f t="shared" si="0"/>
@@ -6874,7 +6908,7 @@
       </c>
       <c r="C43" s="28">
         <f>SUMPRODUCT(('Matching Engine'!I2:I201=1)*('Matching Engine'!H2:H201=1))+SUMPRODUCT(('Matching Engine'!J2:J201=1)*('Matching Engine'!H2:H201=1))+SUMPRODUCT(('Matching Engine'!K2:K201=1)*('Matching Engine'!H2:H201=1))</f>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D43" s="28">
         <f t="shared" si="0"/>
@@ -6939,73 +6973,73 @@
         <f>IF(MOD(B6-B48-B49,2)=1,1,0)</f>
         <v>0</v>
       </c>
-      <c r="C50" s="39" t="s">
-        <v>68</v>
+      <c r="C50" s="67" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A51" s="41" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B51" s="42">
         <f>B48+B49+B50</f>
         <v>1</v>
       </c>
       <c r="C51" s="39" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="39" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B52" s="40">
         <f>INT((B6-B51)/2)</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C52" s="39" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="39" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B53" s="47">
         <f>(B6-B51)/B6</f>
-        <v>0.98039215686274506</v>
+        <v>0.98113207547169812</v>
       </c>
       <c r="C53" s="39" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="39" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B54" s="43" cm="1">
         <f t="array" aca="1" ref="B54" ca="1">_xlfn.LET(_xlpm.a,'Matching Engine'!N2:N51,_xlpm.b,'Matching Engine'!L2:L51,_xlpm.c,B6,_xlpm.s,'Matching Engine'!P2:P51,_xlpm.d,_xlpm.c/2,_xlpm.e,SUMPRODUCT(IF(_xlpm.b=0,1,EXP(-(_xlpm.a+_xlpm.b*_xlpm.s*_xlpm.d/_xlpm.c)))),_xlpm.f,(_xlpm.e+_xlpm.d)/2,_xlpm.g,SUMPRODUCT(IF(_xlpm.b=0,1,EXP(-(_xlpm.a+_xlpm.b*_xlpm.s*_xlpm.f/_xlpm.c)))),_xlpm.h,(_xlpm.g+_xlpm.f)/2,_xlpm.i,SUMPRODUCT(IF(_xlpm.b=0,1,EXP(-(_xlpm.a+_xlpm.b*_xlpm.s*_xlpm.h/_xlpm.c)))),_xlpm.j,(_xlpm.i+_xlpm.h)/2,_xlpm.k,SUMPRODUCT(IF(_xlpm.b=0,1,EXP(-(_xlpm.a+_xlpm.b*_xlpm.s*_xlpm.j/_xlpm.c)))),_xlpm.l,(_xlpm.k+_xlpm.j)/2,_xlpm.m,SUMPRODUCT(IF(_xlpm.b=0,1,EXP(-(_xlpm.a+_xlpm.b*_xlpm.s*_xlpm.l/_xlpm.c)))),_xlpm.n,(_xlpm.m+_xlpm.l)/2,(_xlpm.c-_xlpm.n)/2)</f>
-        <v>21.979892660010357</v>
+        <v>22.911538025831867</v>
       </c>
       <c r="C54" s="39" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="39" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B55" s="47">
         <f ca="1">B54*2/B6</f>
-        <v>0.86195657490236699</v>
+        <v>0.86458634059742889</v>
       </c>
       <c r="C55" s="39" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -7020,13 +7054,13 @@
         <v>1</v>
       </c>
       <c r="C58" s="21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D58" s="21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E58" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -7239,7 +7273,7 @@
     </row>
     <row r="70" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -7254,13 +7288,13 @@
         <v>1</v>
       </c>
       <c r="C71" s="21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D71" s="21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E71" s="21" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -7288,15 +7322,15 @@
     <row r="73" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Kanaya Maryam</v>
+        <v>Rachel</v>
       </c>
       <c r="B73" s="22" t="str">
         <f>IF(A73="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A73,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>Female</v>
+        <v>Nonbinary</v>
       </c>
       <c r="C73" s="22" t="str">
         <f>IF(A73="","",IF(AND(INDEX('Matching Engine'!F$2:F$201,MATCH(A73,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!G$2:G$201,MATCH(A73,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!H$2:H$201,MATCH(A73,'Matching Engine'!A$2:A$201,0))=0),"None",IF(INDEX('Matching Engine'!F$2:F$201,MATCH(A73,'Matching Engine'!A$2:A$201,0))=1,"♂ ","")&amp;IF(INDEX('Matching Engine'!G$2:G$201,MATCH(A73,'Matching Engine'!A$2:A$201,0))=1,"♀ ","")&amp;IF(INDEX('Matching Engine'!H$2:H$201,MATCH(A73,'Matching Engine'!A$2:A$201,0))=1,"⚧","")))</f>
-        <v xml:space="preserve">♀ </v>
+        <v>♀ ⚧</v>
       </c>
       <c r="D73" s="22">
         <f>IF(A73="","",INDEX('Matching Engine'!L$2:L$201,MATCH(A73,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7304,13 +7338,13 @@
       </c>
       <c r="E73" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>22% — 11 of 50 compatible</v>
+        <v>21% — 11 of 52 compatible</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Rose Lalonde</v>
+        <v>Kanaya Maryam</v>
       </c>
       <c r="B74" s="22" t="str">
         <f>IF(A74="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A74,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7322,21 +7356,21 @@
       </c>
       <c r="D74" s="22">
         <f>IF(A74="","",INDEX('Matching Engine'!L$2:L$201,MATCH(A74,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E74" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>22% — 11 of 50 compatible</v>
+        <v>23% — 12 of 52 compatible</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Barack Obama</v>
+        <v>Rose Lalonde</v>
       </c>
       <c r="B75" s="22" t="str">
         <f>IF(A75="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A75,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="C75" s="22" t="str">
         <f>IF(A75="","",IF(AND(INDEX('Matching Engine'!F$2:F$201,MATCH(A75,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!G$2:G$201,MATCH(A75,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!H$2:H$201,MATCH(A75,'Matching Engine'!A$2:A$201,0))=0),"None",IF(INDEX('Matching Engine'!F$2:F$201,MATCH(A75,'Matching Engine'!A$2:A$201,0))=1,"♂ ","")&amp;IF(INDEX('Matching Engine'!G$2:G$201,MATCH(A75,'Matching Engine'!A$2:A$201,0))=1,"♀ ","")&amp;IF(INDEX('Matching Engine'!H$2:H$201,MATCH(A75,'Matching Engine'!A$2:A$201,0))=1,"⚧","")))</f>
@@ -7344,17 +7378,17 @@
       </c>
       <c r="D75" s="22">
         <f>IF(A75="","",INDEX('Matching Engine'!L$2:L$201,MATCH(A75,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E75" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>28% — 14 of 50 compatible</v>
+        <v>23% — 12 of 52 compatible</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Ben</v>
+        <v>Barack Obama</v>
       </c>
       <c r="B76" s="22" t="str">
         <f>IF(A76="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A76,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7370,13 +7404,13 @@
       </c>
       <c r="E76" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>28% — 14 of 50 compatible</v>
+        <v>27% — 14 of 52 compatible</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Biff Williams</v>
+        <v>Ben</v>
       </c>
       <c r="B77" s="22" t="str">
         <f>IF(A77="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A77,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7392,13 +7426,13 @@
       </c>
       <c r="E77" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>28% — 14 of 50 compatible</v>
+        <v>27% — 14 of 52 compatible</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Bill Nye</v>
+        <v>Biff Williams</v>
       </c>
       <c r="B78" s="22" t="str">
         <f>IF(A78="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A78,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7414,13 +7448,13 @@
       </c>
       <c r="E78" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>28% — 14 of 50 compatible</v>
+        <v>27% — 14 of 52 compatible</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Bill Trinnen</v>
+        <v>Bill Nye</v>
       </c>
       <c r="B79" s="22" t="str">
         <f>IF(A79="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A79,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7436,13 +7470,13 @@
       </c>
       <c r="E79" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>28% — 14 of 50 compatible</v>
+        <v>27% — 14 of 52 compatible</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Foreman</v>
+        <v>Bill Trinnen</v>
       </c>
       <c r="B80" s="22" t="str">
         <f>IF(A80="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A80,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7458,13 +7492,13 @@
       </c>
       <c r="E80" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>28% — 14 of 50 compatible</v>
+        <v>27% — 14 of 52 compatible</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Justin Trudeau</v>
+        <v>Foreman</v>
       </c>
       <c r="B81" s="22" t="str">
         <f>IF(A81="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A81,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7480,13 +7514,13 @@
       </c>
       <c r="E81" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>28% — 14 of 50 compatible</v>
+        <v>27% — 14 of 52 compatible</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Kutner</v>
+        <v>Justin Trudeau</v>
       </c>
       <c r="B82" s="22" t="str">
         <f>IF(A82="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A82,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7502,13 +7536,13 @@
       </c>
       <c r="E82" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>28% — 14 of 50 compatible</v>
+        <v>27% — 14 of 52 compatible</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Riley Freeman</v>
+        <v>Kutner</v>
       </c>
       <c r="B83" s="22" t="str">
         <f>IF(A83="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A83,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7524,13 +7558,13 @@
       </c>
       <c r="E83" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>28% — 14 of 50 compatible</v>
+        <v>27% — 14 of 52 compatible</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Robert Freeman</v>
+        <v>Riley Freeman</v>
       </c>
       <c r="B84" s="22" t="str">
         <f>IF(A84="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A84,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7546,13 +7580,13 @@
       </c>
       <c r="E84" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>28% — 14 of 50 compatible</v>
+        <v>27% — 14 of 52 compatible</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Taub</v>
+        <v>Robert Freeman</v>
       </c>
       <c r="B85" s="22" t="str">
         <f>IF(A85="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A85,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7568,21 +7602,21 @@
       </c>
       <c r="E85" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>28% — 14 of 50 compatible</v>
+        <v>27% — 14 of 52 compatible</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Uncle Ruckus</v>
+        <v>Sophia</v>
       </c>
       <c r="B86" s="22" t="str">
         <f>IF(A86="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A86,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="C86" s="22" t="str">
         <f>IF(A86="","",IF(AND(INDEX('Matching Engine'!F$2:F$201,MATCH(A86,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!G$2:G$201,MATCH(A86,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!H$2:H$201,MATCH(A86,'Matching Engine'!A$2:A$201,0))=0),"None",IF(INDEX('Matching Engine'!F$2:F$201,MATCH(A86,'Matching Engine'!A$2:A$201,0))=1,"♂ ","")&amp;IF(INDEX('Matching Engine'!G$2:G$201,MATCH(A86,'Matching Engine'!A$2:A$201,0))=1,"♀ ","")&amp;IF(INDEX('Matching Engine'!H$2:H$201,MATCH(A86,'Matching Engine'!A$2:A$201,0))=1,"⚧","")))</f>
-        <v xml:space="preserve">♀ </v>
+        <v>♀ ⚧</v>
       </c>
       <c r="D86" s="22">
         <f>IF(A86="","",INDEX('Matching Engine'!L$2:L$201,MATCH(A86,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7590,13 +7624,13 @@
       </c>
       <c r="E86" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>28% — 14 of 50 compatible</v>
+        <v>27% — 14 of 52 compatible</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Wayward Vagabond</v>
+        <v>Taub</v>
       </c>
       <c r="B87" s="22" t="str">
         <f>IF(A87="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A87,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7612,13 +7646,13 @@
       </c>
       <c r="E87" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>28% — 14 of 50 compatible</v>
+        <v>27% — 14 of 52 compatible</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Yoshiaki Koizumi</v>
+        <v>Uncle Ruckus</v>
       </c>
       <c r="B88" s="22" t="str">
         <f>IF(A88="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A88,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7634,13 +7668,13 @@
       </c>
       <c r="E88" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>28% — 14 of 50 compatible</v>
+        <v>27% — 14 of 52 compatible</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Huey Freeman</v>
+        <v>WV</v>
       </c>
       <c r="B89" s="22" t="str">
         <f>IF(A89="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A89,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7648,21 +7682,21 @@
       </c>
       <c r="C89" s="22" t="str">
         <f>IF(A89="","",IF(AND(INDEX('Matching Engine'!F$2:F$201,MATCH(A89,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!G$2:G$201,MATCH(A89,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!H$2:H$201,MATCH(A89,'Matching Engine'!A$2:A$201,0))=0),"None",IF(INDEX('Matching Engine'!F$2:F$201,MATCH(A89,'Matching Engine'!A$2:A$201,0))=1,"♂ ","")&amp;IF(INDEX('Matching Engine'!G$2:G$201,MATCH(A89,'Matching Engine'!A$2:A$201,0))=1,"♀ ","")&amp;IF(INDEX('Matching Engine'!H$2:H$201,MATCH(A89,'Matching Engine'!A$2:A$201,0))=1,"⚧","")))</f>
-        <v>♀ ⚧</v>
+        <v xml:space="preserve">♀ </v>
       </c>
       <c r="D89" s="22">
         <f>IF(A89="","",INDEX('Matching Engine'!L$2:L$201,MATCH(A89,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E89" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>30% — 15 of 50 compatible</v>
+        <v>27% — 14 of 52 compatible</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Chuck</v>
+        <v>Yoshiaki Koizumi</v>
       </c>
       <c r="B90" s="22" t="str">
         <f>IF(A90="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A90,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7670,21 +7704,21 @@
       </c>
       <c r="C90" s="22" t="str">
         <f>IF(A90="","",IF(AND(INDEX('Matching Engine'!F$2:F$201,MATCH(A90,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!G$2:G$201,MATCH(A90,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!H$2:H$201,MATCH(A90,'Matching Engine'!A$2:A$201,0))=0),"None",IF(INDEX('Matching Engine'!F$2:F$201,MATCH(A90,'Matching Engine'!A$2:A$201,0))=1,"♂ ","")&amp;IF(INDEX('Matching Engine'!G$2:G$201,MATCH(A90,'Matching Engine'!A$2:A$201,0))=1,"♀ ","")&amp;IF(INDEX('Matching Engine'!H$2:H$201,MATCH(A90,'Matching Engine'!A$2:A$201,0))=1,"⚧","")))</f>
-        <v xml:space="preserve">♂ </v>
+        <v xml:space="preserve">♀ </v>
       </c>
       <c r="D90" s="22">
         <f>IF(A90="","",INDEX('Matching Engine'!L$2:L$201,MATCH(A90,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E90" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>34% — 17 of 50 compatible</v>
+        <v>27% — 14 of 52 compatible</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>House</v>
+        <v>Huey Freeman</v>
       </c>
       <c r="B91" s="22" t="str">
         <f>IF(A91="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A91,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7692,21 +7726,21 @@
       </c>
       <c r="C91" s="22" t="str">
         <f>IF(A91="","",IF(AND(INDEX('Matching Engine'!F$2:F$201,MATCH(A91,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!G$2:G$201,MATCH(A91,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!H$2:H$201,MATCH(A91,'Matching Engine'!A$2:A$201,0))=0),"None",IF(INDEX('Matching Engine'!F$2:F$201,MATCH(A91,'Matching Engine'!A$2:A$201,0))=1,"♂ ","")&amp;IF(INDEX('Matching Engine'!G$2:G$201,MATCH(A91,'Matching Engine'!A$2:A$201,0))=1,"♀ ","")&amp;IF(INDEX('Matching Engine'!H$2:H$201,MATCH(A91,'Matching Engine'!A$2:A$201,0))=1,"⚧","")))</f>
-        <v xml:space="preserve">♂ </v>
+        <v>♀ ⚧</v>
       </c>
       <c r="D91" s="22">
         <f>IF(A91="","",INDEX('Matching Engine'!L$2:L$201,MATCH(A91,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E91" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>34% — 17 of 50 compatible</v>
+        <v>29% — 15 of 52 compatible</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Larry</v>
+        <v>Chuck</v>
       </c>
       <c r="B92" s="22" t="str">
         <f>IF(A92="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A92,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7722,13 +7756,13 @@
       </c>
       <c r="E92" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>34% — 17 of 50 compatible</v>
+        <v>33% — 17 of 52 compatible</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Morty</v>
+        <v>House</v>
       </c>
       <c r="B93" s="22" t="str">
         <f>IF(A93="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A93,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7744,13 +7778,13 @@
       </c>
       <c r="E93" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>34% — 17 of 50 compatible</v>
+        <v>33% — 17 of 52 compatible</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Wilson</v>
+        <v>Larry</v>
       </c>
       <c r="B94" s="22" t="str">
         <f>IF(A94="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A94,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7766,13 +7800,13 @@
       </c>
       <c r="E94" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>34% — 17 of 50 compatible</v>
+        <v>33% — 17 of 52 compatible</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Alvie</v>
+        <v>Morty</v>
       </c>
       <c r="B95" s="22" t="str">
         <f>IF(A95="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A95,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7780,87 +7814,87 @@
       </c>
       <c r="C95" s="22" t="str">
         <f>IF(A95="","",IF(AND(INDEX('Matching Engine'!F$2:F$201,MATCH(A95,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!G$2:G$201,MATCH(A95,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!H$2:H$201,MATCH(A95,'Matching Engine'!A$2:A$201,0))=0),"None",IF(INDEX('Matching Engine'!F$2:F$201,MATCH(A95,'Matching Engine'!A$2:A$201,0))=1,"♂ ","")&amp;IF(INDEX('Matching Engine'!G$2:G$201,MATCH(A95,'Matching Engine'!A$2:A$201,0))=1,"♀ ","")&amp;IF(INDEX('Matching Engine'!H$2:H$201,MATCH(A95,'Matching Engine'!A$2:A$201,0))=1,"⚧","")))</f>
-        <v>♂ ⚧</v>
+        <v xml:space="preserve">♂ </v>
       </c>
       <c r="D95" s="22">
         <f>IF(A95="","",INDEX('Matching Engine'!L$2:L$201,MATCH(A95,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E95" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>36% — 18 of 50 compatible</v>
+        <v>33% — 17 of 52 compatible</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Robin</v>
+        <v>Wilson</v>
       </c>
       <c r="B96" s="22" t="str">
         <f>IF(A96="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A96,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>Nonbinary</v>
+        <v>Male</v>
       </c>
       <c r="C96" s="22" t="str">
         <f>IF(A96="","",IF(AND(INDEX('Matching Engine'!F$2:F$201,MATCH(A96,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!G$2:G$201,MATCH(A96,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!H$2:H$201,MATCH(A96,'Matching Engine'!A$2:A$201,0))=0),"None",IF(INDEX('Matching Engine'!F$2:F$201,MATCH(A96,'Matching Engine'!A$2:A$201,0))=1,"♂ ","")&amp;IF(INDEX('Matching Engine'!G$2:G$201,MATCH(A96,'Matching Engine'!A$2:A$201,0))=1,"♀ ","")&amp;IF(INDEX('Matching Engine'!H$2:H$201,MATCH(A96,'Matching Engine'!A$2:A$201,0))=1,"⚧","")))</f>
-        <v>♂ ♀ ⚧</v>
+        <v xml:space="preserve">♂ </v>
       </c>
       <c r="D96" s="22">
         <f>IF(A96="","",INDEX('Matching Engine'!L$2:L$201,MATCH(A96,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E96" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>46% — 23 of 50 compatible</v>
+        <v>33% — 17 of 52 compatible</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Bea</v>
+        <v>Alvie</v>
       </c>
       <c r="B97" s="22" t="str">
         <f>IF(A97="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A97,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="C97" s="22" t="str">
         <f>IF(A97="","",IF(AND(INDEX('Matching Engine'!F$2:F$201,MATCH(A97,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!G$2:G$201,MATCH(A97,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!H$2:H$201,MATCH(A97,'Matching Engine'!A$2:A$201,0))=0),"None",IF(INDEX('Matching Engine'!F$2:F$201,MATCH(A97,'Matching Engine'!A$2:A$201,0))=1,"♂ ","")&amp;IF(INDEX('Matching Engine'!G$2:G$201,MATCH(A97,'Matching Engine'!A$2:A$201,0))=1,"♀ ","")&amp;IF(INDEX('Matching Engine'!H$2:H$201,MATCH(A97,'Matching Engine'!A$2:A$201,0))=1,"⚧","")))</f>
-        <v xml:space="preserve">♂ </v>
+        <v>♂ ⚧</v>
       </c>
       <c r="D97" s="22">
         <f>IF(A97="","",INDEX('Matching Engine'!L$2:L$201,MATCH(A97,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E97" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>54% — 27 of 50 compatible</v>
+        <v>35% — 18 of 52 compatible</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Cameron</v>
+        <v>Robin</v>
       </c>
       <c r="B98" s="22" t="str">
         <f>IF(A98="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A98,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>Female</v>
+        <v>Nonbinary</v>
       </c>
       <c r="C98" s="22" t="str">
         <f>IF(A98="","",IF(AND(INDEX('Matching Engine'!F$2:F$201,MATCH(A98,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!G$2:G$201,MATCH(A98,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!H$2:H$201,MATCH(A98,'Matching Engine'!A$2:A$201,0))=0),"None",IF(INDEX('Matching Engine'!F$2:F$201,MATCH(A98,'Matching Engine'!A$2:A$201,0))=1,"♂ ","")&amp;IF(INDEX('Matching Engine'!G$2:G$201,MATCH(A98,'Matching Engine'!A$2:A$201,0))=1,"♀ ","")&amp;IF(INDEX('Matching Engine'!H$2:H$201,MATCH(A98,'Matching Engine'!A$2:A$201,0))=1,"⚧","")))</f>
-        <v xml:space="preserve">♂ </v>
+        <v>♂ ♀ ⚧</v>
       </c>
       <c r="D98" s="22">
         <f>IF(A98="","",INDEX('Matching Engine'!L$2:L$201,MATCH(A98,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E98" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>54% — 27 of 50 compatible</v>
+        <v>48% — 25 of 52 compatible</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Cuddy</v>
+        <v>Bea</v>
       </c>
       <c r="B99" s="22" t="str">
         <f>IF(A99="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A99,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7876,13 +7910,13 @@
       </c>
       <c r="E99" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>54% — 27 of 50 compatible</v>
+        <v>52% — 27 of 52 compatible</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Katy Perry</v>
+        <v>Cameron</v>
       </c>
       <c r="B100" s="22" t="str">
         <f>IF(A100="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A100,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7898,57 +7932,57 @@
       </c>
       <c r="E100" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>54% — 27 of 50 compatible</v>
+        <v>52% — 27 of 52 compatible</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Chase</v>
+        <v>Cuddy</v>
       </c>
       <c r="B101" s="22" t="str">
         <f>IF(A101="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A101,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="C101" s="22" t="str">
         <f>IF(A101="","",IF(AND(INDEX('Matching Engine'!F$2:F$201,MATCH(A101,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!G$2:G$201,MATCH(A101,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!H$2:H$201,MATCH(A101,'Matching Engine'!A$2:A$201,0))=0),"None",IF(INDEX('Matching Engine'!F$2:F$201,MATCH(A101,'Matching Engine'!A$2:A$201,0))=1,"♂ ","")&amp;IF(INDEX('Matching Engine'!G$2:G$201,MATCH(A101,'Matching Engine'!A$2:A$201,0))=1,"♀ ","")&amp;IF(INDEX('Matching Engine'!H$2:H$201,MATCH(A101,'Matching Engine'!A$2:A$201,0))=1,"⚧","")))</f>
-        <v>♂ ♀ ⚧</v>
+        <v xml:space="preserve">♂ </v>
       </c>
       <c r="D101" s="22">
         <f>IF(A101="","",INDEX('Matching Engine'!L$2:L$201,MATCH(A101,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E101" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>64% — 32 of 50 compatible</v>
+        <v>52% — 27 of 52 compatible</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Dave Strider</v>
+        <v>Katy Perry</v>
       </c>
       <c r="B102" s="22" t="str">
         <f>IF(A102="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A102,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>Male</v>
+        <v>Female</v>
       </c>
       <c r="C102" s="22" t="str">
         <f>IF(A102="","",IF(AND(INDEX('Matching Engine'!F$2:F$201,MATCH(A102,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!G$2:G$201,MATCH(A102,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!H$2:H$201,MATCH(A102,'Matching Engine'!A$2:A$201,0))=0),"None",IF(INDEX('Matching Engine'!F$2:F$201,MATCH(A102,'Matching Engine'!A$2:A$201,0))=1,"♂ ","")&amp;IF(INDEX('Matching Engine'!G$2:G$201,MATCH(A102,'Matching Engine'!A$2:A$201,0))=1,"♀ ","")&amp;IF(INDEX('Matching Engine'!H$2:H$201,MATCH(A102,'Matching Engine'!A$2:A$201,0))=1,"⚧","")))</f>
-        <v>♂ ♀ ⚧</v>
+        <v xml:space="preserve">♂ </v>
       </c>
       <c r="D102" s="22">
         <f>IF(A102="","",INDEX('Matching Engine'!L$2:L$201,MATCH(A102,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E102" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>64% — 32 of 50 compatible</v>
+        <v>52% — 27 of 52 compatible</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Equius Zahhak</v>
+        <v>Chase</v>
       </c>
       <c r="B103" s="22" t="str">
         <f>IF(A103="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A103,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7964,13 +7998,13 @@
       </c>
       <c r="E103" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>64% — 32 of 50 compatible</v>
+        <v>62% — 32 of 52 compatible</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Eridan Ampora</v>
+        <v>Dave Strider</v>
       </c>
       <c r="B104" s="22" t="str">
         <f>IF(A104="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A104,'Matching Engine'!A$2:A$201,0)))</f>
@@ -7986,13 +8020,13 @@
       </c>
       <c r="E104" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>64% — 32 of 50 compatible</v>
+        <v>62% — 32 of 52 compatible</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Gamzee Makara</v>
+        <v>Equius Zahhak</v>
       </c>
       <c r="B105" s="22" t="str">
         <f>IF(A105="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A105,'Matching Engine'!A$2:A$201,0)))</f>
@@ -8008,13 +8042,13 @@
       </c>
       <c r="E105" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>64% — 32 of 50 compatible</v>
+        <v>62% — 32 of 52 compatible</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Hugh Morris</v>
+        <v>Eridan Ampora</v>
       </c>
       <c r="B106" s="22" t="str">
         <f>IF(A106="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A106,'Matching Engine'!A$2:A$201,0)))</f>
@@ -8030,13 +8064,13 @@
       </c>
       <c r="E106" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>64% — 32 of 50 compatible</v>
+        <v>62% — 32 of 52 compatible</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Jason Speer</v>
+        <v>Gamzee Makara</v>
       </c>
       <c r="B107" s="22" t="str">
         <f>IF(A107="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A107,'Matching Engine'!A$2:A$201,0)))</f>
@@ -8052,13 +8086,13 @@
       </c>
       <c r="E107" s="22" t="str">
         <f t="shared" ref="E107:E138" si="3">IF(A107="","",IF(D107=0,"0% — no compatible partners",TEXT(D107/($B$6-1),"0%")&amp;" — "&amp;D107&amp;" of "&amp;($B$6-1)&amp;" compatible"))</f>
-        <v>64% — 32 of 50 compatible</v>
+        <v>62% — 32 of 52 compatible</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Karkat Vantas</v>
+        <v>Hugh Morris</v>
       </c>
       <c r="B108" s="22" t="str">
         <f>IF(A108="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A108,'Matching Engine'!A$2:A$201,0)))</f>
@@ -8074,13 +8108,13 @@
       </c>
       <c r="E108" s="22" t="str">
         <f t="shared" si="3"/>
-        <v>64% — 32 of 50 compatible</v>
+        <v>62% — 32 of 52 compatible</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Michael Newman</v>
+        <v>Jason Speer</v>
       </c>
       <c r="B109" s="22" t="str">
         <f>IF(A109="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A109,'Matching Engine'!A$2:A$201,0)))</f>
@@ -8096,13 +8130,13 @@
       </c>
       <c r="E109" s="22" t="str">
         <f t="shared" si="3"/>
-        <v>64% — 32 of 50 compatible</v>
+        <v>62% — 32 of 52 compatible</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Randy Sexton</v>
+        <v>Karkat Vantas</v>
       </c>
       <c r="B110" s="22" t="str">
         <f>IF(A110="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A110,'Matching Engine'!A$2:A$201,0)))</f>
@@ -8118,13 +8152,13 @@
       </c>
       <c r="E110" s="22" t="str">
         <f t="shared" si="3"/>
-        <v>64% — 32 of 50 compatible</v>
+        <v>62% — 32 of 52 compatible</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Sollux Captor</v>
+        <v>Michael Newman</v>
       </c>
       <c r="B111" s="22" t="str">
         <f>IF(A111="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A111,'Matching Engine'!A$2:A$201,0)))</f>
@@ -8140,13 +8174,13 @@
       </c>
       <c r="E111" s="22" t="str">
         <f t="shared" si="3"/>
-        <v>64% — 32 of 50 compatible</v>
+        <v>62% — 32 of 52 compatible</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Tavros Nitram</v>
+        <v>Randy Sexton</v>
       </c>
       <c r="B112" s="22" t="str">
         <f>IF(A112="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A112,'Matching Engine'!A$2:A$201,0)))</f>
@@ -8162,39 +8196,39 @@
       </c>
       <c r="E112" s="22" t="str">
         <f t="shared" si="3"/>
-        <v>64% — 32 of 50 compatible</v>
+        <v>62% — 32 of 52 compatible</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Thirteen</v>
+        <v>Sollux Captor</v>
       </c>
       <c r="B113" s="22" t="str">
         <f>IF(A113="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A113,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="C113" s="22" t="str">
         <f>IF(A113="","",IF(AND(INDEX('Matching Engine'!F$2:F$201,MATCH(A113,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!G$2:G$201,MATCH(A113,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!H$2:H$201,MATCH(A113,'Matching Engine'!A$2:A$201,0))=0),"None",IF(INDEX('Matching Engine'!F$2:F$201,MATCH(A113,'Matching Engine'!A$2:A$201,0))=1,"♂ ","")&amp;IF(INDEX('Matching Engine'!G$2:G$201,MATCH(A113,'Matching Engine'!A$2:A$201,0))=1,"♀ ","")&amp;IF(INDEX('Matching Engine'!H$2:H$201,MATCH(A113,'Matching Engine'!A$2:A$201,0))=1,"⚧","")))</f>
-        <v xml:space="preserve">♂ ♀ </v>
+        <v>♂ ♀ ⚧</v>
       </c>
       <c r="D113" s="22">
         <f>IF(A113="","",INDEX('Matching Engine'!L$2:L$201,MATCH(A113,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E113" s="22" t="str">
         <f t="shared" si="3"/>
-        <v>76% — 38 of 50 compatible</v>
+        <v>62% — 32 of 52 compatible</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Aradia Megido</v>
+        <v>Tavros Nitram</v>
       </c>
       <c r="B114" s="22" t="str">
         <f>IF(A114="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A114,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>Female</v>
+        <v>Male</v>
       </c>
       <c r="C114" s="22" t="str">
         <f>IF(A114="","",IF(AND(INDEX('Matching Engine'!F$2:F$201,MATCH(A114,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!G$2:G$201,MATCH(A114,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!H$2:H$201,MATCH(A114,'Matching Engine'!A$2:A$201,0))=0),"None",IF(INDEX('Matching Engine'!F$2:F$201,MATCH(A114,'Matching Engine'!A$2:A$201,0))=1,"♂ ","")&amp;IF(INDEX('Matching Engine'!G$2:G$201,MATCH(A114,'Matching Engine'!A$2:A$201,0))=1,"♀ ","")&amp;IF(INDEX('Matching Engine'!H$2:H$201,MATCH(A114,'Matching Engine'!A$2:A$201,0))=1,"⚧","")))</f>
@@ -8202,17 +8236,17 @@
       </c>
       <c r="D114" s="22">
         <f>IF(A114="","",INDEX('Matching Engine'!L$2:L$201,MATCH(A114,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E114" s="22" t="str">
         <f t="shared" si="3"/>
-        <v>78% — 39 of 50 compatible</v>
+        <v>62% — 32 of 52 compatible</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Dr. Winters</v>
+        <v>Thirteen</v>
       </c>
       <c r="B115" s="22" t="str">
         <f>IF(A115="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A115,'Matching Engine'!A$2:A$201,0)))</f>
@@ -8220,7 +8254,7 @@
       </c>
       <c r="C115" s="22" t="str">
         <f>IF(A115="","",IF(AND(INDEX('Matching Engine'!F$2:F$201,MATCH(A115,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!G$2:G$201,MATCH(A115,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!H$2:H$201,MATCH(A115,'Matching Engine'!A$2:A$201,0))=0),"None",IF(INDEX('Matching Engine'!F$2:F$201,MATCH(A115,'Matching Engine'!A$2:A$201,0))=1,"♂ ","")&amp;IF(INDEX('Matching Engine'!G$2:G$201,MATCH(A115,'Matching Engine'!A$2:A$201,0))=1,"♀ ","")&amp;IF(INDEX('Matching Engine'!H$2:H$201,MATCH(A115,'Matching Engine'!A$2:A$201,0))=1,"⚧","")))</f>
-        <v>♂ ♀ ⚧</v>
+        <v xml:space="preserve">♂ ♀ </v>
       </c>
       <c r="D115" s="22">
         <f>IF(A115="","",INDEX('Matching Engine'!L$2:L$201,MATCH(A115,'Matching Engine'!A$2:A$201,0)))</f>
@@ -8228,13 +8262,13 @@
       </c>
       <c r="E115" s="22" t="str">
         <f t="shared" si="3"/>
-        <v>78% — 39 of 50 compatible</v>
+        <v>75% — 39 of 52 compatible</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Feferi Peixes</v>
+        <v>Aradia Megido</v>
       </c>
       <c r="B116" s="22" t="str">
         <f>IF(A116="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A116,'Matching Engine'!A$2:A$201,0)))</f>
@@ -8246,17 +8280,17 @@
       </c>
       <c r="D116" s="22">
         <f>IF(A116="","",INDEX('Matching Engine'!L$2:L$201,MATCH(A116,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E116" s="22" t="str">
         <f t="shared" si="3"/>
-        <v>78% — 39 of 50 compatible</v>
+        <v>79% — 41 of 52 compatible</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Jade Harley</v>
+        <v>Dr. Winters</v>
       </c>
       <c r="B117" s="22" t="str">
         <f>IF(A117="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A117,'Matching Engine'!A$2:A$201,0)))</f>
@@ -8268,17 +8302,17 @@
       </c>
       <c r="D117" s="22">
         <f>IF(A117="","",INDEX('Matching Engine'!L$2:L$201,MATCH(A117,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E117" s="22" t="str">
         <f t="shared" si="3"/>
-        <v>78% — 39 of 50 compatible</v>
+        <v>79% — 41 of 52 compatible</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>June Egbert</v>
+        <v>Feferi Peixes</v>
       </c>
       <c r="B118" s="22" t="str">
         <f>IF(A118="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A118,'Matching Engine'!A$2:A$201,0)))</f>
@@ -8290,17 +8324,17 @@
       </c>
       <c r="D118" s="22">
         <f>IF(A118="","",INDEX('Matching Engine'!L$2:L$201,MATCH(A118,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E118" s="22" t="str">
         <f t="shared" si="3"/>
-        <v>78% — 39 of 50 compatible</v>
+        <v>79% — 41 of 52 compatible</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Nepeta Leijon</v>
+        <v>Jade Harley</v>
       </c>
       <c r="B119" s="22" t="str">
         <f>IF(A119="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A119,'Matching Engine'!A$2:A$201,0)))</f>
@@ -8312,17 +8346,17 @@
       </c>
       <c r="D119" s="22">
         <f>IF(A119="","",INDEX('Matching Engine'!L$2:L$201,MATCH(A119,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E119" s="22" t="str">
         <f t="shared" si="3"/>
-        <v>78% — 39 of 50 compatible</v>
+        <v>79% — 41 of 52 compatible</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-71,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v>Nikki</v>
+        <v>June Egbert</v>
       </c>
       <c r="B120" s="22" t="str">
         <f>IF(A120="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A120,'Matching Engine'!A$2:A$201,0)))</f>
@@ -8334,33 +8368,33 @@
       </c>
       <c r="D120" s="22">
         <f>IF(A120="","",INDEX('Matching Engine'!L$2:L$201,MATCH(A120,'Matching Engine'!A$2:A$201,0)))</f>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E120" s="22" t="str">
         <f t="shared" si="3"/>
-        <v>78% — 39 of 50 compatible</v>
+        <v>79% — 41 of 52 compatible</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="32" t="str">
         <f>IFERROR(INDEX('Matching Engine'!A$2:A$201,MATCH(ROW()-68,'Matching Engine'!M$2:M$201,0)),"")</f>
-        <v/>
+        <v>Vriska Serket</v>
       </c>
       <c r="B121" s="22" t="str">
         <f>IF(A121="","",INDEX('Matching Engine'!B$2:B$201,MATCH(A121,'Matching Engine'!A$2:A$201,0)))</f>
-        <v/>
+        <v>Female</v>
       </c>
       <c r="C121" s="22" t="str">
         <f>IF(A121="","",IF(AND(INDEX('Matching Engine'!F$2:F$201,MATCH(A121,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!G$2:G$201,MATCH(A121,'Matching Engine'!A$2:A$201,0))=0,INDEX('Matching Engine'!H$2:H$201,MATCH(A121,'Matching Engine'!A$2:A$201,0))=0),"None",IF(INDEX('Matching Engine'!F$2:F$201,MATCH(A121,'Matching Engine'!A$2:A$201,0))=1,"♂ ","")&amp;IF(INDEX('Matching Engine'!G$2:G$201,MATCH(A121,'Matching Engine'!A$2:A$201,0))=1,"♀ ","")&amp;IF(INDEX('Matching Engine'!H$2:H$201,MATCH(A121,'Matching Engine'!A$2:A$201,0))=1,"⚧","")))</f>
-        <v/>
-      </c>
-      <c r="D121" s="22" t="str">
+        <v>♂ ♀ ⚧</v>
+      </c>
+      <c r="D121" s="22">
         <f>IF(A121="","",INDEX('Matching Engine'!L$2:L$201,MATCH(A121,'Matching Engine'!A$2:A$201,0)))</f>
-        <v/>
+        <v>41</v>
       </c>
       <c r="E121" s="22" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>79% — 41 of 52 compatible</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -9860,46 +9894,46 @@
         <v>1</v>
       </c>
       <c r="C1" s="45" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="45" t="s">
         <v>78</v>
       </c>
-      <c r="D1" s="45" t="s">
+      <c r="E1" s="45" t="s">
         <v>79</v>
       </c>
-      <c r="E1" s="45" t="s">
+      <c r="F1" s="45" t="s">
         <v>80</v>
       </c>
-      <c r="F1" s="45" t="s">
+      <c r="G1" s="45" t="s">
         <v>81</v>
       </c>
-      <c r="G1" s="45" t="s">
+      <c r="H1" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="H1" s="45" t="s">
+      <c r="I1" s="45" t="s">
         <v>83</v>
       </c>
-      <c r="I1" s="45" t="s">
+      <c r="J1" s="45" t="s">
         <v>84</v>
       </c>
-      <c r="J1" s="45" t="s">
+      <c r="K1" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="K1" s="45" t="s">
+      <c r="L1" s="45" t="s">
+        <v>74</v>
+      </c>
+      <c r="M1" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="L1" s="45" t="s">
-        <v>75</v>
-      </c>
-      <c r="M1" s="45" t="s">
-        <v>87</v>
-      </c>
       <c r="N1" s="45" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O1" s="45" t="s">
+        <v>94</v>
+      </c>
+      <c r="P1" s="45" t="s">
         <v>95</v>
-      </c>
-      <c r="P1" s="45" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:16" s="31" customFormat="1" x14ac:dyDescent="0.35">
@@ -9949,23 +9983,23 @@
       </c>
       <c r="L2" s="46" cm="1">
         <f t="array" ref="L2">IF(A2="",0,SUMPRODUCT((A$2:A$201&lt;&gt;"")*((F$2:F$201*I2+G$2:G$201*J2+H$2:H$201*K2)&gt;0)*((F2*I$2:I$201+G2*J$2:J$201+H2*K$2:K$201)&gt;0))-IF(F2*I2+G2*J2+H2*K2&gt;0,1,0))</f>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M2" s="46" cm="1">
         <f t="array" ref="M2">IF(A2="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L2))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L2)*(A$2:A$201&lt;A2))+1)</f>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N2" s="46" cm="1">
         <f t="array" aca="1" ref="N2" ca="1">IF(A2="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I2+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J2+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K2)&gt;0)*((F2*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G2*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H2*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>0.72799145299145307</v>
+        <v>0.87907207968183587</v>
       </c>
       <c r="O2" s="46" cm="1">
         <f t="array" aca="1" ref="O2" ca="1">IF(A2="","",IF(L2=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I2+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J2+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K2)&gt;0)*((F2*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G2*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H2*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L2))</f>
-        <v>33.391304347826086</v>
+        <v>32.44</v>
       </c>
       <c r="P2" s="46">
         <f ca="1">IF(A2="","",IF(L2*O2&gt;0,MIN(1,L2/O2),0))</f>
-        <v>0.68880208333333337</v>
+        <v>0.7706535141800247</v>
       </c>
     </row>
     <row r="3" spans="1:16" s="31" customFormat="1" x14ac:dyDescent="0.35">
@@ -10085,19 +10119,19 @@
       </c>
       <c r="M4" s="46" cm="1">
         <f t="array" ref="M4">IF(A4="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L4))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L4)*(A$2:A$201&lt;A4))+1)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N4" s="46" cm="1">
         <f t="array" aca="1" ref="N4" ca="1">IF(A4="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I4+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J4+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K4)&gt;0)*((F4*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G4*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H4*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>0.40523316839106321</v>
+        <v>0.3933013689111251</v>
       </c>
       <c r="O4" s="46" cm="1">
         <f t="array" aca="1" ref="O4" ca="1">IF(A4="","",IF(L4=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I4+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J4+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K4)&gt;0)*((F4*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G4*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H4*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L4))</f>
-        <v>35.5</v>
+        <v>36.857142857142854</v>
       </c>
       <c r="P4" s="46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.39436619718309857</v>
+        <v>0.37984496124031009</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.35">
@@ -10151,15 +10185,15 @@
       </c>
       <c r="M5" s="46" cm="1">
         <f t="array" ref="M5">IF(A5="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L5))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L5)*(A$2:A$201&lt;A5))+1)</f>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="N5" s="46" cm="1">
         <f t="array" aca="1" ref="N5" ca="1">IF(A5="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I5+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J5+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K5)&gt;0)*((F5*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G5*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H5*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.1421346318750076</v>
+        <v>1.1267245715255043</v>
       </c>
       <c r="O5" s="46" cm="1">
         <f t="array" aca="1" ref="O5" ca="1">IF(A5="","",IF(L5=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I5+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J5+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K5)&gt;0)*((F5*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G5*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H5*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L5))</f>
-        <v>30.46875</v>
+        <v>31.125</v>
       </c>
       <c r="P5" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -10217,19 +10251,19 @@
       </c>
       <c r="M6" s="46" cm="1">
         <f t="array" ref="M6">IF(A6="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L6))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L6)*(A$2:A$201&lt;A6))+1)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N6" s="46" cm="1">
         <f t="array" aca="1" ref="N6" ca="1">IF(A6="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I6+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J6+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K6)&gt;0)*((F6*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G6*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H6*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>0.40523316839106321</v>
+        <v>0.3933013689111251</v>
       </c>
       <c r="O6" s="46" cm="1">
         <f t="array" aca="1" ref="O6" ca="1">IF(A6="","",IF(L6=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I6+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J6+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K6)&gt;0)*((F6*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G6*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H6*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L6))</f>
-        <v>35.5</v>
+        <v>36.857142857142854</v>
       </c>
       <c r="P6" s="46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.39436619718309857</v>
+        <v>0.37984496124031009</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.35">
@@ -10283,15 +10317,15 @@
       </c>
       <c r="M7" s="46" cm="1">
         <f t="array" ref="M7">IF(A7="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L7))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L7)*(A$2:A$201&lt;A7))+1)</f>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="N7" s="46" cm="1">
         <f t="array" aca="1" ref="N7" ca="1">IF(A7="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I7+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J7+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K7)&gt;0)*((F7*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G7*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H7*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.1421346318750076</v>
+        <v>1.1267245715255043</v>
       </c>
       <c r="O7" s="46" cm="1">
         <f t="array" aca="1" ref="O7" ca="1">IF(A7="","",IF(L7=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I7+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J7+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K7)&gt;0)*((F7*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G7*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H7*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L7))</f>
-        <v>30.46875</v>
+        <v>31.125</v>
       </c>
       <c r="P7" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -10349,7 +10383,7 @@
       </c>
       <c r="M8" s="46" cm="1">
         <f t="array" ref="M8">IF(A8="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L8))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L8)*(A$2:A$201&lt;A8))+1)</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N8" s="46" cm="1">
         <f t="array" aca="1" ref="N8" ca="1">IF(A8="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I8+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J8+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K8)&gt;0)*((F8*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G8*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H8*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
@@ -10415,19 +10449,19 @@
       </c>
       <c r="M9" s="46" cm="1">
         <f t="array" ref="M9">IF(A9="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L9))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L9)*(A$2:A$201&lt;A9))+1)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N9" s="46" cm="1">
         <f t="array" aca="1" ref="N9" ca="1">IF(A9="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I9+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J9+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K9)&gt;0)*((F9*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G9*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H9*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>0.40523316839106321</v>
+        <v>0.3933013689111251</v>
       </c>
       <c r="O9" s="46" cm="1">
         <f t="array" aca="1" ref="O9" ca="1">IF(A9="","",IF(L9=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I9+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J9+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K9)&gt;0)*((F9*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G9*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H9*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L9))</f>
-        <v>35.5</v>
+        <v>36.857142857142854</v>
       </c>
       <c r="P9" s="46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.39436619718309857</v>
+        <v>0.37984496124031009</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.35">
@@ -10481,7 +10515,7 @@
       </c>
       <c r="M10" s="46" cm="1">
         <f t="array" ref="M10">IF(A10="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L10))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L10)*(A$2:A$201&lt;A10))+1)</f>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="N10" s="46" cm="1">
         <f t="array" aca="1" ref="N10" ca="1">IF(A10="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I10+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J10+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K10)&gt;0)*((F10*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G10*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H10*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
@@ -10547,19 +10581,19 @@
       </c>
       <c r="M11" s="46" cm="1">
         <f t="array" ref="M11">IF(A11="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L11))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L11)*(A$2:A$201&lt;A11))+1)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N11" s="46" cm="1">
         <f t="array" aca="1" ref="N11" ca="1">IF(A11="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I11+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J11+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K11)&gt;0)*((F11*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G11*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H11*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>0.40523316839106321</v>
+        <v>0.3933013689111251</v>
       </c>
       <c r="O11" s="46" cm="1">
         <f t="array" aca="1" ref="O11" ca="1">IF(A11="","",IF(L11=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I11+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J11+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K11)&gt;0)*((F11*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G11*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H11*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L11))</f>
-        <v>35.5</v>
+        <v>36.857142857142854</v>
       </c>
       <c r="P11" s="46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.39436619718309857</v>
+        <v>0.37984496124031009</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.35">
@@ -10613,19 +10647,19 @@
       </c>
       <c r="M12" s="46" cm="1">
         <f t="array" ref="M12">IF(A12="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L12))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L12)*(A$2:A$201&lt;A12))+1)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N12" s="46" cm="1">
         <f t="array" aca="1" ref="N12" ca="1">IF(A12="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I12+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J12+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K12)&gt;0)*((F12*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G12*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H12*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>0.40523316839106321</v>
+        <v>0.3933013689111251</v>
       </c>
       <c r="O12" s="46" cm="1">
         <f t="array" aca="1" ref="O12" ca="1">IF(A12="","",IF(L12=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I12+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J12+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K12)&gt;0)*((F12*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G12*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H12*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L12))</f>
-        <v>35.5</v>
+        <v>36.857142857142854</v>
       </c>
       <c r="P12" s="46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.39436619718309857</v>
+        <v>0.37984496124031009</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.35">
@@ -10679,7 +10713,7 @@
       </c>
       <c r="M13" s="46" cm="1">
         <f t="array" ref="M13">IF(A13="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L13))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L13)*(A$2:A$201&lt;A13))+1)</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N13" s="46" cm="1">
         <f t="array" aca="1" ref="N13" ca="1">IF(A13="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I13+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J13+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K13)&gt;0)*((F13*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G13*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H13*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
@@ -10745,7 +10779,7 @@
       </c>
       <c r="M14" s="46" cm="1">
         <f t="array" ref="M14">IF(A14="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L14))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L14)*(A$2:A$201&lt;A14))+1)</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N14" s="46" cm="1">
         <f t="array" aca="1" ref="N14" ca="1">IF(A14="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I14+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J14+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K14)&gt;0)*((F14*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G14*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H14*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
@@ -10811,7 +10845,7 @@
       </c>
       <c r="M15" s="46" cm="1">
         <f t="array" ref="M15">IF(A15="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L15))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L15)*(A$2:A$201&lt;A15))+1)</f>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N15" s="46" cm="1">
         <f t="array" aca="1" ref="N15" ca="1">IF(A15="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I15+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J15+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K15)&gt;0)*((F15*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G15*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H15*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
@@ -10877,7 +10911,7 @@
       </c>
       <c r="M16" s="46" cm="1">
         <f t="array" ref="M16">IF(A16="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L16))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L16)*(A$2:A$201&lt;A16))+1)</f>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="N16" s="46" cm="1">
         <f t="array" aca="1" ref="N16" ca="1">IF(A16="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I16+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J16+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K16)&gt;0)*((F16*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G16*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H16*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
@@ -10943,7 +10977,7 @@
       </c>
       <c r="M17" s="46" cm="1">
         <f t="array" ref="M17">IF(A17="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L17))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L17)*(A$2:A$201&lt;A17))+1)</f>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="N17" s="46" cm="1">
         <f t="array" aca="1" ref="N17" ca="1">IF(A17="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I17+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J17+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K17)&gt;0)*((F17*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G17*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H17*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
@@ -11009,15 +11043,15 @@
       </c>
       <c r="M18" s="46" cm="1">
         <f t="array" ref="M18">IF(A18="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L18))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L18)*(A$2:A$201&lt;A18))+1)</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="N18" s="46" cm="1">
         <f t="array" aca="1" ref="N18" ca="1">IF(A18="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I18+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J18+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K18)&gt;0)*((F18*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G18*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H18*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.1421346318750076</v>
+        <v>1.1267245715255043</v>
       </c>
       <c r="O18" s="46" cm="1">
         <f t="array" aca="1" ref="O18" ca="1">IF(A18="","",IF(L18=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I18+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J18+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K18)&gt;0)*((F18*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G18*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H18*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L18))</f>
-        <v>30.46875</v>
+        <v>31.125</v>
       </c>
       <c r="P18" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -11075,19 +11109,19 @@
       </c>
       <c r="M19" s="46" cm="1">
         <f t="array" ref="M19">IF(A19="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L19))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L19)*(A$2:A$201&lt;A19))+1)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N19" s="46" cm="1">
         <f t="array" aca="1" ref="N19" ca="1">IF(A19="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I19+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J19+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K19)&gt;0)*((F19*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G19*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H19*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>0.40523316839106321</v>
+        <v>0.3933013689111251</v>
       </c>
       <c r="O19" s="46" cm="1">
         <f t="array" aca="1" ref="O19" ca="1">IF(A19="","",IF(L19=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I19+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J19+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K19)&gt;0)*((F19*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G19*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H19*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L19))</f>
-        <v>35.5</v>
+        <v>36.857142857142854</v>
       </c>
       <c r="P19" s="46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.39436619718309857</v>
+        <v>0.37984496124031009</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.35">
@@ -11137,19 +11171,19 @@
       </c>
       <c r="L20" s="46" cm="1">
         <f t="array" ref="L20">IF(A20="",0,SUMPRODUCT((A$2:A$201&lt;&gt;"")*((F$2:F$201*I20+G$2:G$201*J20+H$2:H$201*K20)&gt;0)*((F20*I$2:I$201+G20*J$2:J$201+H20*K$2:K$201)&gt;0))-IF(F20*I20+G20*J20+H20*K20&gt;0,1,0))</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M20" s="46" cm="1">
         <f t="array" ref="M20">IF(A20="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L20))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L20)*(A$2:A$201&lt;A20))+1)</f>
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="N20" s="46" cm="1">
         <f t="array" aca="1" ref="N20" ca="1">IF(A20="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I20+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J20+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K20)&gt;0)*((F20*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G20*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H20*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.8542540792540783</v>
+        <v>1.8992740998838558</v>
       </c>
       <c r="O20" s="46" cm="1">
         <f t="array" aca="1" ref="O20" ca="1">IF(A20="","",IF(L20=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I20+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J20+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K20)&gt;0)*((F20*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G20*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H20*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L20))</f>
-        <v>25.473684210526315</v>
+        <v>25.692307692307693</v>
       </c>
       <c r="P20" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -11207,19 +11241,19 @@
       </c>
       <c r="M21" s="46" cm="1">
         <f t="array" ref="M21">IF(A21="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L21))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L21)*(A$2:A$201&lt;A21))+1)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N21" s="46" cm="1">
         <f t="array" aca="1" ref="N21" ca="1">IF(A21="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I21+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J21+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K21)&gt;0)*((F21*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G21*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H21*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>0.40523316839106321</v>
+        <v>0.3933013689111251</v>
       </c>
       <c r="O21" s="46" cm="1">
         <f t="array" aca="1" ref="O21" ca="1">IF(A21="","",IF(L21=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I21+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J21+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K21)&gt;0)*((F21*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G21*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H21*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L21))</f>
-        <v>35.5</v>
+        <v>36.857142857142854</v>
       </c>
       <c r="P21" s="46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.39436619718309857</v>
+        <v>0.37984496124031009</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.35">
@@ -11273,19 +11307,19 @@
       </c>
       <c r="M22" s="46" cm="1">
         <f t="array" ref="M22">IF(A22="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L22))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L22)*(A$2:A$201&lt;A22))+1)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N22" s="46" cm="1">
         <f t="array" aca="1" ref="N22" ca="1">IF(A22="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I22+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J22+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K22)&gt;0)*((F22*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G22*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H22*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>0.40523316839106321</v>
+        <v>0.3933013689111251</v>
       </c>
       <c r="O22" s="46" cm="1">
         <f t="array" aca="1" ref="O22" ca="1">IF(A22="","",IF(L22=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I22+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J22+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K22)&gt;0)*((F22*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G22*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H22*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L22))</f>
-        <v>35.5</v>
+        <v>36.857142857142854</v>
       </c>
       <c r="P22" s="46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.39436619718309857</v>
+        <v>0.37984496124031009</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.35">
@@ -11335,19 +11369,19 @@
       </c>
       <c r="L23" s="46" cm="1">
         <f t="array" ref="L23">IF(A23="",0,SUMPRODUCT((A$2:A$201&lt;&gt;"")*((F$2:F$201*I23+G$2:G$201*J23+H$2:H$201*K23)&gt;0)*((F23*I$2:I$201+G23*J$2:J$201+H23*K$2:K$201)&gt;0))-IF(F23*I23+G23*J23+H23*K23&gt;0,1,0))</f>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M23" s="46" cm="1">
         <f t="array" ref="M23">IF(A23="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L23))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L23)*(A$2:A$201&lt;A23))+1)</f>
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="N23" s="46" cm="1">
         <f t="array" aca="1" ref="N23" ca="1">IF(A23="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I23+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J23+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K23)&gt;0)*((F23*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G23*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H23*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.898407103956302</v>
+        <v>2.0314339725315333</v>
       </c>
       <c r="O23" s="46" cm="1">
         <f t="array" aca="1" ref="O23" ca="1">IF(A23="","",IF(L23=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I23+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J23+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K23)&gt;0)*((F23*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G23*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H23*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L23))</f>
-        <v>25.384615384615383</v>
+        <v>25.26829268292683</v>
       </c>
       <c r="P23" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -11401,23 +11435,23 @@
       </c>
       <c r="L24" s="46" cm="1">
         <f t="array" ref="L24">IF(A24="",0,SUMPRODUCT((A$2:A$201&lt;&gt;"")*((F$2:F$201*I24+G$2:G$201*J24+H$2:H$201*K24)&gt;0)*((F24*I$2:I$201+G24*J$2:J$201+H24*K$2:K$201)&gt;0))-IF(F24*I24+G24*J24+H24*K24&gt;0,1,0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M24" s="46" cm="1">
         <f t="array" ref="M24">IF(A24="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L24))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L24)*(A$2:A$201&lt;A24))+1)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N24" s="46" cm="1">
         <f t="array" aca="1" ref="N24" ca="1">IF(A24="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I24+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J24+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K24)&gt;0)*((F24*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G24*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H24*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>0.34799411115200596</v>
+        <v>0.39991512552488162</v>
       </c>
       <c r="O24" s="46" cm="1">
         <f t="array" aca="1" ref="O24" ca="1">IF(A24="","",IF(L24=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I24+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J24+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K24)&gt;0)*((F24*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G24*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H24*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L24))</f>
-        <v>36.363636363636367</v>
+        <v>36.166666666666664</v>
       </c>
       <c r="P24" s="46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.30249999999999999</v>
+        <v>0.33179723502304148</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.35">
@@ -11467,19 +11501,19 @@
       </c>
       <c r="L25" s="46" cm="1">
         <f t="array" ref="L25">IF(A25="",0,SUMPRODUCT((A$2:A$201&lt;&gt;"")*((F$2:F$201*I25+G$2:G$201*J25+H$2:H$201*K25)&gt;0)*((F25*I$2:I$201+G25*J$2:J$201+H25*K$2:K$201)&gt;0))-IF(F25*I25+G25*J25+H25*K25&gt;0,1,0))</f>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M25" s="46" cm="1">
         <f t="array" ref="M25">IF(A25="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L25))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L25)*(A$2:A$201&lt;A25))+1)</f>
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N25" s="46" cm="1">
         <f t="array" aca="1" ref="N25" ca="1">IF(A25="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I25+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J25+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K25)&gt;0)*((F25*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G25*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H25*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.898407103956302</v>
+        <v>2.0314339725315333</v>
       </c>
       <c r="O25" s="46" cm="1">
         <f t="array" aca="1" ref="O25" ca="1">IF(A25="","",IF(L25=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I25+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J25+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K25)&gt;0)*((F25*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G25*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H25*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L25))</f>
-        <v>25.384615384615383</v>
+        <v>25.26829268292683</v>
       </c>
       <c r="P25" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -11537,15 +11571,15 @@
       </c>
       <c r="M26" s="46" cm="1">
         <f t="array" ref="M26">IF(A26="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L26))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L26)*(A$2:A$201&lt;A26))+1)</f>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N26" s="46" cm="1">
         <f t="array" aca="1" ref="N26" ca="1">IF(A26="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I26+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J26+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K26)&gt;0)*((F26*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G26*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H26*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.1421346318750076</v>
+        <v>1.1267245715255043</v>
       </c>
       <c r="O26" s="46" cm="1">
         <f t="array" aca="1" ref="O26" ca="1">IF(A26="","",IF(L26=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I26+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J26+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K26)&gt;0)*((F26*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G26*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H26*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L26))</f>
-        <v>30.46875</v>
+        <v>31.125</v>
       </c>
       <c r="P26" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -11603,19 +11637,19 @@
       </c>
       <c r="M27" s="46" cm="1">
         <f t="array" ref="M27">IF(A27="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L27))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L27)*(A$2:A$201&lt;A27))+1)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N27" s="46" cm="1">
         <f t="array" aca="1" ref="N27" ca="1">IF(A27="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I27+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J27+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K27)&gt;0)*((F27*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G27*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H27*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>0.40523316839106321</v>
+        <v>0.3933013689111251</v>
       </c>
       <c r="O27" s="46" cm="1">
         <f t="array" aca="1" ref="O27" ca="1">IF(A27="","",IF(L27=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I27+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J27+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K27)&gt;0)*((F27*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G27*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H27*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L27))</f>
-        <v>35.5</v>
+        <v>36.857142857142854</v>
       </c>
       <c r="P27" s="46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.39436619718309857</v>
+        <v>0.37984496124031009</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.35">
@@ -11669,19 +11703,19 @@
       </c>
       <c r="M28" s="46" cm="1">
         <f t="array" ref="M28">IF(A28="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L28))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L28)*(A$2:A$201&lt;A28))+1)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N28" s="46" cm="1">
         <f t="array" aca="1" ref="N28" ca="1">IF(A28="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I28+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J28+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K28)&gt;0)*((F28*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G28*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H28*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>0.40523316839106321</v>
+        <v>0.3933013689111251</v>
       </c>
       <c r="O28" s="46" cm="1">
         <f t="array" aca="1" ref="O28" ca="1">IF(A28="","",IF(L28=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I28+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J28+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K28)&gt;0)*((F28*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G28*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H28*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L28))</f>
-        <v>35.5</v>
+        <v>36.857142857142854</v>
       </c>
       <c r="P28" s="46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.39436619718309857</v>
+        <v>0.37984496124031009</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.35">
@@ -11735,19 +11769,19 @@
       </c>
       <c r="M29" s="46" cm="1">
         <f t="array" ref="M29">IF(A29="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L29))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L29)*(A$2:A$201&lt;A29))+1)</f>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N29" s="46" cm="1">
         <f t="array" aca="1" ref="N29" ca="1">IF(A29="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I29+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J29+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K29)&gt;0)*((F29*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G29*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H29*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>0.44871142926062846</v>
+        <v>0.43330136891112514</v>
       </c>
       <c r="O29" s="46" cm="1">
         <f t="array" aca="1" ref="O29" ca="1">IF(A29="","",IF(L29=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I29+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J29+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K29)&gt;0)*((F29*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G29*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H29*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L29))</f>
-        <v>34.666666666666664</v>
+        <v>36.06666666666667</v>
       </c>
       <c r="P29" s="46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.43269230769230771</v>
+        <v>0.4158964879852125</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.35">
@@ -11801,19 +11835,19 @@
       </c>
       <c r="M30" s="46" cm="1">
         <f t="array" ref="M30">IF(A30="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L30))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L30)*(A$2:A$201&lt;A30))+1)</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N30" s="46" cm="1">
         <f t="array" aca="1" ref="N30" ca="1">IF(A30="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I30+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J30+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K30)&gt;0)*((F30*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G30*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H30*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>0.40523316839106321</v>
+        <v>0.3933013689111251</v>
       </c>
       <c r="O30" s="46" cm="1">
         <f t="array" aca="1" ref="O30" ca="1">IF(A30="","",IF(L30=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I30+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J30+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K30)&gt;0)*((F30*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G30*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H30*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L30))</f>
-        <v>35.5</v>
+        <v>36.857142857142854</v>
       </c>
       <c r="P30" s="46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.39436619718309857</v>
+        <v>0.37984496124031009</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.35">
@@ -11867,7 +11901,7 @@
       </c>
       <c r="M31" s="46" cm="1">
         <f t="array" ref="M31">IF(A31="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L31))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L31)*(A$2:A$201&lt;A31))+1)</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N31" s="46" cm="1">
         <f t="array" aca="1" ref="N31" ca="1">IF(A31="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I31+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J31+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K31)&gt;0)*((F31*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G31*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H31*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
@@ -11933,7 +11967,7 @@
       </c>
       <c r="M32" s="46" cm="1">
         <f t="array" ref="M32">IF(A32="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L32))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L32)*(A$2:A$201&lt;A32))+1)</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N32" s="46" cm="1">
         <f t="array" aca="1" ref="N32" ca="1">IF(A32="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I32+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J32+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K32)&gt;0)*((F32*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G32*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H32*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
@@ -11999,15 +12033,15 @@
       </c>
       <c r="M33" s="46" cm="1">
         <f t="array" ref="M33">IF(A33="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L33))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L33)*(A$2:A$201&lt;A33))+1)</f>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="N33" s="46" cm="1">
         <f t="array" aca="1" ref="N33" ca="1">IF(A33="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I33+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J33+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K33)&gt;0)*((F33*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G33*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H33*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.1421346318750076</v>
+        <v>1.1267245715255043</v>
       </c>
       <c r="O33" s="46" cm="1">
         <f t="array" aca="1" ref="O33" ca="1">IF(A33="","",IF(L33=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I33+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J33+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K33)&gt;0)*((F33*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G33*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H33*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L33))</f>
-        <v>30.46875</v>
+        <v>31.125</v>
       </c>
       <c r="P33" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -12065,15 +12099,15 @@
       </c>
       <c r="M34" s="46" cm="1">
         <f t="array" ref="M34">IF(A34="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L34))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L34)*(A$2:A$201&lt;A34))+1)</f>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N34" s="46" cm="1">
         <f t="array" aca="1" ref="N34" ca="1">IF(A34="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I34+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J34+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K34)&gt;0)*((F34*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G34*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H34*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.1421346318750076</v>
+        <v>1.1267245715255043</v>
       </c>
       <c r="O34" s="46" cm="1">
         <f t="array" aca="1" ref="O34" ca="1">IF(A34="","",IF(L34=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I34+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J34+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K34)&gt;0)*((F34*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G34*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H34*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L34))</f>
-        <v>30.46875</v>
+        <v>31.125</v>
       </c>
       <c r="P34" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -12127,19 +12161,19 @@
       </c>
       <c r="L35" s="46" cm="1">
         <f t="array" ref="L35">IF(A35="",0,SUMPRODUCT((A$2:A$201&lt;&gt;"")*((F$2:F$201*I35+G$2:G$201*J35+H$2:H$201*K35)&gt;0)*((F35*I$2:I$201+G35*J$2:J$201+H35*K$2:K$201)&gt;0))-IF(F35*I35+G35*J35+H35*K35&gt;0,1,0))</f>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M35" s="46" cm="1">
         <f t="array" ref="M35">IF(A35="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L35))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L35)*(A$2:A$201&lt;A35))+1)</f>
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N35" s="46" cm="1">
         <f t="array" aca="1" ref="N35" ca="1">IF(A35="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I35+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J35+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K35)&gt;0)*((F35*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G35*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H35*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.8984071039563022</v>
+        <v>2.0314339725315333</v>
       </c>
       <c r="O35" s="46" cm="1">
         <f t="array" aca="1" ref="O35" ca="1">IF(A35="","",IF(L35=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I35+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J35+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K35)&gt;0)*((F35*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G35*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H35*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L35))</f>
-        <v>25.384615384615383</v>
+        <v>25.26829268292683</v>
       </c>
       <c r="P35" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -12193,19 +12227,19 @@
       </c>
       <c r="L36" s="46" cm="1">
         <f t="array" ref="L36">IF(A36="",0,SUMPRODUCT((A$2:A$201&lt;&gt;"")*((F$2:F$201*I36+G$2:G$201*J36+H$2:H$201*K36)&gt;0)*((F36*I$2:I$201+G36*J$2:J$201+H36*K$2:K$201)&gt;0))-IF(F36*I36+G36*J36+H36*K36&gt;0,1,0))</f>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M36" s="46" cm="1">
         <f t="array" ref="M36">IF(A36="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L36))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L36)*(A$2:A$201&lt;A36))+1)</f>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N36" s="46" cm="1">
         <f t="array" aca="1" ref="N36" ca="1">IF(A36="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I36+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J36+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K36)&gt;0)*((F36*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G36*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H36*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.8984071039563022</v>
+        <v>2.0314339725315333</v>
       </c>
       <c r="O36" s="46" cm="1">
         <f t="array" aca="1" ref="O36" ca="1">IF(A36="","",IF(L36=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I36+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J36+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K36)&gt;0)*((F36*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G36*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H36*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L36))</f>
-        <v>25.384615384615383</v>
+        <v>25.26829268292683</v>
       </c>
       <c r="P36" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -12263,19 +12297,19 @@
       </c>
       <c r="M37" s="46" cm="1">
         <f t="array" ref="M37">IF(A37="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L37))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L37)*(A$2:A$201&lt;A37))+1)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N37" s="46" cm="1">
         <f t="array" aca="1" ref="N37" ca="1">IF(A37="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I37+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J37+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K37)&gt;0)*((F37*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G37*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H37*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>0.40523316839106321</v>
+        <v>0.3933013689111251</v>
       </c>
       <c r="O37" s="46" cm="1">
         <f t="array" aca="1" ref="O37" ca="1">IF(A37="","",IF(L37=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I37+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J37+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K37)&gt;0)*((F37*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G37*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H37*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L37))</f>
-        <v>35.5</v>
+        <v>36.857142857142854</v>
       </c>
       <c r="P37" s="46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.39436619718309857</v>
+        <v>0.37984496124031009</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.35">
@@ -12329,19 +12363,19 @@
       </c>
       <c r="M38" s="46" cm="1">
         <f t="array" ref="M38">IF(A38="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L38))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L38)*(A$2:A$201&lt;A38))+1)</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N38" s="46" cm="1">
         <f t="array" aca="1" ref="N38" ca="1">IF(A38="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I38+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J38+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K38)&gt;0)*((F38*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G38*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H38*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>0.40523316839106321</v>
+        <v>0.3933013689111251</v>
       </c>
       <c r="O38" s="46" cm="1">
         <f t="array" aca="1" ref="O38" ca="1">IF(A38="","",IF(L38=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I38+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J38+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K38)&gt;0)*((F38*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G38*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H38*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L38))</f>
-        <v>35.5</v>
+        <v>36.857142857142854</v>
       </c>
       <c r="P38" s="46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.39436619718309857</v>
+        <v>0.37984496124031009</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.35">
@@ -12391,19 +12425,19 @@
       </c>
       <c r="L39" s="46" cm="1">
         <f t="array" ref="L39">IF(A39="",0,SUMPRODUCT((A$2:A$201&lt;&gt;"")*((F$2:F$201*I39+G$2:G$201*J39+H$2:H$201*K39)&gt;0)*((F39*I$2:I$201+G39*J$2:J$201+H39*K$2:K$201)&gt;0))-IF(F39*I39+G39*J39+H39*K39&gt;0,1,0))</f>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M39" s="46" cm="1">
         <f t="array" ref="M39">IF(A39="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L39))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L39)*(A$2:A$201&lt;A39))+1)</f>
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="N39" s="46" cm="1">
         <f t="array" aca="1" ref="N39" ca="1">IF(A39="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I39+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J39+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K39)&gt;0)*((F39*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G39*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H39*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.8984071039563022</v>
+        <v>2.0314339725315333</v>
       </c>
       <c r="O39" s="46" cm="1">
         <f t="array" aca="1" ref="O39" ca="1">IF(A39="","",IF(L39=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I39+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J39+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K39)&gt;0)*((F39*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G39*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H39*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L39))</f>
-        <v>25.384615384615383</v>
+        <v>25.26829268292683</v>
       </c>
       <c r="P39" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -12461,15 +12495,15 @@
       </c>
       <c r="M40" s="46" cm="1">
         <f t="array" ref="M40">IF(A40="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L40))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L40)*(A$2:A$201&lt;A40))+1)</f>
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N40" s="46" cm="1">
         <f t="array" aca="1" ref="N40" ca="1">IF(A40="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I40+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J40+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K40)&gt;0)*((F40*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G40*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H40*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.1421346318750076</v>
+        <v>1.1267245715255043</v>
       </c>
       <c r="O40" s="46" cm="1">
         <f t="array" aca="1" ref="O40" ca="1">IF(A40="","",IF(L40=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I40+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J40+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K40)&gt;0)*((F40*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G40*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H40*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L40))</f>
-        <v>30.46875</v>
+        <v>31.125</v>
       </c>
       <c r="P40" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -12527,15 +12561,15 @@
       </c>
       <c r="M41" s="46" cm="1">
         <f t="array" ref="M41">IF(A41="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L41))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L41)*(A$2:A$201&lt;A41))+1)</f>
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="N41" s="46" cm="1">
         <f t="array" aca="1" ref="N41" ca="1">IF(A41="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I41+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J41+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K41)&gt;0)*((F41*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G41*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H41*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.1421346318750076</v>
+        <v>1.1267245715255043</v>
       </c>
       <c r="O41" s="46" cm="1">
         <f t="array" aca="1" ref="O41" ca="1">IF(A41="","",IF(L41=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I41+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J41+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K41)&gt;0)*((F41*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G41*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H41*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L41))</f>
-        <v>30.46875</v>
+        <v>31.125</v>
       </c>
       <c r="P41" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -12593,15 +12627,15 @@
       </c>
       <c r="M42" s="46" cm="1">
         <f t="array" ref="M42">IF(A42="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L42))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L42)*(A$2:A$201&lt;A42))+1)</f>
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N42" s="46" cm="1">
         <f t="array" aca="1" ref="N42" ca="1">IF(A42="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I42+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J42+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K42)&gt;0)*((F42*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G42*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H42*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.1421346318750076</v>
+        <v>1.1267245715255043</v>
       </c>
       <c r="O42" s="46" cm="1">
         <f t="array" aca="1" ref="O42" ca="1">IF(A42="","",IF(L42=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I42+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J42+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K42)&gt;0)*((F42*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G42*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H42*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L42))</f>
-        <v>30.46875</v>
+        <v>31.125</v>
       </c>
       <c r="P42" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -12655,19 +12689,19 @@
       </c>
       <c r="L43" s="46" cm="1">
         <f t="array" ref="L43">IF(A43="",0,SUMPRODUCT((A$2:A$201&lt;&gt;"")*((F$2:F$201*I43+G$2:G$201*J43+H$2:H$201*K43)&gt;0)*((F43*I$2:I$201+G43*J$2:J$201+H43*K$2:K$201)&gt;0))-IF(F43*I43+G43*J43+H43*K43&gt;0,1,0))</f>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M43" s="46" cm="1">
         <f t="array" ref="M43">IF(A43="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L43))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L43)*(A$2:A$201&lt;A43))+1)</f>
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N43" s="46" cm="1">
         <f t="array" aca="1" ref="N43" ca="1">IF(A43="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I43+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J43+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K43)&gt;0)*((F43*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G43*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H43*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.8984071039563022</v>
+        <v>2.0314339725315333</v>
       </c>
       <c r="O43" s="46" cm="1">
         <f t="array" aca="1" ref="O43" ca="1">IF(A43="","",IF(L43=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I43+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J43+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K43)&gt;0)*((F43*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G43*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H43*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L43))</f>
-        <v>25.384615384615383</v>
+        <v>25.26829268292683</v>
       </c>
       <c r="P43" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -12721,23 +12755,23 @@
       </c>
       <c r="L44" s="46" cm="1">
         <f t="array" ref="L44">IF(A44="",0,SUMPRODUCT((A$2:A$201&lt;&gt;"")*((F$2:F$201*I44+G$2:G$201*J44+H$2:H$201*K44)&gt;0)*((F44*I$2:I$201+G44*J$2:J$201+H44*K$2:K$201)&gt;0))-IF(F44*I44+G44*J44+H44*K44&gt;0,1,0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M44" s="46" cm="1">
         <f t="array" ref="M44">IF(A44="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L44))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L44)*(A$2:A$201&lt;A44))+1)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N44" s="46" cm="1">
         <f t="array" aca="1" ref="N44" ca="1">IF(A44="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I44+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J44+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K44)&gt;0)*((F44*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G44*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H44*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>0.3479941111520059</v>
+        <v>0.39991512552488162</v>
       </c>
       <c r="O44" s="46" cm="1">
         <f t="array" aca="1" ref="O44" ca="1">IF(A44="","",IF(L44=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I44+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J44+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K44)&gt;0)*((F44*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G44*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H44*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L44))</f>
-        <v>36.363636363636367</v>
+        <v>36.166666666666664</v>
       </c>
       <c r="P44" s="46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.30249999999999999</v>
+        <v>0.33179723502304148</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.35">
@@ -12787,19 +12821,19 @@
       </c>
       <c r="L45" s="46" cm="1">
         <f t="array" ref="L45">IF(A45="",0,SUMPRODUCT((A$2:A$201&lt;&gt;"")*((F$2:F$201*I45+G$2:G$201*J45+H$2:H$201*K45)&gt;0)*((F45*I$2:I$201+G45*J$2:J$201+H45*K$2:K$201)&gt;0))-IF(F45*I45+G45*J45+H45*K45&gt;0,1,0))</f>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M45" s="46" cm="1">
         <f t="array" ref="M45">IF(A45="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L45))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L45)*(A$2:A$201&lt;A45))+1)</f>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N45" s="46" cm="1">
         <f t="array" aca="1" ref="N45" ca="1">IF(A45="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I45+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J45+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K45)&gt;0)*((F45*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G45*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H45*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.8984071039563022</v>
+        <v>2.0314339725315333</v>
       </c>
       <c r="O45" s="46" cm="1">
         <f t="array" aca="1" ref="O45" ca="1">IF(A45="","",IF(L45=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I45+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J45+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K45)&gt;0)*((F45*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G45*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H45*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L45))</f>
-        <v>25.384615384615383</v>
+        <v>25.26829268292683</v>
       </c>
       <c r="P45" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -12853,19 +12887,19 @@
       </c>
       <c r="L46" s="46" cm="1">
         <f t="array" ref="L46">IF(A46="",0,SUMPRODUCT((A$2:A$201&lt;&gt;"")*((F$2:F$201*I46+G$2:G$201*J46+H$2:H$201*K46)&gt;0)*((F46*I$2:I$201+G46*J$2:J$201+H46*K$2:K$201)&gt;0))-IF(F46*I46+G46*J46+H46*K46&gt;0,1,0))</f>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M46" s="46" cm="1">
         <f t="array" ref="M46">IF(A46="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L46))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L46)*(A$2:A$201&lt;A46))+1)</f>
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N46" s="46" cm="1">
         <f t="array" aca="1" ref="N46" ca="1">IF(A46="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I46+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J46+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K46)&gt;0)*((F46*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G46*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H46*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.8984071039563022</v>
+        <v>2.0314339725315333</v>
       </c>
       <c r="O46" s="46" cm="1">
         <f t="array" aca="1" ref="O46" ca="1">IF(A46="","",IF(L46=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I46+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J46+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K46)&gt;0)*((F46*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G46*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H46*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L46))</f>
-        <v>25.384615384615383</v>
+        <v>25.26829268292683</v>
       </c>
       <c r="P46" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -12923,15 +12957,15 @@
       </c>
       <c r="M47" s="46" cm="1">
         <f t="array" ref="M47">IF(A47="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L47))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L47)*(A$2:A$201&lt;A47))+1)</f>
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N47" s="46" cm="1">
         <f t="array" aca="1" ref="N47" ca="1">IF(A47="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I47+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J47+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K47)&gt;0)*((F47*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G47*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H47*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.1421346318750076</v>
+        <v>1.1267245715255043</v>
       </c>
       <c r="O47" s="46" cm="1">
         <f t="array" aca="1" ref="O47" ca="1">IF(A47="","",IF(L47=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I47+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J47+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K47)&gt;0)*((F47*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G47*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H47*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L47))</f>
-        <v>30.46875</v>
+        <v>31.125</v>
       </c>
       <c r="P47" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -12989,15 +13023,15 @@
       </c>
       <c r="M48" s="46" cm="1">
         <f t="array" ref="M48">IF(A48="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L48))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L48)*(A$2:A$201&lt;A48))+1)</f>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N48" s="46" cm="1">
         <f t="array" aca="1" ref="N48" ca="1">IF(A48="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I48+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J48+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K48)&gt;0)*((F48*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G48*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H48*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.1421346318750076</v>
+        <v>1.1267245715255043</v>
       </c>
       <c r="O48" s="46" cm="1">
         <f t="array" aca="1" ref="O48" ca="1">IF(A48="","",IF(L48=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I48+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J48+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K48)&gt;0)*((F48*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G48*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H48*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L48))</f>
-        <v>30.46875</v>
+        <v>31.125</v>
       </c>
       <c r="P48" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -13055,15 +13089,15 @@
       </c>
       <c r="M49" s="46" cm="1">
         <f t="array" ref="M49">IF(A49="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L49))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L49)*(A$2:A$201&lt;A49))+1)</f>
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="N49" s="46" cm="1">
         <f t="array" aca="1" ref="N49" ca="1">IF(A49="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I49+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J49+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K49)&gt;0)*((F49*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G49*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H49*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.1421346318750076</v>
+        <v>1.1267245715255043</v>
       </c>
       <c r="O49" s="46" cm="1">
         <f t="array" aca="1" ref="O49" ca="1">IF(A49="","",IF(L49=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I49+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J49+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K49)&gt;0)*((F49*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G49*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H49*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L49))</f>
-        <v>30.46875</v>
+        <v>31.125</v>
       </c>
       <c r="P49" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -13117,19 +13151,19 @@
       </c>
       <c r="L50" s="46" cm="1">
         <f t="array" ref="L50">IF(A50="",0,SUMPRODUCT((A$2:A$201&lt;&gt;"")*((F$2:F$201*I50+G$2:G$201*J50+H$2:H$201*K50)&gt;0)*((F50*I$2:I$201+G50*J$2:J$201+H50*K$2:K$201)&gt;0))-IF(F50*I50+G50*J50+H50*K50&gt;0,1,0))</f>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M50" s="46" cm="1">
         <f t="array" ref="M50">IF(A50="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L50))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L50)*(A$2:A$201&lt;A50))+1)</f>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N50" s="46" cm="1">
         <f t="array" aca="1" ref="N50" ca="1">IF(A50="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I50+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J50+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K50)&gt;0)*((F50*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G50*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H50*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>1.8984071039563022</v>
+        <v>2.0314339725315333</v>
       </c>
       <c r="O50" s="46" cm="1">
         <f t="array" aca="1" ref="O50" ca="1">IF(A50="","",IF(L50=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I50+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J50+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K50)&gt;0)*((F50*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G50*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H50*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L50))</f>
-        <v>25.384615384615383</v>
+        <v>25.26829268292683</v>
       </c>
       <c r="P50" s="46">
         <f t="shared" ca="1" si="6"/>
@@ -13187,25 +13221,25 @@
       </c>
       <c r="M51" s="46" cm="1">
         <f t="array" ref="M51">IF(A51="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L51))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L51)*(A$2:A$201&lt;A51))+1)</f>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="N51" s="46" cm="1">
         <f t="array" aca="1" ref="N51" ca="1">IF(A51="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I51+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J51+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K51)&gt;0)*((F51*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G51*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H51*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>0.71259590792838878</v>
+        <v>0.70911764705882363</v>
       </c>
       <c r="O51" s="46" cm="1">
         <f t="array" aca="1" ref="O51" ca="1">IF(A51="","",IF(L51=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I51+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J51+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K51)&gt;0)*((F51*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G51*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H51*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L51))</f>
-        <v>27.333333333333332</v>
+        <v>27.444444444444443</v>
       </c>
       <c r="P51" s="46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.65853658536585369</v>
+        <v>0.65587044534412964</v>
       </c>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A52" s="46" t="str" cm="1">
         <f t="array" ref="A52">IF(ROW()-1&gt;COUNTA('Mii List'!A$2:A$200),"",INDEX('Mii List'!A$2:A$200,ROW()-1))</f>
-        <v>Wayward Vagabond</v>
+        <v>WV</v>
       </c>
       <c r="B52" s="46" t="str">
         <f>IF(A52="","",INDEX('Mii List'!B$2:B$200,MATCH(A52,'Mii List'!A$2:A$200,0)))</f>
@@ -13253,41 +13287,41 @@
       </c>
       <c r="M52" s="46" cm="1">
         <f t="array" ref="M52">IF(A52="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L52))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L52)*(A$2:A$201&lt;A52))+1)</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="N52" s="46" cm="1">
         <f t="array" aca="1" ref="N52" ca="1">IF(A52="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I52+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J52+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K52)&gt;0)*((F52*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G52*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H52*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v>0.40523316839106321</v>
+        <v>0.3933013689111251</v>
       </c>
       <c r="O52" s="46" cm="1">
         <f t="array" aca="1" ref="O52" ca="1">IF(A52="","",IF(L52=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I52+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J52+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K52)&gt;0)*((F52*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G52*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H52*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L52))</f>
-        <v>35.5</v>
+        <v>36.857142857142854</v>
       </c>
       <c r="P52" s="46">
         <f t="shared" ca="1" si="6"/>
-        <v>0.39436619718309857</v>
+        <v>0.37984496124031009</v>
       </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A53" s="46" t="str" cm="1">
         <f t="array" ref="A53">IF(ROW()-1&gt;COUNTA('Mii List'!A$2:A$200),"",INDEX('Mii List'!A$2:A$200,ROW()-1))</f>
-        <v/>
+        <v>Sophia</v>
       </c>
       <c r="B53" s="46" t="str">
         <f>IF(A53="","",INDEX('Mii List'!B$2:B$200,MATCH(A53,'Mii List'!A$2:A$200,0)))</f>
-        <v/>
+        <v>Female</v>
       </c>
       <c r="C53" s="46" t="str">
         <f>IF(A53="","",INDEX('Mii List'!C$2:C$200,MATCH(A53,'Mii List'!A$2:A$200,0)))</f>
-        <v/>
+        <v>✗</v>
       </c>
       <c r="D53" s="46" t="str">
         <f>IF(A53="","",INDEX('Mii List'!D$2:D$200,MATCH(A53,'Mii List'!A$2:A$200,0)))</f>
-        <v/>
+        <v>✓</v>
       </c>
       <c r="E53" s="46" t="str">
         <f>IF(A53="","",INDEX('Mii List'!E$2:E$200,MATCH(A53,'Mii List'!A$2:A$200,0)))</f>
-        <v/>
+        <v>✓</v>
       </c>
       <c r="F53" s="46">
         <f t="shared" si="0"/>
@@ -13295,11 +13329,11 @@
       </c>
       <c r="G53" s="46">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53" s="46">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" s="46">
         <f t="shared" si="3"/>
@@ -13307,7 +13341,7 @@
       </c>
       <c r="J53" s="46">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K53" s="46">
         <f t="shared" si="5"/>
@@ -13315,45 +13349,45 @@
       </c>
       <c r="L53" s="46" cm="1">
         <f t="array" ref="L53">IF(A53="",0,SUMPRODUCT((A$2:A$201&lt;&gt;"")*((F$2:F$201*I53+G$2:G$201*J53+H$2:H$201*K53)&gt;0)*((F53*I$2:I$201+G53*J$2:J$201+H53*K$2:K$201)&gt;0))-IF(F53*I53+G53*J53+H53*K53&gt;0,1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="M53" s="46" t="str" cm="1">
+        <v>14</v>
+      </c>
+      <c r="M53" s="46" cm="1">
         <f t="array" ref="M53">IF(A53="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L53))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L53)*(A$2:A$201&lt;A53))+1)</f>
-        <v/>
-      </c>
-      <c r="N53" s="46" t="str" cm="1">
+        <v>15</v>
+      </c>
+      <c r="N53" s="46" cm="1">
         <f t="array" aca="1" ref="N53" ca="1">IF(A53="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I53+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J53+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K53)&gt;0)*((F53*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G53*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H53*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v/>
-      </c>
-      <c r="O53" s="46" t="str" cm="1">
+        <v>0.54272897833873446</v>
+      </c>
+      <c r="O53" s="46" cm="1">
         <f t="array" aca="1" ref="O53" ca="1">IF(A53="","",IF(L53=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I53+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J53+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K53)&gt;0)*((F53*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G53*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H53*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L53))</f>
-        <v/>
-      </c>
-      <c r="P53" s="46" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <v>33.428571428571431</v>
+      </c>
+      <c r="P53" s="46">
+        <f t="shared" ca="1" si="6"/>
+        <v>0.41880341880341876</v>
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A54" s="46" t="str" cm="1">
         <f t="array" ref="A54">IF(ROW()-1&gt;COUNTA('Mii List'!A$2:A$200),"",INDEX('Mii List'!A$2:A$200,ROW()-1))</f>
-        <v/>
+        <v>Rachel</v>
       </c>
       <c r="B54" s="46" t="str">
         <f>IF(A54="","",INDEX('Mii List'!B$2:B$200,MATCH(A54,'Mii List'!A$2:A$200,0)))</f>
-        <v/>
+        <v>Nonbinary</v>
       </c>
       <c r="C54" s="46" t="str">
         <f>IF(A54="","",INDEX('Mii List'!C$2:C$200,MATCH(A54,'Mii List'!A$2:A$200,0)))</f>
-        <v/>
+        <v>✗</v>
       </c>
       <c r="D54" s="46" t="str">
         <f>IF(A54="","",INDEX('Mii List'!D$2:D$200,MATCH(A54,'Mii List'!A$2:A$200,0)))</f>
-        <v/>
+        <v>✓</v>
       </c>
       <c r="E54" s="46" t="str">
         <f>IF(A54="","",INDEX('Mii List'!E$2:E$200,MATCH(A54,'Mii List'!A$2:A$200,0)))</f>
-        <v/>
+        <v>✓</v>
       </c>
       <c r="F54" s="46">
         <f t="shared" si="0"/>
@@ -13361,11 +13395,11 @@
       </c>
       <c r="G54" s="46">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54" s="46">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I54" s="46">
         <f t="shared" si="3"/>
@@ -13377,27 +13411,27 @@
       </c>
       <c r="K54" s="46">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" s="46" cm="1">
         <f t="array" ref="L54">IF(A54="",0,SUMPRODUCT((A$2:A$201&lt;&gt;"")*((F$2:F$201*I54+G$2:G$201*J54+H$2:H$201*K54)&gt;0)*((F54*I$2:I$201+G54*J$2:J$201+H54*K$2:K$201)&gt;0))-IF(F54*I54+G54*J54+H54*K54&gt;0,1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="M54" s="46" t="str" cm="1">
+        <v>11</v>
+      </c>
+      <c r="M54" s="46" cm="1">
         <f t="array" ref="M54">IF(A54="","",SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201&lt;L54))+SUMPRODUCT((A$2:A$201&lt;&gt;"")*(L$2:L$201=L54)*(A$2:A$201&lt;A54))+1)</f>
-        <v/>
-      </c>
-      <c r="N54" s="46" t="str" cm="1">
+        <v>2</v>
+      </c>
+      <c r="N54" s="46" cm="1">
         <f t="array" aca="1" ref="N54" ca="1">IF(A54="","",SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I54+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J54+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K54)&gt;0)*((F54*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G54*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H54*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*IF(OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1)&gt;0,1/OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1),0)))</f>
-        <v/>
-      </c>
-      <c r="O54" s="46" t="str" cm="1">
+        <v>0.33094076655052262</v>
+      </c>
+      <c r="O54" s="46" cm="1">
         <f t="array" aca="1" ref="O54" ca="1">IF(A54="","",IF(L54=0,0,SUMPRODUCT(((OFFSET(F$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*I54+OFFSET(G$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*J54+OFFSET(H$2,0,0,COUNTA('Mii List'!A$2:A$200),1)*K54)&gt;0)*((F54*OFFSET(I$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+G54*OFFSET(J$2,0,0,COUNTA('Mii List'!A$2:A$200),1)+H54*OFFSET(K$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&gt;0)*(ROW(OFFSET($A$2,0,0,COUNTA('Mii List'!A$2:A$200),1))&lt;&gt;ROW())*OFFSET(L$2,0,0,COUNTA('Mii List'!A$2:A$200),1))/L54))</f>
-        <v/>
-      </c>
-      <c r="P54" s="46" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <v>37.090909090909093</v>
+      </c>
+      <c r="P54" s="46">
+        <f t="shared" ca="1" si="6"/>
+        <v>0.29656862745098039</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.35">
@@ -23128,1466 +23162,1466 @@
   <sheetData>
     <row r="1" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="64" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="2" spans="1:1" s="64" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="65" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="65" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="6" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="65" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="65" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="65" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="65" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="11" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="65" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="13" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="65" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="65" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="65" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="65" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="65" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="65" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="65" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="65" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="65" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="23" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="65" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="24" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="65" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="65" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="65" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="27" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="65" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="65" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="29" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="30" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="65" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="65" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="32" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="65" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="33" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="65" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="34" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="35" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="65" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="36" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="65" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="37" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="65" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="38" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="65" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="39" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="65" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="40" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="41" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="65" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="42" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="65" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="43" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="65" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="44" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="45" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="65" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="46" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="65" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="47" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="65" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="48" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="65" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="49" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="65" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="50" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="65" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="51" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="52" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="65" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="53" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="65" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="54" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="65" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="55" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="65" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="56" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="65" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="57" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="58" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="65" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="59" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="65" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="60" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="61" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="65" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="62" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="65" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="63" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="64" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="65" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="65" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="65" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="66" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="65" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="67" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="65" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="68" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="65" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="69" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="65" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="70" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="65" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="71" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="65" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="72" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="65" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="73" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="74" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="65" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="75" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="65" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="76" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="65" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="77" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="65" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="78" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="65" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="79" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="65" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="80" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="81" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="65" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="82" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="65" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="83" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="65" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="84" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="65" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="85" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="65" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="86" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="65" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="87" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="88" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="89" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="65" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="90" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="65" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="91" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="92" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="65" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="93" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="65" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="94" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="65" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="95" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="65" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="96" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="97" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="65" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="98" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="65" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="99" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="100" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="65" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="101" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="65" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="102" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="65" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="103" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="65" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="104" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="105" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="65" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="106" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="65" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="107" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="65" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="108" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="65" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="109" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="65" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="110" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="65" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="111" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="65" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="112" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="65" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="113" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="65" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="114" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="65" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="115" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="116" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="65" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="117" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="65" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="118" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="65" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="119" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="65" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="120" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="65" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="121" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="65" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="122" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="65" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="123" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="65" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="124" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="65" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="125" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="126" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="65" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="127" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="65" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="128" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="65" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="129" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="65" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="130" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="131" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="65" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="132" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="65" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="133" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="65" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="134" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="65" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="135" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="136" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="65" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="137" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="65" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="138" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="65" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="139" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="140" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="65" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="141" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="65" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="142" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="65" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="143" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="144" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="65" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="145" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="65" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="146" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="65" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="147" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="65" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="148" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="65" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="149" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="65" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="150" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="151" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="65" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="152" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="65" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="153" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="65" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="154" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="65" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="155" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="65" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="156" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="157" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="65" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="158" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="65" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="159" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="65" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="160" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="65" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="161" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="65" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="162" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="65" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="163" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="65" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="164" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="65" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="165" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="65" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="166" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="65" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="167" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="168" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="65" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="169" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="65" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="170" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="65" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="171" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="65" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="172" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="65" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="173" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="174" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="65" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="175" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="65" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="176" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="65" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="177" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="65" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="178" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="65" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="179" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="65" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="180" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="65" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="181" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="182" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="65" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="183" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="65" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="184" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="65" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="185" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="65" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="186" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="65" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="187" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="65" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="188" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="65" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="189" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="65" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="190" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="191" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="65" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="192" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="65" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="193" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="65" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="194" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="65" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="195" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="65" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="196" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" s="65" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="197" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="65" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="198" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="199" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="65" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="200" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="65" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="201" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" s="65" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="202" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" s="65" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="203" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" s="65" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="204" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" s="65" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="205" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A205" s="65" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="206" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" s="65" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="207" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A207" s="65" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="208" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" s="65" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="209" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A209" s="65" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="210" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A210" s="65" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="211" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="212" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" s="65" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="213" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A213" s="65" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="214" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A214" s="65" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="215" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A215" s="65" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="216" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="217" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A217" s="65" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="218" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A218" s="65" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="219" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A219" s="65" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="220" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A220" s="65" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="221" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221" s="65" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="222" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A222" s="65" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="223" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A223" s="65" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="224" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A224" s="65" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="225" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" s="65" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="226" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" s="65" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="227" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="228" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" s="65" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="229" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A229" s="65" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="230" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="231" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" s="65" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="232" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A232" s="65" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="233" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A233" s="65" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="234" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A234" s="65" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="235" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A235" s="65" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="236" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A236" s="65" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="237" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A237" s="65" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="238" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="239" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A239" s="65" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="240" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A240" s="65" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="241" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A241" s="65" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="242" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A242" s="65" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="243" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="244" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A244" s="65" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="245" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A245" s="65" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="246" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A246" s="65" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="247" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A247" s="65" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="248" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A248" s="65" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="249" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A249" s="65" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="250" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A250" s="65" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="251" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="252" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A252" s="65" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="253" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A253" s="65" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="254" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A254" s="65" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="255" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A255" s="65" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="256" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A256" s="65" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="257" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A257" s="65" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="258" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A258" s="65" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="259" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="260" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A260" s="65" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="261" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="262" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A262" s="65" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="263" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A263" s="65" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="264" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A264" s="65" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="265" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A265" s="65" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="266" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A266" s="65" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="267" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A267" s="65" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="268" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A268" s="65" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="269" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A269" s="65" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="270" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A270" s="65" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="271" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="272" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A272" s="65" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="273" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A273" s="65" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="274" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A274" s="65" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="275" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A275" s="65" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="276" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A276" s="65" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="277" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A277" s="65" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="278" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A278" s="65" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="279" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A279" s="65" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="280" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A280" s="65" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="281" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="282" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A282" s="65" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="283" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="284" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A284" s="65" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="285" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="286" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A286" s="65" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="287" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A287" s="65" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="288" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A288" s="65" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="289" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="290" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A290" s="65" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="291" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A291" s="65" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="292" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A292" s="65" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="293" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A293" s="65" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="294" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="295" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A295" s="65" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="296" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A296" s="65" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="297" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="298" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A298" s="65" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="299" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A299" s="65" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="300" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A300" s="65" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="301" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A301" s="65" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="302" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="303" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A303" s="65" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="304" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A304" s="65" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="305" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A305" s="65" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="306" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A306" s="65" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="307" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="308" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A308" s="65" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="309" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A309" s="65" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="310" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="311" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A311" s="65" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="312" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="313" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A313" s="65" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="314" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A314" s="65" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="315" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="316" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A316" s="65" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="317" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A317" s="65" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="318" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A318" s="65" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="319" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A319" s="65" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="320" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="321" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A321" s="65" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="322" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A322" s="65" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="323" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A323" s="65" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="324" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A324" s="65" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="325" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="326" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A326" s="65" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="327" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A327" s="65" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="328" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A328" s="65" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="329" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="330" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A330" s="65" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="331" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A331" s="65" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="332" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="333" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A333" s="65" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="334" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A334" s="65" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="335" spans="1:1" s="66" customFormat="1" x14ac:dyDescent="0.35"/>
     <row r="336" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A336" s="65" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="337" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A337" s="65" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="338" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A338" s="65" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="339" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A339" s="65" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="340" spans="1:1" s="65" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A340" s="65" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
   </sheetData>
